--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,6 +439,28 @@
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Descripcion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>TEST001</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Martillo de prueba FerreteríaMS</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>CAT001</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Producto de evaluación del guardado GitHub API</t>
         </is>
       </c>
     </row>
@@ -637,7 +659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,6 +679,23 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>TEST001</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>U001</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,6 +461,28 @@
       <c r="D2" s="1" t="inlineStr">
         <is>
           <t>Producto de evaluación del guardado GitHub API</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>TEST002</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>Clavo  de prueba FerreteríaMS</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>CAT002</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>Calvo Producto de evaluación del guardado GitHub API</t>
         </is>
       </c>
     </row>
@@ -659,7 +681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -696,6 +718,40 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>TEST002</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>U001</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>TEST002</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>U002</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -450,7 +450,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Martillo de prueba FerreteríaMS</t>
+          <t>Martillo de prueba FerreteríaMS 123</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
@@ -704,7 +704,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>TEST001</t>
+          <t>TEST002</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
@@ -726,29 +726,29 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>U001</t>
+          <t>U002</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>TEST002</t>
+          <t>TEST001</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>U002</t>
+          <t>U001</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -472,17 +472,17 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>Clavo  de prueba FerreteríaMS</t>
+          <t>Martillo de prueba FerreteríaMS 123</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>CAT002</t>
+          <t>CAT001</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>Calvo Producto de evaluación del guardado GitHub API</t>
+          <t>Producto de evaluación del guardado GitHub API</t>
         </is>
       </c>
     </row>
@@ -681,7 +681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -704,7 +704,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>TEST002</t>
+          <t>TEST001</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
@@ -726,27 +726,10 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>U002</t>
+          <t>U001</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>TEST001</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>U001</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -472,7 +472,7 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>Martillo de prueba FerreteríaMS 123</t>
+          <t>Tornillo de prueba FerreteríaMS 123</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,6 +483,28 @@
       <c r="D3" s="1" t="inlineStr">
         <is>
           <t>Producto de evaluación del guardado GitHub API</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Test-003</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Cinta</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>CAT003</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>Cinta electrica</t>
         </is>
       </c>
     </row>
@@ -681,7 +703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -735,6 +757,23 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Test-003</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>U001</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,6 +505,28 @@
       <c r="D4" s="1" t="inlineStr">
         <is>
           <t>Cinta electrica</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Test-004</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>Clavo</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>CAT003</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>Clavo</t>
         </is>
       </c>
     </row>
@@ -703,7 +725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -774,6 +796,23 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Test-004</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>U001</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -472,7 +472,7 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>Tornillo de prueba FerreteríaMS 123</t>
+          <t>Tornillo de prueba FerreteríaMS 123qq</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
@@ -765,7 +765,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>TEST002</t>
+          <t>Test-003</t>
         </is>
       </c>
       <c r="B3" s="1" t="inlineStr">
@@ -782,7 +782,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Test-003</t>
+          <t>Test-004</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
@@ -799,7 +799,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Test-004</t>
+          <t>TEST002</t>
         </is>
       </c>
       <c r="B5" s="1" t="inlineStr">

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>Cinta</t>
+          <t>Cinta1</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
@@ -765,7 +765,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Test-003</t>
+          <t>Test-004</t>
         </is>
       </c>
       <c r="B3" s="1" t="inlineStr">
@@ -782,7 +782,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Test-004</t>
+          <t>TEST002</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
@@ -799,7 +799,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>TEST002</t>
+          <t>Test-003</t>
         </is>
       </c>
       <c r="B5" s="1" t="inlineStr">

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -450,7 +450,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Martillo de prueba FerreteríaMS 123</t>
+          <t>Martillo de prueba FerreteríaMS 1237777</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
@@ -748,7 +748,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>TEST001</t>
+          <t>Test-004</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
@@ -765,7 +765,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Test-004</t>
+          <t>TEST002</t>
         </is>
       </c>
       <c r="B3" s="1" t="inlineStr">
@@ -782,7 +782,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>TEST002</t>
+          <t>Test-003</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
@@ -799,7 +799,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Test-003</t>
+          <t>TEST001</t>
         </is>
       </c>
       <c r="B5" s="1" t="inlineStr">

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -472,7 +472,7 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>Tornillo de prueba FerreteríaMS 123qq</t>
+          <t>Tornillo de prueba FerreteríaMS 123qq88888</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
@@ -765,7 +765,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>TEST002</t>
+          <t>Test-003</t>
         </is>
       </c>
       <c r="B3" s="1" t="inlineStr">
@@ -782,7 +782,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Test-003</t>
+          <t>TEST001</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
@@ -799,7 +799,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>TEST001</t>
+          <t>TEST002</t>
         </is>
       </c>
       <c r="B5" s="1" t="inlineStr">

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -450,7 +450,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Martillo de prueba FerreteríaMS 1237777</t>
+          <t>Martillo de prueba FerreteríaMS</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
@@ -782,7 +782,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>TEST001</t>
+          <t>TEST002</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
@@ -799,7 +799,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>TEST002</t>
+          <t>TEST001</t>
         </is>
       </c>
       <c r="B5" s="1" t="inlineStr">

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -472,7 +472,7 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>Tornillo de prueba FerreteríaMS 123qq88888</t>
+          <t>Tornillo de prueba</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
@@ -782,7 +782,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>TEST002</t>
+          <t>TEST001</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
@@ -799,7 +799,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>TEST001</t>
+          <t>TEST002</t>
         </is>
       </c>
       <c r="B5" s="1" t="inlineStr">

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>Cinta1</t>
+          <t>Cinta</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
@@ -765,7 +765,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Test-003</t>
+          <t>TEST001</t>
         </is>
       </c>
       <c r="B3" s="1" t="inlineStr">
@@ -782,7 +782,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>TEST001</t>
+          <t>TEST002</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
@@ -799,7 +799,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>TEST002</t>
+          <t>Test-003</t>
         </is>
       </c>
       <c r="B5" s="1" t="inlineStr">

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -527,6 +527,28 @@
       <c r="D5" s="1" t="inlineStr">
         <is>
           <t>Clavo</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Test002</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>Taladro</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>CAT003</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>Taladro de inpacto</t>
         </is>
       </c>
     </row>
@@ -725,7 +747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -813,6 +835,23 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Test002</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>U001</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -551,6 +551,24 @@
           <t>Taladro de inpacto</t>
         </is>
       </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>TEST005</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>Tuerca</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>CAT001</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -747,7 +765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -852,6 +870,23 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>TEST005</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>U001</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,6 +441,11 @@
           <t>Descripcion</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -463,6 +468,11 @@
           <t>Producto de evaluación del guardado GitHub API</t>
         </is>
       </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -485,6 +495,11 @@
           <t>Producto de evaluación del guardado GitHub API</t>
         </is>
       </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -507,6 +522,11 @@
           <t>Cinta electrica</t>
         </is>
       </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -529,6 +549,11 @@
           <t>Clavo</t>
         </is>
       </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -551,6 +576,11 @@
           <t>Taladro de inpacto</t>
         </is>
       </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -569,6 +599,11 @@
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr"/>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -643,7 +678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +707,11 @@
           <t>Posicion</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -699,6 +739,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -718,12 +763,17 @@
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -751,6 +801,11 @@
       <c r="E4" s="1" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
     </row>

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -860,7 +860,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>TEST001</t>
+          <t>TEST002</t>
         </is>
       </c>
       <c r="B3" s="1" t="inlineStr">
@@ -877,7 +877,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>TEST002</t>
+          <t>Test-003</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
@@ -894,7 +894,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Test-003</t>
+          <t>Test002</t>
         </is>
       </c>
       <c r="B5" s="1" t="inlineStr">
@@ -911,7 +911,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Test002</t>
+          <t>TEST005</t>
         </is>
       </c>
       <c r="B6" s="1" t="inlineStr">
@@ -928,7 +928,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>TEST005</t>
+          <t>TEST001</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -933,7 +933,7 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>U001</t>
+          <t>U002</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -933,12 +933,29 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>U002</t>
+          <t>U001</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
           <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>TEST001</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>U003</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>Tornillería y fijaciones</t>
+          <t>Tornillería</t>
         </is>
       </c>
     </row>

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -639,7 +639,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Herramientas manuales</t>
+          <t>Herramientas manuales1</t>
         </is>
       </c>
     </row>

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -664,6 +664,18 @@
       <c r="B4" s="1" t="inlineStr">
         <is>
           <t>Material eléctrico</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>CAT-004</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>Equipos</t>
         </is>
       </c>
     </row>

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -675,7 +675,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>Equipos</t>
+          <t>Equipos 123</t>
         </is>
       </c>
     </row>

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -690,7 +690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -816,6 +816,38 @@
         </is>
       </c>
       <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>U-007</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>N8</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -834,7 +834,7 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,6 +600,33 @@
       </c>
       <c r="D7" s="1" t="inlineStr"/>
       <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>P-007</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>Cables</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>CAT-004</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>Cables1</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
@@ -864,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1003,6 +1030,23 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>P-007</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>U-007</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -465,7 +465,7 @@
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>Martillo de uña 16 oz. Artículo de ferretería para trabajos y proyectos relacionados con herramientas manuales..</t>
+          <t>Martillo de uña 16 oz. Artículo de ferretería para trabajos y proyectos relacionados con herramientas.</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>Alicate universal 8 pulg. Artículo de ferretería para trabajos y proyectos relacionados con herramientas manuales.</t>
+          <t>Alicate universal 8 pulg. Artículo de ferretería para trabajos y proyectos relacionados con herramientas manuales 1234.</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr">
@@ -12541,12 +12541,12 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>FER0006</t>
+          <t>FER0007</t>
         </is>
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>UB0006</t>
+          <t>UB0007</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
@@ -12558,12 +12558,12 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>FER0007</t>
+          <t>FER0008</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>UB0007</t>
+          <t>UB0008</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
@@ -12575,12 +12575,12 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>FER0008</t>
+          <t>FER0009</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>UB0008</t>
+          <t>UB0009</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
@@ -12592,12 +12592,12 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>FER0009</t>
+          <t>FER0010</t>
         </is>
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>UB0009</t>
+          <t>UB0010</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
@@ -12609,12 +12609,12 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>FER0010</t>
+          <t>FER0011</t>
         </is>
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>UB0010</t>
+          <t>UB0011</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
@@ -12626,12 +12626,12 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>FER0011</t>
+          <t>FER0012</t>
         </is>
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>UB0011</t>
+          <t>UB0012</t>
         </is>
       </c>
       <c r="C11" s="1" t="inlineStr">
@@ -12643,12 +12643,12 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>FER0012</t>
+          <t>FER0013</t>
         </is>
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>UB0012</t>
+          <t>UB0013</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
@@ -12660,12 +12660,12 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>FER0013</t>
+          <t>FER0014</t>
         </is>
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>UB0013</t>
+          <t>UB0014</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
@@ -12677,12 +12677,12 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>FER0014</t>
+          <t>FER0015</t>
         </is>
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>UB0014</t>
+          <t>UB0015</t>
         </is>
       </c>
       <c r="C14" s="1" t="inlineStr">
@@ -12694,12 +12694,12 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>FER0015</t>
+          <t>FER0016</t>
         </is>
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>UB0015</t>
+          <t>UB0016</t>
         </is>
       </c>
       <c r="C15" s="1" t="inlineStr">
@@ -12711,12 +12711,12 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>FER0016</t>
+          <t>FER0017</t>
         </is>
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>UB0016</t>
+          <t>UB0017</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
@@ -12728,12 +12728,12 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>FER0017</t>
+          <t>FER0018</t>
         </is>
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>UB0017</t>
+          <t>UB0018</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
@@ -12745,12 +12745,12 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>FER0018</t>
+          <t>FER0019</t>
         </is>
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>UB0018</t>
+          <t>UB0019</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr">
@@ -12762,12 +12762,12 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>FER0019</t>
+          <t>FER0020</t>
         </is>
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>UB0019</t>
+          <t>UB0020</t>
         </is>
       </c>
       <c r="C19" s="1" t="inlineStr">
@@ -12779,12 +12779,12 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>FER0020</t>
+          <t>FER0021</t>
         </is>
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>UB0020</t>
+          <t>UB0021</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr">
@@ -12796,12 +12796,12 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>FER0021</t>
+          <t>FER0022</t>
         </is>
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>UB0021</t>
+          <t>UB0022</t>
         </is>
       </c>
       <c r="C21" s="1" t="inlineStr">
@@ -12813,12 +12813,12 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>FER0022</t>
+          <t>FER0023</t>
         </is>
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>UB0022</t>
+          <t>UB0023</t>
         </is>
       </c>
       <c r="C22" s="1" t="inlineStr">
@@ -12830,12 +12830,12 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>FER0023</t>
+          <t>FER0024</t>
         </is>
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>UB0023</t>
+          <t>UB0024</t>
         </is>
       </c>
       <c r="C23" s="1" t="inlineStr">
@@ -12847,12 +12847,12 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>FER0024</t>
+          <t>FER0025</t>
         </is>
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>UB0024</t>
+          <t>UB0025</t>
         </is>
       </c>
       <c r="C24" s="1" t="inlineStr">
@@ -12864,12 +12864,12 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>FER0025</t>
+          <t>FER0026</t>
         </is>
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>UB0025</t>
+          <t>UB0026</t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr">
@@ -12881,12 +12881,12 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>FER0026</t>
+          <t>FER0027</t>
         </is>
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>UB0026</t>
+          <t>UB0027</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr">
@@ -12898,12 +12898,12 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>FER0027</t>
+          <t>FER0028</t>
         </is>
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>UB0027</t>
+          <t>UB0028</t>
         </is>
       </c>
       <c r="C27" s="1" t="inlineStr">
@@ -12915,12 +12915,12 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>FER0028</t>
+          <t>FER0029</t>
         </is>
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>UB0028</t>
+          <t>UB0029</t>
         </is>
       </c>
       <c r="C28" s="1" t="inlineStr">
@@ -12932,12 +12932,12 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>FER0029</t>
+          <t>FER0030</t>
         </is>
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>UB0029</t>
+          <t>UB0030</t>
         </is>
       </c>
       <c r="C29" s="1" t="inlineStr">
@@ -12949,12 +12949,12 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>FER0030</t>
+          <t>FER0031</t>
         </is>
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>UB0030</t>
+          <t>UB0031</t>
         </is>
       </c>
       <c r="C30" s="1" t="inlineStr">
@@ -12966,12 +12966,12 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>FER0031</t>
+          <t>FER0032</t>
         </is>
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>UB0031</t>
+          <t>UB0032</t>
         </is>
       </c>
       <c r="C31" s="1" t="inlineStr">
@@ -12983,12 +12983,12 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>FER0032</t>
+          <t>FER0033</t>
         </is>
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>UB0032</t>
+          <t>UB0033</t>
         </is>
       </c>
       <c r="C32" s="1" t="inlineStr">
@@ -13000,12 +13000,12 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>FER0033</t>
+          <t>FER0034</t>
         </is>
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>UB0033</t>
+          <t>UB0034</t>
         </is>
       </c>
       <c r="C33" s="1" t="inlineStr">
@@ -13017,12 +13017,12 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>FER0034</t>
+          <t>FER0035</t>
         </is>
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>UB0034</t>
+          <t>UB0035</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr">
@@ -13034,12 +13034,12 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>FER0035</t>
+          <t>FER0036</t>
         </is>
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>UB0035</t>
+          <t>UB0036</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
@@ -13051,12 +13051,12 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>FER0036</t>
+          <t>FER0037</t>
         </is>
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>UB0036</t>
+          <t>UB0037</t>
         </is>
       </c>
       <c r="C36" s="1" t="inlineStr">
@@ -13068,12 +13068,12 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>FER0037</t>
+          <t>FER0038</t>
         </is>
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>UB0037</t>
+          <t>UB0038</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
@@ -13085,12 +13085,12 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>FER0038</t>
+          <t>FER0039</t>
         </is>
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>UB0038</t>
+          <t>UB0039</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
@@ -13102,12 +13102,12 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>FER0039</t>
+          <t>FER0040</t>
         </is>
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>UB0039</t>
+          <t>UB0040</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr">
@@ -13119,12 +13119,12 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>FER0040</t>
+          <t>FER0041</t>
         </is>
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>UB0040</t>
+          <t>UB0041</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr">
@@ -13136,12 +13136,12 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>FER0041</t>
+          <t>FER0042</t>
         </is>
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>UB0041</t>
+          <t>UB0042</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
@@ -13153,12 +13153,12 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>FER0042</t>
+          <t>FER0043</t>
         </is>
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>UB0042</t>
+          <t>UB0043</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
@@ -13170,12 +13170,12 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>FER0043</t>
+          <t>FER0044</t>
         </is>
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>UB0043</t>
+          <t>UB0044</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
@@ -13187,12 +13187,12 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>FER0044</t>
+          <t>FER0045</t>
         </is>
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>UB0044</t>
+          <t>UB0045</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
@@ -13204,12 +13204,12 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>FER0045</t>
+          <t>FER0046</t>
         </is>
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>UB0045</t>
+          <t>UB0046</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
@@ -13221,12 +13221,12 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>FER0046</t>
+          <t>FER0047</t>
         </is>
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>UB0046</t>
+          <t>UB0047</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
@@ -13238,12 +13238,12 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>FER0047</t>
+          <t>FER0048</t>
         </is>
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>UB0047</t>
+          <t>UB0048</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr">
@@ -13255,12 +13255,12 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>FER0048</t>
+          <t>FER0049</t>
         </is>
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>UB0048</t>
+          <t>UB0049</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr">
@@ -13272,12 +13272,12 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>FER0049</t>
+          <t>FER0050</t>
         </is>
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>UB0049</t>
+          <t>UB0050</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr">
@@ -13289,12 +13289,12 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>FER0050</t>
+          <t>FER0051</t>
         </is>
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>UB0050</t>
+          <t>UB0051</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
@@ -13306,12 +13306,12 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>FER0051</t>
+          <t>FER0052</t>
         </is>
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>UB0051</t>
+          <t>UB0052</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
@@ -13323,12 +13323,12 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>FER0052</t>
+          <t>FER0053</t>
         </is>
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>UB0052</t>
+          <t>UB0053</t>
         </is>
       </c>
       <c r="C52" s="1" t="inlineStr">
@@ -13340,12 +13340,12 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>FER0053</t>
+          <t>FER0054</t>
         </is>
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>UB0053</t>
+          <t>UB0054</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
@@ -13357,12 +13357,12 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>FER0054</t>
+          <t>FER0055</t>
         </is>
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>UB0054</t>
+          <t>UB0055</t>
         </is>
       </c>
       <c r="C54" s="1" t="inlineStr">
@@ -13374,12 +13374,12 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>FER0055</t>
+          <t>FER0056</t>
         </is>
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>UB0055</t>
+          <t>UB0056</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr">
@@ -13391,12 +13391,12 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>FER0056</t>
+          <t>FER0057</t>
         </is>
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>UB0056</t>
+          <t>UB0057</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr">
@@ -13408,12 +13408,12 @@
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>FER0057</t>
+          <t>FER0058</t>
         </is>
       </c>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>UB0057</t>
+          <t>UB0058</t>
         </is>
       </c>
       <c r="C57" s="1" t="inlineStr">
@@ -13425,12 +13425,12 @@
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>FER0058</t>
+          <t>FER0059</t>
         </is>
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>UB0058</t>
+          <t>UB0059</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
@@ -13442,12 +13442,12 @@
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>FER0059</t>
+          <t>FER0060</t>
         </is>
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>UB0059</t>
+          <t>UB0060</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
@@ -13459,12 +13459,12 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>FER0060</t>
+          <t>FER0061</t>
         </is>
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>UB0060</t>
+          <t>UB0061</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
@@ -13476,12 +13476,12 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>FER0061</t>
+          <t>FER0062</t>
         </is>
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>UB0061</t>
+          <t>UB0062</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
@@ -13493,12 +13493,12 @@
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>FER0062</t>
+          <t>FER0063</t>
         </is>
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>UB0062</t>
+          <t>UB0063</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
@@ -13510,12 +13510,12 @@
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>FER0063</t>
+          <t>FER0064</t>
         </is>
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>UB0063</t>
+          <t>UB0064</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
@@ -13527,12 +13527,12 @@
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>FER0064</t>
+          <t>FER0065</t>
         </is>
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>UB0064</t>
+          <t>UB0065</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
@@ -13544,12 +13544,12 @@
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>FER0065</t>
+          <t>FER0066</t>
         </is>
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>UB0065</t>
+          <t>UB0066</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
@@ -13561,12 +13561,12 @@
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>FER0066</t>
+          <t>FER0067</t>
         </is>
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>UB0066</t>
+          <t>UB0067</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
@@ -13578,12 +13578,12 @@
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>FER0067</t>
+          <t>FER0068</t>
         </is>
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>UB0067</t>
+          <t>UB0068</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
@@ -13595,12 +13595,12 @@
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>FER0068</t>
+          <t>FER0069</t>
         </is>
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>UB0068</t>
+          <t>UB0069</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
@@ -13612,12 +13612,12 @@
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>FER0069</t>
+          <t>FER0070</t>
         </is>
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>UB0069</t>
+          <t>UB0070</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
@@ -13629,12 +13629,12 @@
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>FER0070</t>
+          <t>FER0071</t>
         </is>
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>UB0070</t>
+          <t>UB0071</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr">
@@ -13646,12 +13646,12 @@
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>FER0071</t>
+          <t>FER0072</t>
         </is>
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>UB0071</t>
+          <t>UB0072</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
@@ -13663,12 +13663,12 @@
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>FER0072</t>
+          <t>FER0073</t>
         </is>
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>UB0072</t>
+          <t>UB0073</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
@@ -13680,12 +13680,12 @@
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>FER0073</t>
+          <t>FER0074</t>
         </is>
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>UB0073</t>
+          <t>UB0074</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr">
@@ -13697,12 +13697,12 @@
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>FER0074</t>
+          <t>FER0075</t>
         </is>
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>UB0074</t>
+          <t>UB0075</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
@@ -13714,12 +13714,12 @@
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>FER0075</t>
+          <t>FER0076</t>
         </is>
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>UB0075</t>
+          <t>UB0076</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr">
@@ -13731,12 +13731,12 @@
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>FER0076</t>
+          <t>FER0077</t>
         </is>
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>UB0076</t>
+          <t>UB0077</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
@@ -13748,12 +13748,12 @@
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>FER0077</t>
+          <t>FER0078</t>
         </is>
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>UB0077</t>
+          <t>UB0078</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
@@ -13765,12 +13765,12 @@
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>FER0078</t>
+          <t>FER0079</t>
         </is>
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>UB0078</t>
+          <t>UB0079</t>
         </is>
       </c>
       <c r="C78" s="1" t="inlineStr">
@@ -13782,12 +13782,12 @@
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>FER0079</t>
+          <t>FER0080</t>
         </is>
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>UB0079</t>
+          <t>UB0080</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
@@ -13799,12 +13799,12 @@
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>FER0080</t>
+          <t>FER0081</t>
         </is>
       </c>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>UB0080</t>
+          <t>UB0081</t>
         </is>
       </c>
       <c r="C80" s="1" t="inlineStr">
@@ -13816,12 +13816,12 @@
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>FER0081</t>
+          <t>FER0082</t>
         </is>
       </c>
       <c r="B81" s="1" t="inlineStr">
         <is>
-          <t>UB0081</t>
+          <t>UB0082</t>
         </is>
       </c>
       <c r="C81" s="1" t="inlineStr">
@@ -13833,12 +13833,12 @@
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>FER0082</t>
+          <t>FER0083</t>
         </is>
       </c>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>UB0082</t>
+          <t>UB0083</t>
         </is>
       </c>
       <c r="C82" s="1" t="inlineStr">
@@ -13850,12 +13850,12 @@
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>FER0083</t>
+          <t>FER0084</t>
         </is>
       </c>
       <c r="B83" s="1" t="inlineStr">
         <is>
-          <t>UB0083</t>
+          <t>UB0084</t>
         </is>
       </c>
       <c r="C83" s="1" t="inlineStr">
@@ -13867,12 +13867,12 @@
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>FER0084</t>
+          <t>FER0085</t>
         </is>
       </c>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>UB0084</t>
+          <t>UB0085</t>
         </is>
       </c>
       <c r="C84" s="1" t="inlineStr">
@@ -13884,12 +13884,12 @@
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>FER0085</t>
+          <t>FER0086</t>
         </is>
       </c>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>UB0085</t>
+          <t>UB0086</t>
         </is>
       </c>
       <c r="C85" s="1" t="inlineStr">
@@ -13901,12 +13901,12 @@
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>FER0086</t>
+          <t>FER0087</t>
         </is>
       </c>
       <c r="B86" s="1" t="inlineStr">
         <is>
-          <t>UB0086</t>
+          <t>UB0087</t>
         </is>
       </c>
       <c r="C86" s="1" t="inlineStr">
@@ -13918,12 +13918,12 @@
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>FER0087</t>
+          <t>FER0088</t>
         </is>
       </c>
       <c r="B87" s="1" t="inlineStr">
         <is>
-          <t>UB0087</t>
+          <t>UB0088</t>
         </is>
       </c>
       <c r="C87" s="1" t="inlineStr">
@@ -13935,12 +13935,12 @@
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>FER0088</t>
+          <t>FER0089</t>
         </is>
       </c>
       <c r="B88" s="1" t="inlineStr">
         <is>
-          <t>UB0088</t>
+          <t>UB0089</t>
         </is>
       </c>
       <c r="C88" s="1" t="inlineStr">
@@ -13952,12 +13952,12 @@
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>FER0089</t>
+          <t>FER0090</t>
         </is>
       </c>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>UB0089</t>
+          <t>UB0090</t>
         </is>
       </c>
       <c r="C89" s="1" t="inlineStr">
@@ -13969,12 +13969,12 @@
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>FER0090</t>
+          <t>FER0091</t>
         </is>
       </c>
       <c r="B90" s="1" t="inlineStr">
         <is>
-          <t>UB0090</t>
+          <t>UB0091</t>
         </is>
       </c>
       <c r="C90" s="1" t="inlineStr">
@@ -13986,12 +13986,12 @@
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>FER0091</t>
+          <t>FER0092</t>
         </is>
       </c>
       <c r="B91" s="1" t="inlineStr">
         <is>
-          <t>UB0091</t>
+          <t>UB0092</t>
         </is>
       </c>
       <c r="C91" s="1" t="inlineStr">
@@ -14003,12 +14003,12 @@
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>FER0092</t>
+          <t>FER0093</t>
         </is>
       </c>
       <c r="B92" s="1" t="inlineStr">
         <is>
-          <t>UB0092</t>
+          <t>UB0093</t>
         </is>
       </c>
       <c r="C92" s="1" t="inlineStr">
@@ -14020,12 +14020,12 @@
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>FER0093</t>
+          <t>FER0094</t>
         </is>
       </c>
       <c r="B93" s="1" t="inlineStr">
         <is>
-          <t>UB0093</t>
+          <t>UB0094</t>
         </is>
       </c>
       <c r="C93" s="1" t="inlineStr">
@@ -14037,12 +14037,12 @@
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>FER0094</t>
+          <t>FER0095</t>
         </is>
       </c>
       <c r="B94" s="1" t="inlineStr">
         <is>
-          <t>UB0094</t>
+          <t>UB0095</t>
         </is>
       </c>
       <c r="C94" s="1" t="inlineStr">
@@ -14054,12 +14054,12 @@
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>FER0095</t>
+          <t>FER0096</t>
         </is>
       </c>
       <c r="B95" s="1" t="inlineStr">
         <is>
-          <t>UB0095</t>
+          <t>UB0096</t>
         </is>
       </c>
       <c r="C95" s="1" t="inlineStr">
@@ -14071,12 +14071,12 @@
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>FER0096</t>
+          <t>FER0097</t>
         </is>
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>UB0096</t>
+          <t>UB0097</t>
         </is>
       </c>
       <c r="C96" s="1" t="inlineStr">
@@ -14088,12 +14088,12 @@
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>FER0097</t>
+          <t>FER0098</t>
         </is>
       </c>
       <c r="B97" s="1" t="inlineStr">
         <is>
-          <t>UB0097</t>
+          <t>UB0098</t>
         </is>
       </c>
       <c r="C97" s="1" t="inlineStr">
@@ -14105,12 +14105,12 @@
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>FER0098</t>
+          <t>FER0099</t>
         </is>
       </c>
       <c r="B98" s="1" t="inlineStr">
         <is>
-          <t>UB0098</t>
+          <t>UB0099</t>
         </is>
       </c>
       <c r="C98" s="1" t="inlineStr">
@@ -14122,12 +14122,12 @@
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>FER0099</t>
+          <t>FER0100</t>
         </is>
       </c>
       <c r="B99" s="1" t="inlineStr">
         <is>
-          <t>UB0099</t>
+          <t>UB0100</t>
         </is>
       </c>
       <c r="C99" s="1" t="inlineStr">
@@ -14139,12 +14139,12 @@
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>FER0100</t>
+          <t>FER0101</t>
         </is>
       </c>
       <c r="B100" s="1" t="inlineStr">
         <is>
-          <t>UB0100</t>
+          <t>UB0101</t>
         </is>
       </c>
       <c r="C100" s="1" t="inlineStr">
@@ -14156,12 +14156,12 @@
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>FER0101</t>
+          <t>FER0102</t>
         </is>
       </c>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t>UB0101</t>
+          <t>UB0102</t>
         </is>
       </c>
       <c r="C101" s="1" t="inlineStr">
@@ -14173,12 +14173,12 @@
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>FER0102</t>
+          <t>FER0103</t>
         </is>
       </c>
       <c r="B102" s="1" t="inlineStr">
         <is>
-          <t>UB0102</t>
+          <t>UB0103</t>
         </is>
       </c>
       <c r="C102" s="1" t="inlineStr">
@@ -14190,12 +14190,12 @@
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>FER0103</t>
+          <t>FER0104</t>
         </is>
       </c>
       <c r="B103" s="1" t="inlineStr">
         <is>
-          <t>UB0103</t>
+          <t>UB0104</t>
         </is>
       </c>
       <c r="C103" s="1" t="inlineStr">
@@ -14207,12 +14207,12 @@
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>FER0104</t>
+          <t>FER0105</t>
         </is>
       </c>
       <c r="B104" s="1" t="inlineStr">
         <is>
-          <t>UB0104</t>
+          <t>UB0105</t>
         </is>
       </c>
       <c r="C104" s="1" t="inlineStr">
@@ -14224,12 +14224,12 @@
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>FER0105</t>
+          <t>FER0106</t>
         </is>
       </c>
       <c r="B105" s="1" t="inlineStr">
         <is>
-          <t>UB0105</t>
+          <t>UB0106</t>
         </is>
       </c>
       <c r="C105" s="1" t="inlineStr">
@@ -14241,12 +14241,12 @@
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>FER0106</t>
+          <t>FER0107</t>
         </is>
       </c>
       <c r="B106" s="1" t="inlineStr">
         <is>
-          <t>UB0106</t>
+          <t>UB0107</t>
         </is>
       </c>
       <c r="C106" s="1" t="inlineStr">
@@ -14258,12 +14258,12 @@
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>FER0107</t>
+          <t>FER0108</t>
         </is>
       </c>
       <c r="B107" s="1" t="inlineStr">
         <is>
-          <t>UB0107</t>
+          <t>UB0108</t>
         </is>
       </c>
       <c r="C107" s="1" t="inlineStr">
@@ -14275,12 +14275,12 @@
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>FER0108</t>
+          <t>FER0109</t>
         </is>
       </c>
       <c r="B108" s="1" t="inlineStr">
         <is>
-          <t>UB0108</t>
+          <t>UB0109</t>
         </is>
       </c>
       <c r="C108" s="1" t="inlineStr">
@@ -14292,12 +14292,12 @@
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>FER0109</t>
+          <t>FER0110</t>
         </is>
       </c>
       <c r="B109" s="1" t="inlineStr">
         <is>
-          <t>UB0109</t>
+          <t>UB0110</t>
         </is>
       </c>
       <c r="C109" s="1" t="inlineStr">
@@ -14309,12 +14309,12 @@
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>FER0110</t>
+          <t>FER0111</t>
         </is>
       </c>
       <c r="B110" s="1" t="inlineStr">
         <is>
-          <t>UB0110</t>
+          <t>UB0111</t>
         </is>
       </c>
       <c r="C110" s="1" t="inlineStr">
@@ -14326,12 +14326,12 @@
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>FER0111</t>
+          <t>FER0112</t>
         </is>
       </c>
       <c r="B111" s="1" t="inlineStr">
         <is>
-          <t>UB0111</t>
+          <t>UB0112</t>
         </is>
       </c>
       <c r="C111" s="1" t="inlineStr">
@@ -14343,12 +14343,12 @@
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>FER0112</t>
+          <t>FER0113</t>
         </is>
       </c>
       <c r="B112" s="1" t="inlineStr">
         <is>
-          <t>UB0112</t>
+          <t>UB0113</t>
         </is>
       </c>
       <c r="C112" s="1" t="inlineStr">
@@ -14360,12 +14360,12 @@
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>FER0113</t>
+          <t>FER0114</t>
         </is>
       </c>
       <c r="B113" s="1" t="inlineStr">
         <is>
-          <t>UB0113</t>
+          <t>UB0114</t>
         </is>
       </c>
       <c r="C113" s="1" t="inlineStr">
@@ -14377,12 +14377,12 @@
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>FER0114</t>
+          <t>FER0115</t>
         </is>
       </c>
       <c r="B114" s="1" t="inlineStr">
         <is>
-          <t>UB0114</t>
+          <t>UB0115</t>
         </is>
       </c>
       <c r="C114" s="1" t="inlineStr">
@@ -14394,12 +14394,12 @@
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>FER0115</t>
+          <t>FER0116</t>
         </is>
       </c>
       <c r="B115" s="1" t="inlineStr">
         <is>
-          <t>UB0115</t>
+          <t>UB0116</t>
         </is>
       </c>
       <c r="C115" s="1" t="inlineStr">
@@ -14411,12 +14411,12 @@
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>FER0116</t>
+          <t>FER0117</t>
         </is>
       </c>
       <c r="B116" s="1" t="inlineStr">
         <is>
-          <t>UB0116</t>
+          <t>UB0117</t>
         </is>
       </c>
       <c r="C116" s="1" t="inlineStr">
@@ -14428,12 +14428,12 @@
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>FER0117</t>
+          <t>FER0118</t>
         </is>
       </c>
       <c r="B117" s="1" t="inlineStr">
         <is>
-          <t>UB0117</t>
+          <t>UB0118</t>
         </is>
       </c>
       <c r="C117" s="1" t="inlineStr">
@@ -14445,12 +14445,12 @@
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>FER0118</t>
+          <t>FER0119</t>
         </is>
       </c>
       <c r="B118" s="1" t="inlineStr">
         <is>
-          <t>UB0118</t>
+          <t>UB0119</t>
         </is>
       </c>
       <c r="C118" s="1" t="inlineStr">
@@ -14462,12 +14462,12 @@
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>FER0119</t>
+          <t>FER0120</t>
         </is>
       </c>
       <c r="B119" s="1" t="inlineStr">
         <is>
-          <t>UB0119</t>
+          <t>UB0120</t>
         </is>
       </c>
       <c r="C119" s="1" t="inlineStr">
@@ -14479,12 +14479,12 @@
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>FER0120</t>
+          <t>FER0121</t>
         </is>
       </c>
       <c r="B120" s="1" t="inlineStr">
         <is>
-          <t>UB0120</t>
+          <t>UB0121</t>
         </is>
       </c>
       <c r="C120" s="1" t="inlineStr">
@@ -14496,12 +14496,12 @@
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>FER0121</t>
+          <t>FER0122</t>
         </is>
       </c>
       <c r="B121" s="1" t="inlineStr">
         <is>
-          <t>UB0121</t>
+          <t>UB0122</t>
         </is>
       </c>
       <c r="C121" s="1" t="inlineStr">
@@ -14513,12 +14513,12 @@
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>FER0122</t>
+          <t>FER0123</t>
         </is>
       </c>
       <c r="B122" s="1" t="inlineStr">
         <is>
-          <t>UB0122</t>
+          <t>UB0123</t>
         </is>
       </c>
       <c r="C122" s="1" t="inlineStr">
@@ -14530,12 +14530,12 @@
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>FER0123</t>
+          <t>FER0124</t>
         </is>
       </c>
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t>UB0123</t>
+          <t>UB0124</t>
         </is>
       </c>
       <c r="C123" s="1" t="inlineStr">
@@ -14547,12 +14547,12 @@
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>FER0124</t>
+          <t>FER0125</t>
         </is>
       </c>
       <c r="B124" s="1" t="inlineStr">
         <is>
-          <t>UB0124</t>
+          <t>UB0125</t>
         </is>
       </c>
       <c r="C124" s="1" t="inlineStr">
@@ -14564,12 +14564,12 @@
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>FER0125</t>
+          <t>FER0126</t>
         </is>
       </c>
       <c r="B125" s="1" t="inlineStr">
         <is>
-          <t>UB0125</t>
+          <t>UB0126</t>
         </is>
       </c>
       <c r="C125" s="1" t="inlineStr">
@@ -14581,12 +14581,12 @@
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>FER0126</t>
+          <t>FER0127</t>
         </is>
       </c>
       <c r="B126" s="1" t="inlineStr">
         <is>
-          <t>UB0126</t>
+          <t>UB0127</t>
         </is>
       </c>
       <c r="C126" s="1" t="inlineStr">
@@ -14598,12 +14598,12 @@
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>FER0127</t>
+          <t>FER0128</t>
         </is>
       </c>
       <c r="B127" s="1" t="inlineStr">
         <is>
-          <t>UB0127</t>
+          <t>UB0128</t>
         </is>
       </c>
       <c r="C127" s="1" t="inlineStr">
@@ -14615,12 +14615,12 @@
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>FER0128</t>
+          <t>FER0129</t>
         </is>
       </c>
       <c r="B128" s="1" t="inlineStr">
         <is>
-          <t>UB0128</t>
+          <t>UB0129</t>
         </is>
       </c>
       <c r="C128" s="1" t="inlineStr">
@@ -14632,12 +14632,12 @@
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>FER0129</t>
+          <t>FER0130</t>
         </is>
       </c>
       <c r="B129" s="1" t="inlineStr">
         <is>
-          <t>UB0129</t>
+          <t>UB0130</t>
         </is>
       </c>
       <c r="C129" s="1" t="inlineStr">
@@ -14649,12 +14649,12 @@
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>FER0130</t>
+          <t>FER0131</t>
         </is>
       </c>
       <c r="B130" s="1" t="inlineStr">
         <is>
-          <t>UB0130</t>
+          <t>UB0131</t>
         </is>
       </c>
       <c r="C130" s="1" t="inlineStr">
@@ -14666,12 +14666,12 @@
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>FER0131</t>
+          <t>FER0132</t>
         </is>
       </c>
       <c r="B131" s="1" t="inlineStr">
         <is>
-          <t>UB0131</t>
+          <t>UB0132</t>
         </is>
       </c>
       <c r="C131" s="1" t="inlineStr">
@@ -14683,12 +14683,12 @@
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>FER0132</t>
+          <t>FER0133</t>
         </is>
       </c>
       <c r="B132" s="1" t="inlineStr">
         <is>
-          <t>UB0132</t>
+          <t>UB0133</t>
         </is>
       </c>
       <c r="C132" s="1" t="inlineStr">
@@ -14700,12 +14700,12 @@
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>FER0133</t>
+          <t>FER0134</t>
         </is>
       </c>
       <c r="B133" s="1" t="inlineStr">
         <is>
-          <t>UB0133</t>
+          <t>UB0134</t>
         </is>
       </c>
       <c r="C133" s="1" t="inlineStr">
@@ -14717,12 +14717,12 @@
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>FER0134</t>
+          <t>FER0135</t>
         </is>
       </c>
       <c r="B134" s="1" t="inlineStr">
         <is>
-          <t>UB0134</t>
+          <t>UB0135</t>
         </is>
       </c>
       <c r="C134" s="1" t="inlineStr">
@@ -14734,12 +14734,12 @@
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>FER0135</t>
+          <t>FER0136</t>
         </is>
       </c>
       <c r="B135" s="1" t="inlineStr">
         <is>
-          <t>UB0135</t>
+          <t>UB0136</t>
         </is>
       </c>
       <c r="C135" s="1" t="inlineStr">
@@ -14751,12 +14751,12 @@
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>FER0136</t>
+          <t>FER0137</t>
         </is>
       </c>
       <c r="B136" s="1" t="inlineStr">
         <is>
-          <t>UB0136</t>
+          <t>UB0137</t>
         </is>
       </c>
       <c r="C136" s="1" t="inlineStr">
@@ -14768,12 +14768,12 @@
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>FER0137</t>
+          <t>FER0138</t>
         </is>
       </c>
       <c r="B137" s="1" t="inlineStr">
         <is>
-          <t>UB0137</t>
+          <t>UB0138</t>
         </is>
       </c>
       <c r="C137" s="1" t="inlineStr">
@@ -14785,12 +14785,12 @@
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>FER0138</t>
+          <t>FER0139</t>
         </is>
       </c>
       <c r="B138" s="1" t="inlineStr">
         <is>
-          <t>UB0138</t>
+          <t>UB0139</t>
         </is>
       </c>
       <c r="C138" s="1" t="inlineStr">
@@ -14802,12 +14802,12 @@
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>FER0139</t>
+          <t>FER0140</t>
         </is>
       </c>
       <c r="B139" s="1" t="inlineStr">
         <is>
-          <t>UB0139</t>
+          <t>UB0140</t>
         </is>
       </c>
       <c r="C139" s="1" t="inlineStr">
@@ -14819,12 +14819,12 @@
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>FER0140</t>
+          <t>FER0141</t>
         </is>
       </c>
       <c r="B140" s="1" t="inlineStr">
         <is>
-          <t>UB0140</t>
+          <t>UB0141</t>
         </is>
       </c>
       <c r="C140" s="1" t="inlineStr">
@@ -14836,12 +14836,12 @@
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>FER0141</t>
+          <t>FER0142</t>
         </is>
       </c>
       <c r="B141" s="1" t="inlineStr">
         <is>
-          <t>UB0141</t>
+          <t>UB0142</t>
         </is>
       </c>
       <c r="C141" s="1" t="inlineStr">
@@ -14853,12 +14853,12 @@
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>FER0142</t>
+          <t>FER0143</t>
         </is>
       </c>
       <c r="B142" s="1" t="inlineStr">
         <is>
-          <t>UB0142</t>
+          <t>UB0143</t>
         </is>
       </c>
       <c r="C142" s="1" t="inlineStr">
@@ -14870,12 +14870,12 @@
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>FER0143</t>
+          <t>FER0144</t>
         </is>
       </c>
       <c r="B143" s="1" t="inlineStr">
         <is>
-          <t>UB0143</t>
+          <t>UB0144</t>
         </is>
       </c>
       <c r="C143" s="1" t="inlineStr">
@@ -14887,12 +14887,12 @@
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>FER0144</t>
+          <t>FER0145</t>
         </is>
       </c>
       <c r="B144" s="1" t="inlineStr">
         <is>
-          <t>UB0144</t>
+          <t>UB0145</t>
         </is>
       </c>
       <c r="C144" s="1" t="inlineStr">
@@ -14904,12 +14904,12 @@
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>FER0145</t>
+          <t>FER0146</t>
         </is>
       </c>
       <c r="B145" s="1" t="inlineStr">
         <is>
-          <t>UB0145</t>
+          <t>UB0146</t>
         </is>
       </c>
       <c r="C145" s="1" t="inlineStr">
@@ -14921,12 +14921,12 @@
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>FER0146</t>
+          <t>FER0147</t>
         </is>
       </c>
       <c r="B146" s="1" t="inlineStr">
         <is>
-          <t>UB0146</t>
+          <t>UB0147</t>
         </is>
       </c>
       <c r="C146" s="1" t="inlineStr">
@@ -14938,12 +14938,12 @@
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>FER0147</t>
+          <t>FER0148</t>
         </is>
       </c>
       <c r="B147" s="1" t="inlineStr">
         <is>
-          <t>UB0147</t>
+          <t>UB0148</t>
         </is>
       </c>
       <c r="C147" s="1" t="inlineStr">
@@ -14955,12 +14955,12 @@
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>FER0148</t>
+          <t>FER0149</t>
         </is>
       </c>
       <c r="B148" s="1" t="inlineStr">
         <is>
-          <t>UB0148</t>
+          <t>UB0149</t>
         </is>
       </c>
       <c r="C148" s="1" t="inlineStr">
@@ -14972,12 +14972,12 @@
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>FER0149</t>
+          <t>FER0150</t>
         </is>
       </c>
       <c r="B149" s="1" t="inlineStr">
         <is>
-          <t>UB0149</t>
+          <t>UB0150</t>
         </is>
       </c>
       <c r="C149" s="1" t="inlineStr">
@@ -14989,12 +14989,12 @@
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>FER0150</t>
+          <t>FER0151</t>
         </is>
       </c>
       <c r="B150" s="1" t="inlineStr">
         <is>
-          <t>UB0150</t>
+          <t>UB0151</t>
         </is>
       </c>
       <c r="C150" s="1" t="inlineStr">
@@ -15006,12 +15006,12 @@
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>FER0151</t>
+          <t>FER0152</t>
         </is>
       </c>
       <c r="B151" s="1" t="inlineStr">
         <is>
-          <t>UB0151</t>
+          <t>UB0152</t>
         </is>
       </c>
       <c r="C151" s="1" t="inlineStr">
@@ -15023,12 +15023,12 @@
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>FER0152</t>
+          <t>FER0153</t>
         </is>
       </c>
       <c r="B152" s="1" t="inlineStr">
         <is>
-          <t>UB0152</t>
+          <t>UB0153</t>
         </is>
       </c>
       <c r="C152" s="1" t="inlineStr">
@@ -15040,12 +15040,12 @@
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>FER0153</t>
+          <t>FER0154</t>
         </is>
       </c>
       <c r="B153" s="1" t="inlineStr">
         <is>
-          <t>UB0153</t>
+          <t>UB0154</t>
         </is>
       </c>
       <c r="C153" s="1" t="inlineStr">
@@ -15057,12 +15057,12 @@
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>FER0154</t>
+          <t>FER0155</t>
         </is>
       </c>
       <c r="B154" s="1" t="inlineStr">
         <is>
-          <t>UB0154</t>
+          <t>UB0155</t>
         </is>
       </c>
       <c r="C154" s="1" t="inlineStr">
@@ -15074,12 +15074,12 @@
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>FER0155</t>
+          <t>FER0156</t>
         </is>
       </c>
       <c r="B155" s="1" t="inlineStr">
         <is>
-          <t>UB0155</t>
+          <t>UB0156</t>
         </is>
       </c>
       <c r="C155" s="1" t="inlineStr">
@@ -15091,12 +15091,12 @@
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>FER0156</t>
+          <t>FER0157</t>
         </is>
       </c>
       <c r="B156" s="1" t="inlineStr">
         <is>
-          <t>UB0156</t>
+          <t>UB0157</t>
         </is>
       </c>
       <c r="C156" s="1" t="inlineStr">
@@ -15108,12 +15108,12 @@
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>FER0157</t>
+          <t>FER0158</t>
         </is>
       </c>
       <c r="B157" s="1" t="inlineStr">
         <is>
-          <t>UB0157</t>
+          <t>UB0158</t>
         </is>
       </c>
       <c r="C157" s="1" t="inlineStr">
@@ -15125,12 +15125,12 @@
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>FER0158</t>
+          <t>FER0159</t>
         </is>
       </c>
       <c r="B158" s="1" t="inlineStr">
         <is>
-          <t>UB0158</t>
+          <t>UB0159</t>
         </is>
       </c>
       <c r="C158" s="1" t="inlineStr">
@@ -15142,12 +15142,12 @@
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>FER0159</t>
+          <t>FER0160</t>
         </is>
       </c>
       <c r="B159" s="1" t="inlineStr">
         <is>
-          <t>UB0159</t>
+          <t>UB0160</t>
         </is>
       </c>
       <c r="C159" s="1" t="inlineStr">
@@ -15159,12 +15159,12 @@
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>FER0160</t>
+          <t>FER0161</t>
         </is>
       </c>
       <c r="B160" s="1" t="inlineStr">
         <is>
-          <t>UB0160</t>
+          <t>UB0161</t>
         </is>
       </c>
       <c r="C160" s="1" t="inlineStr">
@@ -15176,12 +15176,12 @@
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>FER0161</t>
+          <t>FER0162</t>
         </is>
       </c>
       <c r="B161" s="1" t="inlineStr">
         <is>
-          <t>UB0161</t>
+          <t>UB0162</t>
         </is>
       </c>
       <c r="C161" s="1" t="inlineStr">
@@ -15193,12 +15193,12 @@
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>FER0162</t>
+          <t>FER0163</t>
         </is>
       </c>
       <c r="B162" s="1" t="inlineStr">
         <is>
-          <t>UB0162</t>
+          <t>UB0163</t>
         </is>
       </c>
       <c r="C162" s="1" t="inlineStr">
@@ -15210,12 +15210,12 @@
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>FER0163</t>
+          <t>FER0164</t>
         </is>
       </c>
       <c r="B163" s="1" t="inlineStr">
         <is>
-          <t>UB0163</t>
+          <t>UB0164</t>
         </is>
       </c>
       <c r="C163" s="1" t="inlineStr">
@@ -15227,12 +15227,12 @@
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>FER0164</t>
+          <t>FER0165</t>
         </is>
       </c>
       <c r="B164" s="1" t="inlineStr">
         <is>
-          <t>UB0164</t>
+          <t>UB0165</t>
         </is>
       </c>
       <c r="C164" s="1" t="inlineStr">
@@ -15244,12 +15244,12 @@
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>FER0165</t>
+          <t>FER0166</t>
         </is>
       </c>
       <c r="B165" s="1" t="inlineStr">
         <is>
-          <t>UB0165</t>
+          <t>UB0166</t>
         </is>
       </c>
       <c r="C165" s="1" t="inlineStr">
@@ -15261,12 +15261,12 @@
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>FER0166</t>
+          <t>FER0167</t>
         </is>
       </c>
       <c r="B166" s="1" t="inlineStr">
         <is>
-          <t>UB0166</t>
+          <t>UB0167</t>
         </is>
       </c>
       <c r="C166" s="1" t="inlineStr">
@@ -15278,12 +15278,12 @@
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>FER0167</t>
+          <t>FER0168</t>
         </is>
       </c>
       <c r="B167" s="1" t="inlineStr">
         <is>
-          <t>UB0167</t>
+          <t>UB0168</t>
         </is>
       </c>
       <c r="C167" s="1" t="inlineStr">
@@ -15295,12 +15295,12 @@
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>FER0168</t>
+          <t>FER0169</t>
         </is>
       </c>
       <c r="B168" s="1" t="inlineStr">
         <is>
-          <t>UB0168</t>
+          <t>UB0169</t>
         </is>
       </c>
       <c r="C168" s="1" t="inlineStr">
@@ -15312,12 +15312,12 @@
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>FER0169</t>
+          <t>FER0170</t>
         </is>
       </c>
       <c r="B169" s="1" t="inlineStr">
         <is>
-          <t>UB0169</t>
+          <t>UB0170</t>
         </is>
       </c>
       <c r="C169" s="1" t="inlineStr">
@@ -15329,12 +15329,12 @@
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>FER0170</t>
+          <t>FER0171</t>
         </is>
       </c>
       <c r="B170" s="1" t="inlineStr">
         <is>
-          <t>UB0170</t>
+          <t>UB0171</t>
         </is>
       </c>
       <c r="C170" s="1" t="inlineStr">
@@ -15346,12 +15346,12 @@
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t>FER0171</t>
+          <t>FER0172</t>
         </is>
       </c>
       <c r="B171" s="1" t="inlineStr">
         <is>
-          <t>UB0171</t>
+          <t>UB0172</t>
         </is>
       </c>
       <c r="C171" s="1" t="inlineStr">
@@ -15363,12 +15363,12 @@
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t>FER0172</t>
+          <t>FER0173</t>
         </is>
       </c>
       <c r="B172" s="1" t="inlineStr">
         <is>
-          <t>UB0172</t>
+          <t>UB0173</t>
         </is>
       </c>
       <c r="C172" s="1" t="inlineStr">
@@ -15380,12 +15380,12 @@
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
         <is>
-          <t>FER0173</t>
+          <t>FER0174</t>
         </is>
       </c>
       <c r="B173" s="1" t="inlineStr">
         <is>
-          <t>UB0173</t>
+          <t>UB0174</t>
         </is>
       </c>
       <c r="C173" s="1" t="inlineStr">
@@ -15397,12 +15397,12 @@
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
         <is>
-          <t>FER0174</t>
+          <t>FER0175</t>
         </is>
       </c>
       <c r="B174" s="1" t="inlineStr">
         <is>
-          <t>UB0174</t>
+          <t>UB0175</t>
         </is>
       </c>
       <c r="C174" s="1" t="inlineStr">
@@ -15414,12 +15414,12 @@
     <row r="175">
       <c r="A175" s="1" t="inlineStr">
         <is>
-          <t>FER0175</t>
+          <t>FER0176</t>
         </is>
       </c>
       <c r="B175" s="1" t="inlineStr">
         <is>
-          <t>UB0175</t>
+          <t>UB0176</t>
         </is>
       </c>
       <c r="C175" s="1" t="inlineStr">
@@ -15431,12 +15431,12 @@
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
         <is>
-          <t>FER0176</t>
+          <t>FER0177</t>
         </is>
       </c>
       <c r="B176" s="1" t="inlineStr">
         <is>
-          <t>UB0176</t>
+          <t>UB0177</t>
         </is>
       </c>
       <c r="C176" s="1" t="inlineStr">
@@ -15448,12 +15448,12 @@
     <row r="177">
       <c r="A177" s="1" t="inlineStr">
         <is>
-          <t>FER0177</t>
+          <t>FER0178</t>
         </is>
       </c>
       <c r="B177" s="1" t="inlineStr">
         <is>
-          <t>UB0177</t>
+          <t>UB0178</t>
         </is>
       </c>
       <c r="C177" s="1" t="inlineStr">
@@ -15465,12 +15465,12 @@
     <row r="178">
       <c r="A178" s="1" t="inlineStr">
         <is>
-          <t>FER0178</t>
+          <t>FER0179</t>
         </is>
       </c>
       <c r="B178" s="1" t="inlineStr">
         <is>
-          <t>UB0178</t>
+          <t>UB0179</t>
         </is>
       </c>
       <c r="C178" s="1" t="inlineStr">
@@ -15482,12 +15482,12 @@
     <row r="179">
       <c r="A179" s="1" t="inlineStr">
         <is>
-          <t>FER0179</t>
+          <t>FER0180</t>
         </is>
       </c>
       <c r="B179" s="1" t="inlineStr">
         <is>
-          <t>UB0179</t>
+          <t>UB0180</t>
         </is>
       </c>
       <c r="C179" s="1" t="inlineStr">
@@ -15499,12 +15499,12 @@
     <row r="180">
       <c r="A180" s="1" t="inlineStr">
         <is>
-          <t>FER0180</t>
+          <t>FER0181</t>
         </is>
       </c>
       <c r="B180" s="1" t="inlineStr">
         <is>
-          <t>UB0180</t>
+          <t>UB0181</t>
         </is>
       </c>
       <c r="C180" s="1" t="inlineStr">
@@ -15516,12 +15516,12 @@
     <row r="181">
       <c r="A181" s="1" t="inlineStr">
         <is>
-          <t>FER0181</t>
+          <t>FER0182</t>
         </is>
       </c>
       <c r="B181" s="1" t="inlineStr">
         <is>
-          <t>UB0181</t>
+          <t>UB0182</t>
         </is>
       </c>
       <c r="C181" s="1" t="inlineStr">
@@ -15533,12 +15533,12 @@
     <row r="182">
       <c r="A182" s="1" t="inlineStr">
         <is>
-          <t>FER0182</t>
+          <t>FER0183</t>
         </is>
       </c>
       <c r="B182" s="1" t="inlineStr">
         <is>
-          <t>UB0182</t>
+          <t>UB0183</t>
         </is>
       </c>
       <c r="C182" s="1" t="inlineStr">
@@ -15550,12 +15550,12 @@
     <row r="183">
       <c r="A183" s="1" t="inlineStr">
         <is>
-          <t>FER0183</t>
+          <t>FER0184</t>
         </is>
       </c>
       <c r="B183" s="1" t="inlineStr">
         <is>
-          <t>UB0183</t>
+          <t>UB0184</t>
         </is>
       </c>
       <c r="C183" s="1" t="inlineStr">
@@ -15567,12 +15567,12 @@
     <row r="184">
       <c r="A184" s="1" t="inlineStr">
         <is>
-          <t>FER0184</t>
+          <t>FER0185</t>
         </is>
       </c>
       <c r="B184" s="1" t="inlineStr">
         <is>
-          <t>UB0184</t>
+          <t>UB0185</t>
         </is>
       </c>
       <c r="C184" s="1" t="inlineStr">
@@ -15584,12 +15584,12 @@
     <row r="185">
       <c r="A185" s="1" t="inlineStr">
         <is>
-          <t>FER0185</t>
+          <t>FER0186</t>
         </is>
       </c>
       <c r="B185" s="1" t="inlineStr">
         <is>
-          <t>UB0185</t>
+          <t>UB0186</t>
         </is>
       </c>
       <c r="C185" s="1" t="inlineStr">
@@ -15601,12 +15601,12 @@
     <row r="186">
       <c r="A186" s="1" t="inlineStr">
         <is>
-          <t>FER0186</t>
+          <t>FER0187</t>
         </is>
       </c>
       <c r="B186" s="1" t="inlineStr">
         <is>
-          <t>UB0186</t>
+          <t>UB0187</t>
         </is>
       </c>
       <c r="C186" s="1" t="inlineStr">
@@ -15618,12 +15618,12 @@
     <row r="187">
       <c r="A187" s="1" t="inlineStr">
         <is>
-          <t>FER0187</t>
+          <t>FER0188</t>
         </is>
       </c>
       <c r="B187" s="1" t="inlineStr">
         <is>
-          <t>UB0187</t>
+          <t>UB0188</t>
         </is>
       </c>
       <c r="C187" s="1" t="inlineStr">
@@ -15635,12 +15635,12 @@
     <row r="188">
       <c r="A188" s="1" t="inlineStr">
         <is>
-          <t>FER0188</t>
+          <t>FER0189</t>
         </is>
       </c>
       <c r="B188" s="1" t="inlineStr">
         <is>
-          <t>UB0188</t>
+          <t>UB0189</t>
         </is>
       </c>
       <c r="C188" s="1" t="inlineStr">
@@ -15652,12 +15652,12 @@
     <row r="189">
       <c r="A189" s="1" t="inlineStr">
         <is>
-          <t>FER0189</t>
+          <t>FER0190</t>
         </is>
       </c>
       <c r="B189" s="1" t="inlineStr">
         <is>
-          <t>UB0189</t>
+          <t>UB0190</t>
         </is>
       </c>
       <c r="C189" s="1" t="inlineStr">
@@ -15669,12 +15669,12 @@
     <row r="190">
       <c r="A190" s="1" t="inlineStr">
         <is>
-          <t>FER0190</t>
+          <t>FER0191</t>
         </is>
       </c>
       <c r="B190" s="1" t="inlineStr">
         <is>
-          <t>UB0190</t>
+          <t>UB0191</t>
         </is>
       </c>
       <c r="C190" s="1" t="inlineStr">
@@ -15686,12 +15686,12 @@
     <row r="191">
       <c r="A191" s="1" t="inlineStr">
         <is>
-          <t>FER0191</t>
+          <t>FER0192</t>
         </is>
       </c>
       <c r="B191" s="1" t="inlineStr">
         <is>
-          <t>UB0191</t>
+          <t>UB0192</t>
         </is>
       </c>
       <c r="C191" s="1" t="inlineStr">
@@ -15703,12 +15703,12 @@
     <row r="192">
       <c r="A192" s="1" t="inlineStr">
         <is>
-          <t>FER0192</t>
+          <t>FER0193</t>
         </is>
       </c>
       <c r="B192" s="1" t="inlineStr">
         <is>
-          <t>UB0192</t>
+          <t>UB0193</t>
         </is>
       </c>
       <c r="C192" s="1" t="inlineStr">
@@ -15720,12 +15720,12 @@
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
         <is>
-          <t>FER0193</t>
+          <t>FER0194</t>
         </is>
       </c>
       <c r="B193" s="1" t="inlineStr">
         <is>
-          <t>UB0193</t>
+          <t>UB0194</t>
         </is>
       </c>
       <c r="C193" s="1" t="inlineStr">
@@ -15737,12 +15737,12 @@
     <row r="194">
       <c r="A194" s="1" t="inlineStr">
         <is>
-          <t>FER0194</t>
+          <t>FER0195</t>
         </is>
       </c>
       <c r="B194" s="1" t="inlineStr">
         <is>
-          <t>UB0194</t>
+          <t>UB0195</t>
         </is>
       </c>
       <c r="C194" s="1" t="inlineStr">
@@ -15754,12 +15754,12 @@
     <row r="195">
       <c r="A195" s="1" t="inlineStr">
         <is>
-          <t>FER0195</t>
+          <t>FER0196</t>
         </is>
       </c>
       <c r="B195" s="1" t="inlineStr">
         <is>
-          <t>UB0195</t>
+          <t>UB0196</t>
         </is>
       </c>
       <c r="C195" s="1" t="inlineStr">
@@ -15771,12 +15771,12 @@
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
         <is>
-          <t>FER0196</t>
+          <t>FER0197</t>
         </is>
       </c>
       <c r="B196" s="1" t="inlineStr">
         <is>
-          <t>UB0196</t>
+          <t>UB0197</t>
         </is>
       </c>
       <c r="C196" s="1" t="inlineStr">
@@ -15788,12 +15788,12 @@
     <row r="197">
       <c r="A197" s="1" t="inlineStr">
         <is>
-          <t>FER0197</t>
+          <t>FER0198</t>
         </is>
       </c>
       <c r="B197" s="1" t="inlineStr">
         <is>
-          <t>UB0197</t>
+          <t>UB0198</t>
         </is>
       </c>
       <c r="C197" s="1" t="inlineStr">
@@ -15805,12 +15805,12 @@
     <row r="198">
       <c r="A198" s="1" t="inlineStr">
         <is>
-          <t>FER0198</t>
+          <t>FER0199</t>
         </is>
       </c>
       <c r="B198" s="1" t="inlineStr">
         <is>
-          <t>UB0198</t>
+          <t>UB0199</t>
         </is>
       </c>
       <c r="C198" s="1" t="inlineStr">
@@ -15822,12 +15822,12 @@
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
         <is>
-          <t>FER0199</t>
+          <t>FER0200</t>
         </is>
       </c>
       <c r="B199" s="1" t="inlineStr">
         <is>
-          <t>UB0199</t>
+          <t>UB0200</t>
         </is>
       </c>
       <c r="C199" s="1" t="inlineStr">
@@ -15839,12 +15839,12 @@
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
         <is>
-          <t>FER0200</t>
+          <t>FER0001</t>
         </is>
       </c>
       <c r="B200" s="1" t="inlineStr">
         <is>
-          <t>UB0200</t>
+          <t>UB0001</t>
         </is>
       </c>
       <c r="C200" s="1" t="inlineStr">
@@ -15856,12 +15856,12 @@
     <row r="201">
       <c r="A201" s="1" t="inlineStr">
         <is>
-          <t>FER0001</t>
+          <t>FER0006</t>
         </is>
       </c>
       <c r="B201" s="1" t="inlineStr">
         <is>
-          <t>UB0001</t>
+          <t>UB0006</t>
         </is>
       </c>
       <c r="C201" s="1" t="inlineStr">

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -600,7 +600,8 @@
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>Alicate universal 8 pulg. Artículo de ferretería para trabajos y proyectos relacionados con herramientas manuales 1234.</t>
+          <t>Alicate universal 8 pulg. Artículo de ferretería para trabajos y proyectos relacionados con herramientas manuales
+.</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr">

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -5542,7 +5542,7 @@
       </c>
       <c r="D190" s="1" t="inlineStr">
         <is>
-          <t>Cinta adhesiva de ducto gris. Artículo de ferretería para trabajos y proyectos relacionados con adhesivos y mantenimiento.</t>
+          <t>Cinta adhesiva de ducto gris. Artículo de ferretería para trabajos y proyectos relacionados con adhesivos y mantenimiento. INFORMACION MODIFICADA 1234567</t>
         </is>
       </c>
       <c r="E190" s="1" t="inlineStr">
@@ -12451,7 +12451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C201"/>
+  <dimension ref="A1:C202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15636,12 +15636,12 @@
     <row r="188">
       <c r="A188" s="1" t="inlineStr">
         <is>
-          <t>FER0189</t>
+          <t>FER0190</t>
         </is>
       </c>
       <c r="B188" s="1" t="inlineStr">
         <is>
-          <t>UB0189</t>
+          <t>UB0190</t>
         </is>
       </c>
       <c r="C188" s="1" t="inlineStr">
@@ -15653,12 +15653,12 @@
     <row r="189">
       <c r="A189" s="1" t="inlineStr">
         <is>
-          <t>FER0190</t>
+          <t>FER0191</t>
         </is>
       </c>
       <c r="B189" s="1" t="inlineStr">
         <is>
-          <t>UB0190</t>
+          <t>UB0191</t>
         </is>
       </c>
       <c r="C189" s="1" t="inlineStr">
@@ -15670,12 +15670,12 @@
     <row r="190">
       <c r="A190" s="1" t="inlineStr">
         <is>
-          <t>FER0191</t>
+          <t>FER0192</t>
         </is>
       </c>
       <c r="B190" s="1" t="inlineStr">
         <is>
-          <t>UB0191</t>
+          <t>UB0192</t>
         </is>
       </c>
       <c r="C190" s="1" t="inlineStr">
@@ -15687,12 +15687,12 @@
     <row r="191">
       <c r="A191" s="1" t="inlineStr">
         <is>
-          <t>FER0192</t>
+          <t>FER0193</t>
         </is>
       </c>
       <c r="B191" s="1" t="inlineStr">
         <is>
-          <t>UB0192</t>
+          <t>UB0193</t>
         </is>
       </c>
       <c r="C191" s="1" t="inlineStr">
@@ -15704,12 +15704,12 @@
     <row r="192">
       <c r="A192" s="1" t="inlineStr">
         <is>
-          <t>FER0193</t>
+          <t>FER0194</t>
         </is>
       </c>
       <c r="B192" s="1" t="inlineStr">
         <is>
-          <t>UB0193</t>
+          <t>UB0194</t>
         </is>
       </c>
       <c r="C192" s="1" t="inlineStr">
@@ -15721,12 +15721,12 @@
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
         <is>
-          <t>FER0194</t>
+          <t>FER0195</t>
         </is>
       </c>
       <c r="B193" s="1" t="inlineStr">
         <is>
-          <t>UB0194</t>
+          <t>UB0195</t>
         </is>
       </c>
       <c r="C193" s="1" t="inlineStr">
@@ -15738,12 +15738,12 @@
     <row r="194">
       <c r="A194" s="1" t="inlineStr">
         <is>
-          <t>FER0195</t>
+          <t>FER0196</t>
         </is>
       </c>
       <c r="B194" s="1" t="inlineStr">
         <is>
-          <t>UB0195</t>
+          <t>UB0196</t>
         </is>
       </c>
       <c r="C194" s="1" t="inlineStr">
@@ -15755,12 +15755,12 @@
     <row r="195">
       <c r="A195" s="1" t="inlineStr">
         <is>
-          <t>FER0196</t>
+          <t>FER0197</t>
         </is>
       </c>
       <c r="B195" s="1" t="inlineStr">
         <is>
-          <t>UB0196</t>
+          <t>UB0197</t>
         </is>
       </c>
       <c r="C195" s="1" t="inlineStr">
@@ -15772,12 +15772,12 @@
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
         <is>
-          <t>FER0197</t>
+          <t>FER0198</t>
         </is>
       </c>
       <c r="B196" s="1" t="inlineStr">
         <is>
-          <t>UB0197</t>
+          <t>UB0198</t>
         </is>
       </c>
       <c r="C196" s="1" t="inlineStr">
@@ -15789,12 +15789,12 @@
     <row r="197">
       <c r="A197" s="1" t="inlineStr">
         <is>
-          <t>FER0198</t>
+          <t>FER0199</t>
         </is>
       </c>
       <c r="B197" s="1" t="inlineStr">
         <is>
-          <t>UB0198</t>
+          <t>UB0199</t>
         </is>
       </c>
       <c r="C197" s="1" t="inlineStr">
@@ -15806,12 +15806,12 @@
     <row r="198">
       <c r="A198" s="1" t="inlineStr">
         <is>
-          <t>FER0199</t>
+          <t>FER0200</t>
         </is>
       </c>
       <c r="B198" s="1" t="inlineStr">
         <is>
-          <t>UB0199</t>
+          <t>UB0200</t>
         </is>
       </c>
       <c r="C198" s="1" t="inlineStr">
@@ -15823,12 +15823,12 @@
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
         <is>
-          <t>FER0200</t>
+          <t>FER0001</t>
         </is>
       </c>
       <c r="B199" s="1" t="inlineStr">
         <is>
-          <t>UB0200</t>
+          <t>UB0001</t>
         </is>
       </c>
       <c r="C199" s="1" t="inlineStr">
@@ -15840,12 +15840,12 @@
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
         <is>
-          <t>FER0001</t>
+          <t>FER0006</t>
         </is>
       </c>
       <c r="B200" s="1" t="inlineStr">
         <is>
-          <t>UB0001</t>
+          <t>UB0006</t>
         </is>
       </c>
       <c r="C200" s="1" t="inlineStr">
@@ -15857,15 +15857,32 @@
     <row r="201">
       <c r="A201" s="1" t="inlineStr">
         <is>
-          <t>FER0006</t>
+          <t>FER0189</t>
         </is>
       </c>
       <c r="B201" s="1" t="inlineStr">
         <is>
-          <t>UB0006</t>
+          <t>UB0189</t>
         </is>
       </c>
       <c r="C201" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="inlineStr">
+        <is>
+          <t>FER0189</t>
+        </is>
+      </c>
+      <c r="B202" s="1" t="inlineStr">
+        <is>
+          <t>UB0043</t>
+        </is>
+      </c>
+      <c r="C202" s="1" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -5542,7 +5542,7 @@
       </c>
       <c r="D190" s="1" t="inlineStr">
         <is>
-          <t>Cinta adhesiva de ducto gris. Artículo de ferretería para trabajos y proyectos relacionados con adhesivos y mantenimiento. INFORMACION MODIFICADA 1234567</t>
+          <t>Cinta adhesiva de ducto gris. Artículo de ferretería para trabajos y proyectos relacionados con adhesivos y mantenimiento. INFORMACION</t>
         </is>
       </c>
       <c r="E190" s="1" t="inlineStr">
@@ -12451,7 +12451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C202"/>
+  <dimension ref="A1:C201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15867,23 +15867,6 @@
       </c>
       <c r="C201" s="1" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="1" t="inlineStr">
-        <is>
-          <t>FER0189</t>
-        </is>
-      </c>
-      <c r="B202" s="1" t="inlineStr">
-        <is>
-          <t>UB0043</t>
-        </is>
-      </c>
-      <c r="C202" s="1" t="inlineStr">
-        <is>
           <t>Sí</t>
         </is>
       </c>

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -5542,7 +5542,7 @@
       </c>
       <c r="D190" s="1" t="inlineStr">
         <is>
-          <t>Cinta adhesiva de ducto gris. Artículo de ferretería para trabajos y proyectos relacionados con adhesivos y mantenimiento. INFORMACION</t>
+          <t>Cinta adhesiva de ducto gris. Artículo de ferretería para trabajos y proyectos relacionados con adhesivos y mantenimiento. INFORMACION CAMBIADA PARA PROBAR</t>
         </is>
       </c>
       <c r="E190" s="1" t="inlineStr">
@@ -12451,7 +12451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C201"/>
+  <dimension ref="A1:C202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15867,6 +15867,23 @@
       </c>
       <c r="C201" s="1" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="inlineStr">
+        <is>
+          <t>FER0189</t>
+        </is>
+      </c>
+      <c r="B202" s="1" t="inlineStr">
+        <is>
+          <t>UB0001</t>
+        </is>
+      </c>
+      <c r="C202" s="1" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
-          <t>Rotomartillo SDS Plus. Artículo de ferretería para trabajos y proyectos relacionados con herramientas eléctricas.</t>
+          <t>Rotomartillo SDS Plus. Artículo de ferretería para trabajos y proyectos relacionados con herramientas eléctricas. PARA PROBAR</t>
         </is>
       </c>
       <c r="E30" s="1" t="inlineStr">
@@ -12451,7 +12451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C202"/>
+  <dimension ref="A1:C203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12916,12 +12916,12 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>FER0029</t>
+          <t>FER0030</t>
         </is>
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>UB0029</t>
+          <t>UB0030</t>
         </is>
       </c>
       <c r="C28" s="1" t="inlineStr">
@@ -12933,12 +12933,12 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>FER0030</t>
+          <t>FER0031</t>
         </is>
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>UB0030</t>
+          <t>UB0031</t>
         </is>
       </c>
       <c r="C29" s="1" t="inlineStr">
@@ -12950,12 +12950,12 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>FER0031</t>
+          <t>FER0032</t>
         </is>
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>UB0031</t>
+          <t>UB0032</t>
         </is>
       </c>
       <c r="C30" s="1" t="inlineStr">
@@ -12967,12 +12967,12 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>FER0032</t>
+          <t>FER0033</t>
         </is>
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>UB0032</t>
+          <t>UB0033</t>
         </is>
       </c>
       <c r="C31" s="1" t="inlineStr">
@@ -12984,12 +12984,12 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>FER0033</t>
+          <t>FER0034</t>
         </is>
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>UB0033</t>
+          <t>UB0034</t>
         </is>
       </c>
       <c r="C32" s="1" t="inlineStr">
@@ -13001,12 +13001,12 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>FER0034</t>
+          <t>FER0035</t>
         </is>
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>UB0034</t>
+          <t>UB0035</t>
         </is>
       </c>
       <c r="C33" s="1" t="inlineStr">
@@ -13018,12 +13018,12 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>FER0035</t>
+          <t>FER0036</t>
         </is>
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>UB0035</t>
+          <t>UB0036</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr">
@@ -13035,12 +13035,12 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>FER0036</t>
+          <t>FER0037</t>
         </is>
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>UB0036</t>
+          <t>UB0037</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
@@ -13052,12 +13052,12 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>FER0037</t>
+          <t>FER0038</t>
         </is>
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>UB0037</t>
+          <t>UB0038</t>
         </is>
       </c>
       <c r="C36" s="1" t="inlineStr">
@@ -13069,12 +13069,12 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>FER0038</t>
+          <t>FER0039</t>
         </is>
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>UB0038</t>
+          <t>UB0039</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
@@ -13086,12 +13086,12 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>FER0039</t>
+          <t>FER0040</t>
         </is>
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>UB0039</t>
+          <t>UB0040</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
@@ -13103,12 +13103,12 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>FER0040</t>
+          <t>FER0041</t>
         </is>
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>UB0040</t>
+          <t>UB0041</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr">
@@ -13120,12 +13120,12 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>FER0041</t>
+          <t>FER0042</t>
         </is>
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>UB0041</t>
+          <t>UB0042</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr">
@@ -13137,12 +13137,12 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>FER0042</t>
+          <t>FER0043</t>
         </is>
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>UB0042</t>
+          <t>UB0043</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
@@ -13154,12 +13154,12 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>FER0043</t>
+          <t>FER0044</t>
         </is>
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>UB0043</t>
+          <t>UB0044</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
@@ -13171,12 +13171,12 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>FER0044</t>
+          <t>FER0045</t>
         </is>
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>UB0044</t>
+          <t>UB0045</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
@@ -13188,12 +13188,12 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>FER0045</t>
+          <t>FER0046</t>
         </is>
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>UB0045</t>
+          <t>UB0046</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
@@ -13205,12 +13205,12 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>FER0046</t>
+          <t>FER0047</t>
         </is>
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>UB0046</t>
+          <t>UB0047</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
@@ -13222,12 +13222,12 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>FER0047</t>
+          <t>FER0048</t>
         </is>
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>UB0047</t>
+          <t>UB0048</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
@@ -13239,12 +13239,12 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>FER0048</t>
+          <t>FER0049</t>
         </is>
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>UB0048</t>
+          <t>UB0049</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr">
@@ -13256,12 +13256,12 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>FER0049</t>
+          <t>FER0050</t>
         </is>
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>UB0049</t>
+          <t>UB0050</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr">
@@ -13273,12 +13273,12 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>FER0050</t>
+          <t>FER0051</t>
         </is>
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>UB0050</t>
+          <t>UB0051</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr">
@@ -13290,12 +13290,12 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>FER0051</t>
+          <t>FER0052</t>
         </is>
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>UB0051</t>
+          <t>UB0052</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
@@ -13307,12 +13307,12 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>FER0052</t>
+          <t>FER0053</t>
         </is>
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>UB0052</t>
+          <t>UB0053</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
@@ -13324,12 +13324,12 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>FER0053</t>
+          <t>FER0054</t>
         </is>
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>UB0053</t>
+          <t>UB0054</t>
         </is>
       </c>
       <c r="C52" s="1" t="inlineStr">
@@ -13341,12 +13341,12 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>FER0054</t>
+          <t>FER0055</t>
         </is>
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>UB0054</t>
+          <t>UB0055</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
@@ -13358,12 +13358,12 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>FER0055</t>
+          <t>FER0056</t>
         </is>
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>UB0055</t>
+          <t>UB0056</t>
         </is>
       </c>
       <c r="C54" s="1" t="inlineStr">
@@ -13375,12 +13375,12 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>FER0056</t>
+          <t>FER0057</t>
         </is>
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>UB0056</t>
+          <t>UB0057</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr">
@@ -13392,12 +13392,12 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>FER0057</t>
+          <t>FER0058</t>
         </is>
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>UB0057</t>
+          <t>UB0058</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr">
@@ -13409,12 +13409,12 @@
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>FER0058</t>
+          <t>FER0059</t>
         </is>
       </c>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>UB0058</t>
+          <t>UB0059</t>
         </is>
       </c>
       <c r="C57" s="1" t="inlineStr">
@@ -13426,12 +13426,12 @@
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>FER0059</t>
+          <t>FER0060</t>
         </is>
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>UB0059</t>
+          <t>UB0060</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
@@ -13443,12 +13443,12 @@
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>FER0060</t>
+          <t>FER0061</t>
         </is>
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>UB0060</t>
+          <t>UB0061</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
@@ -13460,12 +13460,12 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>FER0061</t>
+          <t>FER0062</t>
         </is>
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>UB0061</t>
+          <t>UB0062</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
@@ -13477,12 +13477,12 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>FER0062</t>
+          <t>FER0063</t>
         </is>
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>UB0062</t>
+          <t>UB0063</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
@@ -13494,12 +13494,12 @@
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>FER0063</t>
+          <t>FER0064</t>
         </is>
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>UB0063</t>
+          <t>UB0064</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
@@ -13511,12 +13511,12 @@
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>FER0064</t>
+          <t>FER0065</t>
         </is>
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>UB0064</t>
+          <t>UB0065</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
@@ -13528,12 +13528,12 @@
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>FER0065</t>
+          <t>FER0066</t>
         </is>
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>UB0065</t>
+          <t>UB0066</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
@@ -13545,12 +13545,12 @@
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>FER0066</t>
+          <t>FER0067</t>
         </is>
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>UB0066</t>
+          <t>UB0067</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
@@ -13562,12 +13562,12 @@
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>FER0067</t>
+          <t>FER0068</t>
         </is>
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>UB0067</t>
+          <t>UB0068</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
@@ -13579,12 +13579,12 @@
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>FER0068</t>
+          <t>FER0069</t>
         </is>
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>UB0068</t>
+          <t>UB0069</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
@@ -13596,12 +13596,12 @@
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>FER0069</t>
+          <t>FER0070</t>
         </is>
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>UB0069</t>
+          <t>UB0070</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
@@ -13613,12 +13613,12 @@
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>FER0070</t>
+          <t>FER0071</t>
         </is>
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>UB0070</t>
+          <t>UB0071</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
@@ -13630,12 +13630,12 @@
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>FER0071</t>
+          <t>FER0072</t>
         </is>
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>UB0071</t>
+          <t>UB0072</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr">
@@ -13647,12 +13647,12 @@
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>FER0072</t>
+          <t>FER0073</t>
         </is>
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>UB0072</t>
+          <t>UB0073</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
@@ -13664,12 +13664,12 @@
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>FER0073</t>
+          <t>FER0074</t>
         </is>
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>UB0073</t>
+          <t>UB0074</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
@@ -13681,12 +13681,12 @@
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>FER0074</t>
+          <t>FER0075</t>
         </is>
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>UB0074</t>
+          <t>UB0075</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr">
@@ -13698,12 +13698,12 @@
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>FER0075</t>
+          <t>FER0076</t>
         </is>
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>UB0075</t>
+          <t>UB0076</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
@@ -13715,12 +13715,12 @@
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>FER0076</t>
+          <t>FER0077</t>
         </is>
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>UB0076</t>
+          <t>UB0077</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr">
@@ -13732,12 +13732,12 @@
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>FER0077</t>
+          <t>FER0078</t>
         </is>
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>UB0077</t>
+          <t>UB0078</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
@@ -13749,12 +13749,12 @@
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>FER0078</t>
+          <t>FER0079</t>
         </is>
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>UB0078</t>
+          <t>UB0079</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
@@ -13766,12 +13766,12 @@
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>FER0079</t>
+          <t>FER0080</t>
         </is>
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>UB0079</t>
+          <t>UB0080</t>
         </is>
       </c>
       <c r="C78" s="1" t="inlineStr">
@@ -13783,12 +13783,12 @@
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>FER0080</t>
+          <t>FER0081</t>
         </is>
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>UB0080</t>
+          <t>UB0081</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
@@ -13800,12 +13800,12 @@
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>FER0081</t>
+          <t>FER0082</t>
         </is>
       </c>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>UB0081</t>
+          <t>UB0082</t>
         </is>
       </c>
       <c r="C80" s="1" t="inlineStr">
@@ -13817,12 +13817,12 @@
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>FER0082</t>
+          <t>FER0083</t>
         </is>
       </c>
       <c r="B81" s="1" t="inlineStr">
         <is>
-          <t>UB0082</t>
+          <t>UB0083</t>
         </is>
       </c>
       <c r="C81" s="1" t="inlineStr">
@@ -13834,12 +13834,12 @@
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>FER0083</t>
+          <t>FER0084</t>
         </is>
       </c>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>UB0083</t>
+          <t>UB0084</t>
         </is>
       </c>
       <c r="C82" s="1" t="inlineStr">
@@ -13851,12 +13851,12 @@
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>FER0084</t>
+          <t>FER0085</t>
         </is>
       </c>
       <c r="B83" s="1" t="inlineStr">
         <is>
-          <t>UB0084</t>
+          <t>UB0085</t>
         </is>
       </c>
       <c r="C83" s="1" t="inlineStr">
@@ -13868,12 +13868,12 @@
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>FER0085</t>
+          <t>FER0086</t>
         </is>
       </c>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>UB0085</t>
+          <t>UB0086</t>
         </is>
       </c>
       <c r="C84" s="1" t="inlineStr">
@@ -13885,12 +13885,12 @@
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>FER0086</t>
+          <t>FER0087</t>
         </is>
       </c>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>UB0086</t>
+          <t>UB0087</t>
         </is>
       </c>
       <c r="C85" s="1" t="inlineStr">
@@ -13902,12 +13902,12 @@
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>FER0087</t>
+          <t>FER0088</t>
         </is>
       </c>
       <c r="B86" s="1" t="inlineStr">
         <is>
-          <t>UB0087</t>
+          <t>UB0088</t>
         </is>
       </c>
       <c r="C86" s="1" t="inlineStr">
@@ -13919,12 +13919,12 @@
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>FER0088</t>
+          <t>FER0089</t>
         </is>
       </c>
       <c r="B87" s="1" t="inlineStr">
         <is>
-          <t>UB0088</t>
+          <t>UB0089</t>
         </is>
       </c>
       <c r="C87" s="1" t="inlineStr">
@@ -13936,12 +13936,12 @@
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>FER0089</t>
+          <t>FER0090</t>
         </is>
       </c>
       <c r="B88" s="1" t="inlineStr">
         <is>
-          <t>UB0089</t>
+          <t>UB0090</t>
         </is>
       </c>
       <c r="C88" s="1" t="inlineStr">
@@ -13953,12 +13953,12 @@
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>FER0090</t>
+          <t>FER0091</t>
         </is>
       </c>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>UB0090</t>
+          <t>UB0091</t>
         </is>
       </c>
       <c r="C89" s="1" t="inlineStr">
@@ -13970,12 +13970,12 @@
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>FER0091</t>
+          <t>FER0092</t>
         </is>
       </c>
       <c r="B90" s="1" t="inlineStr">
         <is>
-          <t>UB0091</t>
+          <t>UB0092</t>
         </is>
       </c>
       <c r="C90" s="1" t="inlineStr">
@@ -13987,12 +13987,12 @@
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>FER0092</t>
+          <t>FER0093</t>
         </is>
       </c>
       <c r="B91" s="1" t="inlineStr">
         <is>
-          <t>UB0092</t>
+          <t>UB0093</t>
         </is>
       </c>
       <c r="C91" s="1" t="inlineStr">
@@ -14004,12 +14004,12 @@
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>FER0093</t>
+          <t>FER0094</t>
         </is>
       </c>
       <c r="B92" s="1" t="inlineStr">
         <is>
-          <t>UB0093</t>
+          <t>UB0094</t>
         </is>
       </c>
       <c r="C92" s="1" t="inlineStr">
@@ -14021,12 +14021,12 @@
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>FER0094</t>
+          <t>FER0095</t>
         </is>
       </c>
       <c r="B93" s="1" t="inlineStr">
         <is>
-          <t>UB0094</t>
+          <t>UB0095</t>
         </is>
       </c>
       <c r="C93" s="1" t="inlineStr">
@@ -14038,12 +14038,12 @@
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>FER0095</t>
+          <t>FER0096</t>
         </is>
       </c>
       <c r="B94" s="1" t="inlineStr">
         <is>
-          <t>UB0095</t>
+          <t>UB0096</t>
         </is>
       </c>
       <c r="C94" s="1" t="inlineStr">
@@ -14055,12 +14055,12 @@
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>FER0096</t>
+          <t>FER0097</t>
         </is>
       </c>
       <c r="B95" s="1" t="inlineStr">
         <is>
-          <t>UB0096</t>
+          <t>UB0097</t>
         </is>
       </c>
       <c r="C95" s="1" t="inlineStr">
@@ -14072,12 +14072,12 @@
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>FER0097</t>
+          <t>FER0098</t>
         </is>
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>UB0097</t>
+          <t>UB0098</t>
         </is>
       </c>
       <c r="C96" s="1" t="inlineStr">
@@ -14089,12 +14089,12 @@
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>FER0098</t>
+          <t>FER0099</t>
         </is>
       </c>
       <c r="B97" s="1" t="inlineStr">
         <is>
-          <t>UB0098</t>
+          <t>UB0099</t>
         </is>
       </c>
       <c r="C97" s="1" t="inlineStr">
@@ -14106,12 +14106,12 @@
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>FER0099</t>
+          <t>FER0100</t>
         </is>
       </c>
       <c r="B98" s="1" t="inlineStr">
         <is>
-          <t>UB0099</t>
+          <t>UB0100</t>
         </is>
       </c>
       <c r="C98" s="1" t="inlineStr">
@@ -14123,12 +14123,12 @@
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>FER0100</t>
+          <t>FER0101</t>
         </is>
       </c>
       <c r="B99" s="1" t="inlineStr">
         <is>
-          <t>UB0100</t>
+          <t>UB0101</t>
         </is>
       </c>
       <c r="C99" s="1" t="inlineStr">
@@ -14140,12 +14140,12 @@
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>FER0101</t>
+          <t>FER0102</t>
         </is>
       </c>
       <c r="B100" s="1" t="inlineStr">
         <is>
-          <t>UB0101</t>
+          <t>UB0102</t>
         </is>
       </c>
       <c r="C100" s="1" t="inlineStr">
@@ -14157,12 +14157,12 @@
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>FER0102</t>
+          <t>FER0103</t>
         </is>
       </c>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t>UB0102</t>
+          <t>UB0103</t>
         </is>
       </c>
       <c r="C101" s="1" t="inlineStr">
@@ -14174,12 +14174,12 @@
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>FER0103</t>
+          <t>FER0104</t>
         </is>
       </c>
       <c r="B102" s="1" t="inlineStr">
         <is>
-          <t>UB0103</t>
+          <t>UB0104</t>
         </is>
       </c>
       <c r="C102" s="1" t="inlineStr">
@@ -14191,12 +14191,12 @@
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>FER0104</t>
+          <t>FER0105</t>
         </is>
       </c>
       <c r="B103" s="1" t="inlineStr">
         <is>
-          <t>UB0104</t>
+          <t>UB0105</t>
         </is>
       </c>
       <c r="C103" s="1" t="inlineStr">
@@ -14208,12 +14208,12 @@
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>FER0105</t>
+          <t>FER0106</t>
         </is>
       </c>
       <c r="B104" s="1" t="inlineStr">
         <is>
-          <t>UB0105</t>
+          <t>UB0106</t>
         </is>
       </c>
       <c r="C104" s="1" t="inlineStr">
@@ -14225,12 +14225,12 @@
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>FER0106</t>
+          <t>FER0107</t>
         </is>
       </c>
       <c r="B105" s="1" t="inlineStr">
         <is>
-          <t>UB0106</t>
+          <t>UB0107</t>
         </is>
       </c>
       <c r="C105" s="1" t="inlineStr">
@@ -14242,12 +14242,12 @@
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>FER0107</t>
+          <t>FER0108</t>
         </is>
       </c>
       <c r="B106" s="1" t="inlineStr">
         <is>
-          <t>UB0107</t>
+          <t>UB0108</t>
         </is>
       </c>
       <c r="C106" s="1" t="inlineStr">
@@ -14259,12 +14259,12 @@
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>FER0108</t>
+          <t>FER0109</t>
         </is>
       </c>
       <c r="B107" s="1" t="inlineStr">
         <is>
-          <t>UB0108</t>
+          <t>UB0109</t>
         </is>
       </c>
       <c r="C107" s="1" t="inlineStr">
@@ -14276,12 +14276,12 @@
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>FER0109</t>
+          <t>FER0110</t>
         </is>
       </c>
       <c r="B108" s="1" t="inlineStr">
         <is>
-          <t>UB0109</t>
+          <t>UB0110</t>
         </is>
       </c>
       <c r="C108" s="1" t="inlineStr">
@@ -14293,12 +14293,12 @@
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>FER0110</t>
+          <t>FER0111</t>
         </is>
       </c>
       <c r="B109" s="1" t="inlineStr">
         <is>
-          <t>UB0110</t>
+          <t>UB0111</t>
         </is>
       </c>
       <c r="C109" s="1" t="inlineStr">
@@ -14310,12 +14310,12 @@
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>FER0111</t>
+          <t>FER0112</t>
         </is>
       </c>
       <c r="B110" s="1" t="inlineStr">
         <is>
-          <t>UB0111</t>
+          <t>UB0112</t>
         </is>
       </c>
       <c r="C110" s="1" t="inlineStr">
@@ -14327,12 +14327,12 @@
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>FER0112</t>
+          <t>FER0113</t>
         </is>
       </c>
       <c r="B111" s="1" t="inlineStr">
         <is>
-          <t>UB0112</t>
+          <t>UB0113</t>
         </is>
       </c>
       <c r="C111" s="1" t="inlineStr">
@@ -14344,12 +14344,12 @@
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>FER0113</t>
+          <t>FER0114</t>
         </is>
       </c>
       <c r="B112" s="1" t="inlineStr">
         <is>
-          <t>UB0113</t>
+          <t>UB0114</t>
         </is>
       </c>
       <c r="C112" s="1" t="inlineStr">
@@ -14361,12 +14361,12 @@
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>FER0114</t>
+          <t>FER0115</t>
         </is>
       </c>
       <c r="B113" s="1" t="inlineStr">
         <is>
-          <t>UB0114</t>
+          <t>UB0115</t>
         </is>
       </c>
       <c r="C113" s="1" t="inlineStr">
@@ -14378,12 +14378,12 @@
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>FER0115</t>
+          <t>FER0116</t>
         </is>
       </c>
       <c r="B114" s="1" t="inlineStr">
         <is>
-          <t>UB0115</t>
+          <t>UB0116</t>
         </is>
       </c>
       <c r="C114" s="1" t="inlineStr">
@@ -14395,12 +14395,12 @@
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>FER0116</t>
+          <t>FER0117</t>
         </is>
       </c>
       <c r="B115" s="1" t="inlineStr">
         <is>
-          <t>UB0116</t>
+          <t>UB0117</t>
         </is>
       </c>
       <c r="C115" s="1" t="inlineStr">
@@ -14412,12 +14412,12 @@
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>FER0117</t>
+          <t>FER0118</t>
         </is>
       </c>
       <c r="B116" s="1" t="inlineStr">
         <is>
-          <t>UB0117</t>
+          <t>UB0118</t>
         </is>
       </c>
       <c r="C116" s="1" t="inlineStr">
@@ -14429,12 +14429,12 @@
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>FER0118</t>
+          <t>FER0119</t>
         </is>
       </c>
       <c r="B117" s="1" t="inlineStr">
         <is>
-          <t>UB0118</t>
+          <t>UB0119</t>
         </is>
       </c>
       <c r="C117" s="1" t="inlineStr">
@@ -14446,12 +14446,12 @@
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>FER0119</t>
+          <t>FER0120</t>
         </is>
       </c>
       <c r="B118" s="1" t="inlineStr">
         <is>
-          <t>UB0119</t>
+          <t>UB0120</t>
         </is>
       </c>
       <c r="C118" s="1" t="inlineStr">
@@ -14463,12 +14463,12 @@
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>FER0120</t>
+          <t>FER0121</t>
         </is>
       </c>
       <c r="B119" s="1" t="inlineStr">
         <is>
-          <t>UB0120</t>
+          <t>UB0121</t>
         </is>
       </c>
       <c r="C119" s="1" t="inlineStr">
@@ -14480,12 +14480,12 @@
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>FER0121</t>
+          <t>FER0122</t>
         </is>
       </c>
       <c r="B120" s="1" t="inlineStr">
         <is>
-          <t>UB0121</t>
+          <t>UB0122</t>
         </is>
       </c>
       <c r="C120" s="1" t="inlineStr">
@@ -14497,12 +14497,12 @@
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>FER0122</t>
+          <t>FER0123</t>
         </is>
       </c>
       <c r="B121" s="1" t="inlineStr">
         <is>
-          <t>UB0122</t>
+          <t>UB0123</t>
         </is>
       </c>
       <c r="C121" s="1" t="inlineStr">
@@ -14514,12 +14514,12 @@
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>FER0123</t>
+          <t>FER0124</t>
         </is>
       </c>
       <c r="B122" s="1" t="inlineStr">
         <is>
-          <t>UB0123</t>
+          <t>UB0124</t>
         </is>
       </c>
       <c r="C122" s="1" t="inlineStr">
@@ -14531,12 +14531,12 @@
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>FER0124</t>
+          <t>FER0125</t>
         </is>
       </c>
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t>UB0124</t>
+          <t>UB0125</t>
         </is>
       </c>
       <c r="C123" s="1" t="inlineStr">
@@ -14548,12 +14548,12 @@
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>FER0125</t>
+          <t>FER0126</t>
         </is>
       </c>
       <c r="B124" s="1" t="inlineStr">
         <is>
-          <t>UB0125</t>
+          <t>UB0126</t>
         </is>
       </c>
       <c r="C124" s="1" t="inlineStr">
@@ -14565,12 +14565,12 @@
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>FER0126</t>
+          <t>FER0127</t>
         </is>
       </c>
       <c r="B125" s="1" t="inlineStr">
         <is>
-          <t>UB0126</t>
+          <t>UB0127</t>
         </is>
       </c>
       <c r="C125" s="1" t="inlineStr">
@@ -14582,12 +14582,12 @@
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>FER0127</t>
+          <t>FER0128</t>
         </is>
       </c>
       <c r="B126" s="1" t="inlineStr">
         <is>
-          <t>UB0127</t>
+          <t>UB0128</t>
         </is>
       </c>
       <c r="C126" s="1" t="inlineStr">
@@ -14599,12 +14599,12 @@
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>FER0128</t>
+          <t>FER0129</t>
         </is>
       </c>
       <c r="B127" s="1" t="inlineStr">
         <is>
-          <t>UB0128</t>
+          <t>UB0129</t>
         </is>
       </c>
       <c r="C127" s="1" t="inlineStr">
@@ -14616,12 +14616,12 @@
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>FER0129</t>
+          <t>FER0130</t>
         </is>
       </c>
       <c r="B128" s="1" t="inlineStr">
         <is>
-          <t>UB0129</t>
+          <t>UB0130</t>
         </is>
       </c>
       <c r="C128" s="1" t="inlineStr">
@@ -14633,12 +14633,12 @@
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>FER0130</t>
+          <t>FER0131</t>
         </is>
       </c>
       <c r="B129" s="1" t="inlineStr">
         <is>
-          <t>UB0130</t>
+          <t>UB0131</t>
         </is>
       </c>
       <c r="C129" s="1" t="inlineStr">
@@ -14650,12 +14650,12 @@
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>FER0131</t>
+          <t>FER0132</t>
         </is>
       </c>
       <c r="B130" s="1" t="inlineStr">
         <is>
-          <t>UB0131</t>
+          <t>UB0132</t>
         </is>
       </c>
       <c r="C130" s="1" t="inlineStr">
@@ -14667,12 +14667,12 @@
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>FER0132</t>
+          <t>FER0133</t>
         </is>
       </c>
       <c r="B131" s="1" t="inlineStr">
         <is>
-          <t>UB0132</t>
+          <t>UB0133</t>
         </is>
       </c>
       <c r="C131" s="1" t="inlineStr">
@@ -14684,12 +14684,12 @@
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>FER0133</t>
+          <t>FER0134</t>
         </is>
       </c>
       <c r="B132" s="1" t="inlineStr">
         <is>
-          <t>UB0133</t>
+          <t>UB0134</t>
         </is>
       </c>
       <c r="C132" s="1" t="inlineStr">
@@ -14701,12 +14701,12 @@
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>FER0134</t>
+          <t>FER0135</t>
         </is>
       </c>
       <c r="B133" s="1" t="inlineStr">
         <is>
-          <t>UB0134</t>
+          <t>UB0135</t>
         </is>
       </c>
       <c r="C133" s="1" t="inlineStr">
@@ -14718,12 +14718,12 @@
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>FER0135</t>
+          <t>FER0136</t>
         </is>
       </c>
       <c r="B134" s="1" t="inlineStr">
         <is>
-          <t>UB0135</t>
+          <t>UB0136</t>
         </is>
       </c>
       <c r="C134" s="1" t="inlineStr">
@@ -14735,12 +14735,12 @@
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>FER0136</t>
+          <t>FER0137</t>
         </is>
       </c>
       <c r="B135" s="1" t="inlineStr">
         <is>
-          <t>UB0136</t>
+          <t>UB0137</t>
         </is>
       </c>
       <c r="C135" s="1" t="inlineStr">
@@ -14752,12 +14752,12 @@
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>FER0137</t>
+          <t>FER0138</t>
         </is>
       </c>
       <c r="B136" s="1" t="inlineStr">
         <is>
-          <t>UB0137</t>
+          <t>UB0138</t>
         </is>
       </c>
       <c r="C136" s="1" t="inlineStr">
@@ -14769,12 +14769,12 @@
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>FER0138</t>
+          <t>FER0139</t>
         </is>
       </c>
       <c r="B137" s="1" t="inlineStr">
         <is>
-          <t>UB0138</t>
+          <t>UB0139</t>
         </is>
       </c>
       <c r="C137" s="1" t="inlineStr">
@@ -14786,12 +14786,12 @@
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>FER0139</t>
+          <t>FER0140</t>
         </is>
       </c>
       <c r="B138" s="1" t="inlineStr">
         <is>
-          <t>UB0139</t>
+          <t>UB0140</t>
         </is>
       </c>
       <c r="C138" s="1" t="inlineStr">
@@ -14803,12 +14803,12 @@
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>FER0140</t>
+          <t>FER0141</t>
         </is>
       </c>
       <c r="B139" s="1" t="inlineStr">
         <is>
-          <t>UB0140</t>
+          <t>UB0141</t>
         </is>
       </c>
       <c r="C139" s="1" t="inlineStr">
@@ -14820,12 +14820,12 @@
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>FER0141</t>
+          <t>FER0142</t>
         </is>
       </c>
       <c r="B140" s="1" t="inlineStr">
         <is>
-          <t>UB0141</t>
+          <t>UB0142</t>
         </is>
       </c>
       <c r="C140" s="1" t="inlineStr">
@@ -14837,12 +14837,12 @@
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>FER0142</t>
+          <t>FER0143</t>
         </is>
       </c>
       <c r="B141" s="1" t="inlineStr">
         <is>
-          <t>UB0142</t>
+          <t>UB0143</t>
         </is>
       </c>
       <c r="C141" s="1" t="inlineStr">
@@ -14854,12 +14854,12 @@
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>FER0143</t>
+          <t>FER0144</t>
         </is>
       </c>
       <c r="B142" s="1" t="inlineStr">
         <is>
-          <t>UB0143</t>
+          <t>UB0144</t>
         </is>
       </c>
       <c r="C142" s="1" t="inlineStr">
@@ -14871,12 +14871,12 @@
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>FER0144</t>
+          <t>FER0145</t>
         </is>
       </c>
       <c r="B143" s="1" t="inlineStr">
         <is>
-          <t>UB0144</t>
+          <t>UB0145</t>
         </is>
       </c>
       <c r="C143" s="1" t="inlineStr">
@@ -14888,12 +14888,12 @@
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>FER0145</t>
+          <t>FER0146</t>
         </is>
       </c>
       <c r="B144" s="1" t="inlineStr">
         <is>
-          <t>UB0145</t>
+          <t>UB0146</t>
         </is>
       </c>
       <c r="C144" s="1" t="inlineStr">
@@ -14905,12 +14905,12 @@
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>FER0146</t>
+          <t>FER0147</t>
         </is>
       </c>
       <c r="B145" s="1" t="inlineStr">
         <is>
-          <t>UB0146</t>
+          <t>UB0147</t>
         </is>
       </c>
       <c r="C145" s="1" t="inlineStr">
@@ -14922,12 +14922,12 @@
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>FER0147</t>
+          <t>FER0148</t>
         </is>
       </c>
       <c r="B146" s="1" t="inlineStr">
         <is>
-          <t>UB0147</t>
+          <t>UB0148</t>
         </is>
       </c>
       <c r="C146" s="1" t="inlineStr">
@@ -14939,12 +14939,12 @@
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>FER0148</t>
+          <t>FER0149</t>
         </is>
       </c>
       <c r="B147" s="1" t="inlineStr">
         <is>
-          <t>UB0148</t>
+          <t>UB0149</t>
         </is>
       </c>
       <c r="C147" s="1" t="inlineStr">
@@ -14956,12 +14956,12 @@
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>FER0149</t>
+          <t>FER0150</t>
         </is>
       </c>
       <c r="B148" s="1" t="inlineStr">
         <is>
-          <t>UB0149</t>
+          <t>UB0150</t>
         </is>
       </c>
       <c r="C148" s="1" t="inlineStr">
@@ -14973,12 +14973,12 @@
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>FER0150</t>
+          <t>FER0151</t>
         </is>
       </c>
       <c r="B149" s="1" t="inlineStr">
         <is>
-          <t>UB0150</t>
+          <t>UB0151</t>
         </is>
       </c>
       <c r="C149" s="1" t="inlineStr">
@@ -14990,12 +14990,12 @@
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>FER0151</t>
+          <t>FER0152</t>
         </is>
       </c>
       <c r="B150" s="1" t="inlineStr">
         <is>
-          <t>UB0151</t>
+          <t>UB0152</t>
         </is>
       </c>
       <c r="C150" s="1" t="inlineStr">
@@ -15007,12 +15007,12 @@
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>FER0152</t>
+          <t>FER0153</t>
         </is>
       </c>
       <c r="B151" s="1" t="inlineStr">
         <is>
-          <t>UB0152</t>
+          <t>UB0153</t>
         </is>
       </c>
       <c r="C151" s="1" t="inlineStr">
@@ -15024,12 +15024,12 @@
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>FER0153</t>
+          <t>FER0154</t>
         </is>
       </c>
       <c r="B152" s="1" t="inlineStr">
         <is>
-          <t>UB0153</t>
+          <t>UB0154</t>
         </is>
       </c>
       <c r="C152" s="1" t="inlineStr">
@@ -15041,12 +15041,12 @@
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>FER0154</t>
+          <t>FER0155</t>
         </is>
       </c>
       <c r="B153" s="1" t="inlineStr">
         <is>
-          <t>UB0154</t>
+          <t>UB0155</t>
         </is>
       </c>
       <c r="C153" s="1" t="inlineStr">
@@ -15058,12 +15058,12 @@
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>FER0155</t>
+          <t>FER0156</t>
         </is>
       </c>
       <c r="B154" s="1" t="inlineStr">
         <is>
-          <t>UB0155</t>
+          <t>UB0156</t>
         </is>
       </c>
       <c r="C154" s="1" t="inlineStr">
@@ -15075,12 +15075,12 @@
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>FER0156</t>
+          <t>FER0157</t>
         </is>
       </c>
       <c r="B155" s="1" t="inlineStr">
         <is>
-          <t>UB0156</t>
+          <t>UB0157</t>
         </is>
       </c>
       <c r="C155" s="1" t="inlineStr">
@@ -15092,12 +15092,12 @@
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>FER0157</t>
+          <t>FER0158</t>
         </is>
       </c>
       <c r="B156" s="1" t="inlineStr">
         <is>
-          <t>UB0157</t>
+          <t>UB0158</t>
         </is>
       </c>
       <c r="C156" s="1" t="inlineStr">
@@ -15109,12 +15109,12 @@
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>FER0158</t>
+          <t>FER0159</t>
         </is>
       </c>
       <c r="B157" s="1" t="inlineStr">
         <is>
-          <t>UB0158</t>
+          <t>UB0159</t>
         </is>
       </c>
       <c r="C157" s="1" t="inlineStr">
@@ -15126,12 +15126,12 @@
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>FER0159</t>
+          <t>FER0160</t>
         </is>
       </c>
       <c r="B158" s="1" t="inlineStr">
         <is>
-          <t>UB0159</t>
+          <t>UB0160</t>
         </is>
       </c>
       <c r="C158" s="1" t="inlineStr">
@@ -15143,12 +15143,12 @@
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>FER0160</t>
+          <t>FER0161</t>
         </is>
       </c>
       <c r="B159" s="1" t="inlineStr">
         <is>
-          <t>UB0160</t>
+          <t>UB0161</t>
         </is>
       </c>
       <c r="C159" s="1" t="inlineStr">
@@ -15160,12 +15160,12 @@
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>FER0161</t>
+          <t>FER0162</t>
         </is>
       </c>
       <c r="B160" s="1" t="inlineStr">
         <is>
-          <t>UB0161</t>
+          <t>UB0162</t>
         </is>
       </c>
       <c r="C160" s="1" t="inlineStr">
@@ -15177,12 +15177,12 @@
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>FER0162</t>
+          <t>FER0163</t>
         </is>
       </c>
       <c r="B161" s="1" t="inlineStr">
         <is>
-          <t>UB0162</t>
+          <t>UB0163</t>
         </is>
       </c>
       <c r="C161" s="1" t="inlineStr">
@@ -15194,12 +15194,12 @@
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>FER0163</t>
+          <t>FER0164</t>
         </is>
       </c>
       <c r="B162" s="1" t="inlineStr">
         <is>
-          <t>UB0163</t>
+          <t>UB0164</t>
         </is>
       </c>
       <c r="C162" s="1" t="inlineStr">
@@ -15211,12 +15211,12 @@
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>FER0164</t>
+          <t>FER0165</t>
         </is>
       </c>
       <c r="B163" s="1" t="inlineStr">
         <is>
-          <t>UB0164</t>
+          <t>UB0165</t>
         </is>
       </c>
       <c r="C163" s="1" t="inlineStr">
@@ -15228,12 +15228,12 @@
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>FER0165</t>
+          <t>FER0166</t>
         </is>
       </c>
       <c r="B164" s="1" t="inlineStr">
         <is>
-          <t>UB0165</t>
+          <t>UB0166</t>
         </is>
       </c>
       <c r="C164" s="1" t="inlineStr">
@@ -15245,12 +15245,12 @@
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>FER0166</t>
+          <t>FER0167</t>
         </is>
       </c>
       <c r="B165" s="1" t="inlineStr">
         <is>
-          <t>UB0166</t>
+          <t>UB0167</t>
         </is>
       </c>
       <c r="C165" s="1" t="inlineStr">
@@ -15262,12 +15262,12 @@
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>FER0167</t>
+          <t>FER0168</t>
         </is>
       </c>
       <c r="B166" s="1" t="inlineStr">
         <is>
-          <t>UB0167</t>
+          <t>UB0168</t>
         </is>
       </c>
       <c r="C166" s="1" t="inlineStr">
@@ -15279,12 +15279,12 @@
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>FER0168</t>
+          <t>FER0169</t>
         </is>
       </c>
       <c r="B167" s="1" t="inlineStr">
         <is>
-          <t>UB0168</t>
+          <t>UB0169</t>
         </is>
       </c>
       <c r="C167" s="1" t="inlineStr">
@@ -15296,12 +15296,12 @@
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>FER0169</t>
+          <t>FER0170</t>
         </is>
       </c>
       <c r="B168" s="1" t="inlineStr">
         <is>
-          <t>UB0169</t>
+          <t>UB0170</t>
         </is>
       </c>
       <c r="C168" s="1" t="inlineStr">
@@ -15313,12 +15313,12 @@
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>FER0170</t>
+          <t>FER0171</t>
         </is>
       </c>
       <c r="B169" s="1" t="inlineStr">
         <is>
-          <t>UB0170</t>
+          <t>UB0171</t>
         </is>
       </c>
       <c r="C169" s="1" t="inlineStr">
@@ -15330,12 +15330,12 @@
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>FER0171</t>
+          <t>FER0172</t>
         </is>
       </c>
       <c r="B170" s="1" t="inlineStr">
         <is>
-          <t>UB0171</t>
+          <t>UB0172</t>
         </is>
       </c>
       <c r="C170" s="1" t="inlineStr">
@@ -15347,12 +15347,12 @@
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t>FER0172</t>
+          <t>FER0173</t>
         </is>
       </c>
       <c r="B171" s="1" t="inlineStr">
         <is>
-          <t>UB0172</t>
+          <t>UB0173</t>
         </is>
       </c>
       <c r="C171" s="1" t="inlineStr">
@@ -15364,12 +15364,12 @@
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t>FER0173</t>
+          <t>FER0174</t>
         </is>
       </c>
       <c r="B172" s="1" t="inlineStr">
         <is>
-          <t>UB0173</t>
+          <t>UB0174</t>
         </is>
       </c>
       <c r="C172" s="1" t="inlineStr">
@@ -15381,12 +15381,12 @@
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
         <is>
-          <t>FER0174</t>
+          <t>FER0175</t>
         </is>
       </c>
       <c r="B173" s="1" t="inlineStr">
         <is>
-          <t>UB0174</t>
+          <t>UB0175</t>
         </is>
       </c>
       <c r="C173" s="1" t="inlineStr">
@@ -15398,12 +15398,12 @@
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
         <is>
-          <t>FER0175</t>
+          <t>FER0176</t>
         </is>
       </c>
       <c r="B174" s="1" t="inlineStr">
         <is>
-          <t>UB0175</t>
+          <t>UB0176</t>
         </is>
       </c>
       <c r="C174" s="1" t="inlineStr">
@@ -15415,12 +15415,12 @@
     <row r="175">
       <c r="A175" s="1" t="inlineStr">
         <is>
-          <t>FER0176</t>
+          <t>FER0177</t>
         </is>
       </c>
       <c r="B175" s="1" t="inlineStr">
         <is>
-          <t>UB0176</t>
+          <t>UB0177</t>
         </is>
       </c>
       <c r="C175" s="1" t="inlineStr">
@@ -15432,12 +15432,12 @@
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
         <is>
-          <t>FER0177</t>
+          <t>FER0178</t>
         </is>
       </c>
       <c r="B176" s="1" t="inlineStr">
         <is>
-          <t>UB0177</t>
+          <t>UB0178</t>
         </is>
       </c>
       <c r="C176" s="1" t="inlineStr">
@@ -15449,12 +15449,12 @@
     <row r="177">
       <c r="A177" s="1" t="inlineStr">
         <is>
-          <t>FER0178</t>
+          <t>FER0179</t>
         </is>
       </c>
       <c r="B177" s="1" t="inlineStr">
         <is>
-          <t>UB0178</t>
+          <t>UB0179</t>
         </is>
       </c>
       <c r="C177" s="1" t="inlineStr">
@@ -15466,12 +15466,12 @@
     <row r="178">
       <c r="A178" s="1" t="inlineStr">
         <is>
-          <t>FER0179</t>
+          <t>FER0180</t>
         </is>
       </c>
       <c r="B178" s="1" t="inlineStr">
         <is>
-          <t>UB0179</t>
+          <t>UB0180</t>
         </is>
       </c>
       <c r="C178" s="1" t="inlineStr">
@@ -15483,12 +15483,12 @@
     <row r="179">
       <c r="A179" s="1" t="inlineStr">
         <is>
-          <t>FER0180</t>
+          <t>FER0181</t>
         </is>
       </c>
       <c r="B179" s="1" t="inlineStr">
         <is>
-          <t>UB0180</t>
+          <t>UB0181</t>
         </is>
       </c>
       <c r="C179" s="1" t="inlineStr">
@@ -15500,12 +15500,12 @@
     <row r="180">
       <c r="A180" s="1" t="inlineStr">
         <is>
-          <t>FER0181</t>
+          <t>FER0182</t>
         </is>
       </c>
       <c r="B180" s="1" t="inlineStr">
         <is>
-          <t>UB0181</t>
+          <t>UB0182</t>
         </is>
       </c>
       <c r="C180" s="1" t="inlineStr">
@@ -15517,12 +15517,12 @@
     <row r="181">
       <c r="A181" s="1" t="inlineStr">
         <is>
-          <t>FER0182</t>
+          <t>FER0183</t>
         </is>
       </c>
       <c r="B181" s="1" t="inlineStr">
         <is>
-          <t>UB0182</t>
+          <t>UB0183</t>
         </is>
       </c>
       <c r="C181" s="1" t="inlineStr">
@@ -15534,12 +15534,12 @@
     <row r="182">
       <c r="A182" s="1" t="inlineStr">
         <is>
-          <t>FER0183</t>
+          <t>FER0184</t>
         </is>
       </c>
       <c r="B182" s="1" t="inlineStr">
         <is>
-          <t>UB0183</t>
+          <t>UB0184</t>
         </is>
       </c>
       <c r="C182" s="1" t="inlineStr">
@@ -15551,12 +15551,12 @@
     <row r="183">
       <c r="A183" s="1" t="inlineStr">
         <is>
-          <t>FER0184</t>
+          <t>FER0185</t>
         </is>
       </c>
       <c r="B183" s="1" t="inlineStr">
         <is>
-          <t>UB0184</t>
+          <t>UB0185</t>
         </is>
       </c>
       <c r="C183" s="1" t="inlineStr">
@@ -15568,12 +15568,12 @@
     <row r="184">
       <c r="A184" s="1" t="inlineStr">
         <is>
-          <t>FER0185</t>
+          <t>FER0186</t>
         </is>
       </c>
       <c r="B184" s="1" t="inlineStr">
         <is>
-          <t>UB0185</t>
+          <t>UB0186</t>
         </is>
       </c>
       <c r="C184" s="1" t="inlineStr">
@@ -15585,12 +15585,12 @@
     <row r="185">
       <c r="A185" s="1" t="inlineStr">
         <is>
-          <t>FER0186</t>
+          <t>FER0187</t>
         </is>
       </c>
       <c r="B185" s="1" t="inlineStr">
         <is>
-          <t>UB0186</t>
+          <t>UB0187</t>
         </is>
       </c>
       <c r="C185" s="1" t="inlineStr">
@@ -15602,12 +15602,12 @@
     <row r="186">
       <c r="A186" s="1" t="inlineStr">
         <is>
-          <t>FER0187</t>
+          <t>FER0188</t>
         </is>
       </c>
       <c r="B186" s="1" t="inlineStr">
         <is>
-          <t>UB0187</t>
+          <t>UB0188</t>
         </is>
       </c>
       <c r="C186" s="1" t="inlineStr">
@@ -15619,12 +15619,12 @@
     <row r="187">
       <c r="A187" s="1" t="inlineStr">
         <is>
-          <t>FER0188</t>
+          <t>FER0190</t>
         </is>
       </c>
       <c r="B187" s="1" t="inlineStr">
         <is>
-          <t>UB0188</t>
+          <t>UB0190</t>
         </is>
       </c>
       <c r="C187" s="1" t="inlineStr">
@@ -15636,12 +15636,12 @@
     <row r="188">
       <c r="A188" s="1" t="inlineStr">
         <is>
-          <t>FER0190</t>
+          <t>FER0191</t>
         </is>
       </c>
       <c r="B188" s="1" t="inlineStr">
         <is>
-          <t>UB0190</t>
+          <t>UB0191</t>
         </is>
       </c>
       <c r="C188" s="1" t="inlineStr">
@@ -15653,12 +15653,12 @@
     <row r="189">
       <c r="A189" s="1" t="inlineStr">
         <is>
-          <t>FER0191</t>
+          <t>FER0192</t>
         </is>
       </c>
       <c r="B189" s="1" t="inlineStr">
         <is>
-          <t>UB0191</t>
+          <t>UB0192</t>
         </is>
       </c>
       <c r="C189" s="1" t="inlineStr">
@@ -15670,12 +15670,12 @@
     <row r="190">
       <c r="A190" s="1" t="inlineStr">
         <is>
-          <t>FER0192</t>
+          <t>FER0193</t>
         </is>
       </c>
       <c r="B190" s="1" t="inlineStr">
         <is>
-          <t>UB0192</t>
+          <t>UB0193</t>
         </is>
       </c>
       <c r="C190" s="1" t="inlineStr">
@@ -15687,12 +15687,12 @@
     <row r="191">
       <c r="A191" s="1" t="inlineStr">
         <is>
-          <t>FER0193</t>
+          <t>FER0194</t>
         </is>
       </c>
       <c r="B191" s="1" t="inlineStr">
         <is>
-          <t>UB0193</t>
+          <t>UB0194</t>
         </is>
       </c>
       <c r="C191" s="1" t="inlineStr">
@@ -15704,12 +15704,12 @@
     <row r="192">
       <c r="A192" s="1" t="inlineStr">
         <is>
-          <t>FER0194</t>
+          <t>FER0195</t>
         </is>
       </c>
       <c r="B192" s="1" t="inlineStr">
         <is>
-          <t>UB0194</t>
+          <t>UB0195</t>
         </is>
       </c>
       <c r="C192" s="1" t="inlineStr">
@@ -15721,12 +15721,12 @@
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
         <is>
-          <t>FER0195</t>
+          <t>FER0196</t>
         </is>
       </c>
       <c r="B193" s="1" t="inlineStr">
         <is>
-          <t>UB0195</t>
+          <t>UB0196</t>
         </is>
       </c>
       <c r="C193" s="1" t="inlineStr">
@@ -15738,12 +15738,12 @@
     <row r="194">
       <c r="A194" s="1" t="inlineStr">
         <is>
-          <t>FER0196</t>
+          <t>FER0197</t>
         </is>
       </c>
       <c r="B194" s="1" t="inlineStr">
         <is>
-          <t>UB0196</t>
+          <t>UB0197</t>
         </is>
       </c>
       <c r="C194" s="1" t="inlineStr">
@@ -15755,12 +15755,12 @@
     <row r="195">
       <c r="A195" s="1" t="inlineStr">
         <is>
-          <t>FER0197</t>
+          <t>FER0198</t>
         </is>
       </c>
       <c r="B195" s="1" t="inlineStr">
         <is>
-          <t>UB0197</t>
+          <t>UB0198</t>
         </is>
       </c>
       <c r="C195" s="1" t="inlineStr">
@@ -15772,12 +15772,12 @@
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
         <is>
-          <t>FER0198</t>
+          <t>FER0199</t>
         </is>
       </c>
       <c r="B196" s="1" t="inlineStr">
         <is>
-          <t>UB0198</t>
+          <t>UB0199</t>
         </is>
       </c>
       <c r="C196" s="1" t="inlineStr">
@@ -15789,12 +15789,12 @@
     <row r="197">
       <c r="A197" s="1" t="inlineStr">
         <is>
-          <t>FER0199</t>
+          <t>FER0200</t>
         </is>
       </c>
       <c r="B197" s="1" t="inlineStr">
         <is>
-          <t>UB0199</t>
+          <t>UB0200</t>
         </is>
       </c>
       <c r="C197" s="1" t="inlineStr">
@@ -15806,12 +15806,12 @@
     <row r="198">
       <c r="A198" s="1" t="inlineStr">
         <is>
-          <t>FER0200</t>
+          <t>FER0001</t>
         </is>
       </c>
       <c r="B198" s="1" t="inlineStr">
         <is>
-          <t>UB0200</t>
+          <t>UB0001</t>
         </is>
       </c>
       <c r="C198" s="1" t="inlineStr">
@@ -15823,12 +15823,12 @@
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
         <is>
-          <t>FER0001</t>
+          <t>FER0006</t>
         </is>
       </c>
       <c r="B199" s="1" t="inlineStr">
         <is>
-          <t>UB0001</t>
+          <t>UB0006</t>
         </is>
       </c>
       <c r="C199" s="1" t="inlineStr">
@@ -15840,17 +15840,17 @@
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
         <is>
-          <t>FER0006</t>
+          <t>FER0189</t>
         </is>
       </c>
       <c r="B200" s="1" t="inlineStr">
         <is>
-          <t>UB0006</t>
+          <t>UB0189</t>
         </is>
       </c>
       <c r="C200" s="1" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -15862,29 +15862,46 @@
       </c>
       <c r="B201" s="1" t="inlineStr">
         <is>
-          <t>UB0189</t>
+          <t>UB0001</t>
         </is>
       </c>
       <c r="C201" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="inlineStr">
         <is>
-          <t>FER0189</t>
+          <t>FER0029</t>
         </is>
       </c>
       <c r="B202" s="1" t="inlineStr">
         <is>
+          <t>UB0029</t>
+        </is>
+      </c>
+      <c r="C202" s="1" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="inlineStr">
+        <is>
+          <t>FER0029</t>
+        </is>
+      </c>
+      <c r="B203" s="1" t="inlineStr">
+        <is>
           <t>UB0001</t>
         </is>
       </c>
-      <c r="C202" s="1" t="inlineStr">
-        <is>
-          <t>Sí</t>
+      <c r="C203" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -12451,7 +12451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C203"/>
+  <dimension ref="A1:C202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15888,23 +15888,6 @@
         </is>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" s="1" t="inlineStr">
-        <is>
-          <t>FER0029</t>
-        </is>
-      </c>
-      <c r="B203" s="1" t="inlineStr">
-        <is>
-          <t>UB0001</t>
-        </is>
-      </c>
-      <c r="C203" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -1227,7 +1227,7 @@
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -1227,7 +1227,7 @@
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -1573,7 +1573,7 @@
       </c>
       <c r="D43" s="1" t="inlineStr">
         <is>
-          <t>Clavos comunes 2 pulg. Artículo de ferretería para trabajos y proyectos relacionados con tornillería y fijaciones.</t>
+          <t>Clavos comunes 2 pulg. Artículo de ferretería para trabajos y proyectos relacionados con tornillería y fijaciones. Esta en tres areas</t>
         </is>
       </c>
       <c r="E43" s="1" t="inlineStr">
@@ -12451,7 +12451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C202"/>
+  <dimension ref="A1:C204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13120,12 +13120,12 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>FER0042</t>
+          <t>FER0043</t>
         </is>
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>UB0042</t>
+          <t>UB0043</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr">
@@ -13137,12 +13137,12 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>FER0043</t>
+          <t>FER0044</t>
         </is>
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>UB0043</t>
+          <t>UB0044</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
@@ -13154,12 +13154,12 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>FER0044</t>
+          <t>FER0045</t>
         </is>
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>UB0044</t>
+          <t>UB0045</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
@@ -13171,12 +13171,12 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>FER0045</t>
+          <t>FER0046</t>
         </is>
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>UB0045</t>
+          <t>UB0046</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
@@ -13188,12 +13188,12 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>FER0046</t>
+          <t>FER0047</t>
         </is>
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>UB0046</t>
+          <t>UB0047</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
@@ -13205,12 +13205,12 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>FER0047</t>
+          <t>FER0048</t>
         </is>
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>UB0047</t>
+          <t>UB0048</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
@@ -13222,12 +13222,12 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>FER0048</t>
+          <t>FER0049</t>
         </is>
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>UB0048</t>
+          <t>UB0049</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
@@ -13239,12 +13239,12 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>FER0049</t>
+          <t>FER0050</t>
         </is>
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>UB0049</t>
+          <t>UB0050</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr">
@@ -13256,12 +13256,12 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>FER0050</t>
+          <t>FER0051</t>
         </is>
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>UB0050</t>
+          <t>UB0051</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr">
@@ -13273,12 +13273,12 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>FER0051</t>
+          <t>FER0052</t>
         </is>
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>UB0051</t>
+          <t>UB0052</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr">
@@ -13290,12 +13290,12 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>FER0052</t>
+          <t>FER0053</t>
         </is>
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>UB0052</t>
+          <t>UB0053</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
@@ -13307,12 +13307,12 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>FER0053</t>
+          <t>FER0054</t>
         </is>
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>UB0053</t>
+          <t>UB0054</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
@@ -13324,12 +13324,12 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>FER0054</t>
+          <t>FER0055</t>
         </is>
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>UB0054</t>
+          <t>UB0055</t>
         </is>
       </c>
       <c r="C52" s="1" t="inlineStr">
@@ -13341,12 +13341,12 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>FER0055</t>
+          <t>FER0056</t>
         </is>
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>UB0055</t>
+          <t>UB0056</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
@@ -13358,12 +13358,12 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>FER0056</t>
+          <t>FER0057</t>
         </is>
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>UB0056</t>
+          <t>UB0057</t>
         </is>
       </c>
       <c r="C54" s="1" t="inlineStr">
@@ -13375,12 +13375,12 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>FER0057</t>
+          <t>FER0058</t>
         </is>
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>UB0057</t>
+          <t>UB0058</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr">
@@ -13392,12 +13392,12 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>FER0058</t>
+          <t>FER0059</t>
         </is>
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>UB0058</t>
+          <t>UB0059</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr">
@@ -13409,12 +13409,12 @@
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>FER0059</t>
+          <t>FER0060</t>
         </is>
       </c>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>UB0059</t>
+          <t>UB0060</t>
         </is>
       </c>
       <c r="C57" s="1" t="inlineStr">
@@ -13426,12 +13426,12 @@
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>FER0060</t>
+          <t>FER0061</t>
         </is>
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>UB0060</t>
+          <t>UB0061</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
@@ -13443,12 +13443,12 @@
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>FER0061</t>
+          <t>FER0062</t>
         </is>
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>UB0061</t>
+          <t>UB0062</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
@@ -13460,12 +13460,12 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>FER0062</t>
+          <t>FER0063</t>
         </is>
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>UB0062</t>
+          <t>UB0063</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
@@ -13477,12 +13477,12 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>FER0063</t>
+          <t>FER0064</t>
         </is>
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>UB0063</t>
+          <t>UB0064</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
@@ -13494,12 +13494,12 @@
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>FER0064</t>
+          <t>FER0065</t>
         </is>
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>UB0064</t>
+          <t>UB0065</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
@@ -13511,12 +13511,12 @@
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>FER0065</t>
+          <t>FER0066</t>
         </is>
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>UB0065</t>
+          <t>UB0066</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
@@ -13528,12 +13528,12 @@
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>FER0066</t>
+          <t>FER0067</t>
         </is>
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>UB0066</t>
+          <t>UB0067</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
@@ -13545,12 +13545,12 @@
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>FER0067</t>
+          <t>FER0068</t>
         </is>
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>UB0067</t>
+          <t>UB0068</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
@@ -13562,12 +13562,12 @@
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>FER0068</t>
+          <t>FER0069</t>
         </is>
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>UB0068</t>
+          <t>UB0069</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
@@ -13579,12 +13579,12 @@
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>FER0069</t>
+          <t>FER0070</t>
         </is>
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>UB0069</t>
+          <t>UB0070</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
@@ -13596,12 +13596,12 @@
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>FER0070</t>
+          <t>FER0071</t>
         </is>
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>UB0070</t>
+          <t>UB0071</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
@@ -13613,12 +13613,12 @@
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>FER0071</t>
+          <t>FER0072</t>
         </is>
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>UB0071</t>
+          <t>UB0072</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
@@ -13630,12 +13630,12 @@
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>FER0072</t>
+          <t>FER0073</t>
         </is>
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>UB0072</t>
+          <t>UB0073</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr">
@@ -13647,12 +13647,12 @@
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>FER0073</t>
+          <t>FER0074</t>
         </is>
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>UB0073</t>
+          <t>UB0074</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
@@ -13664,12 +13664,12 @@
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>FER0074</t>
+          <t>FER0075</t>
         </is>
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>UB0074</t>
+          <t>UB0075</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
@@ -13681,12 +13681,12 @@
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>FER0075</t>
+          <t>FER0076</t>
         </is>
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>UB0075</t>
+          <t>UB0076</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr">
@@ -13698,12 +13698,12 @@
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>FER0076</t>
+          <t>FER0077</t>
         </is>
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>UB0076</t>
+          <t>UB0077</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
@@ -13715,12 +13715,12 @@
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>FER0077</t>
+          <t>FER0078</t>
         </is>
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>UB0077</t>
+          <t>UB0078</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr">
@@ -13732,12 +13732,12 @@
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>FER0078</t>
+          <t>FER0079</t>
         </is>
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>UB0078</t>
+          <t>UB0079</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
@@ -13749,12 +13749,12 @@
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>FER0079</t>
+          <t>FER0080</t>
         </is>
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>UB0079</t>
+          <t>UB0080</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
@@ -13766,12 +13766,12 @@
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>FER0080</t>
+          <t>FER0081</t>
         </is>
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>UB0080</t>
+          <t>UB0081</t>
         </is>
       </c>
       <c r="C78" s="1" t="inlineStr">
@@ -13783,12 +13783,12 @@
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>FER0081</t>
+          <t>FER0082</t>
         </is>
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>UB0081</t>
+          <t>UB0082</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
@@ -13800,12 +13800,12 @@
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>FER0082</t>
+          <t>FER0083</t>
         </is>
       </c>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>UB0082</t>
+          <t>UB0083</t>
         </is>
       </c>
       <c r="C80" s="1" t="inlineStr">
@@ -13817,12 +13817,12 @@
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>FER0083</t>
+          <t>FER0084</t>
         </is>
       </c>
       <c r="B81" s="1" t="inlineStr">
         <is>
-          <t>UB0083</t>
+          <t>UB0084</t>
         </is>
       </c>
       <c r="C81" s="1" t="inlineStr">
@@ -13834,12 +13834,12 @@
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>FER0084</t>
+          <t>FER0085</t>
         </is>
       </c>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>UB0084</t>
+          <t>UB0085</t>
         </is>
       </c>
       <c r="C82" s="1" t="inlineStr">
@@ -13851,12 +13851,12 @@
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>FER0085</t>
+          <t>FER0086</t>
         </is>
       </c>
       <c r="B83" s="1" t="inlineStr">
         <is>
-          <t>UB0085</t>
+          <t>UB0086</t>
         </is>
       </c>
       <c r="C83" s="1" t="inlineStr">
@@ -13868,12 +13868,12 @@
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>FER0086</t>
+          <t>FER0087</t>
         </is>
       </c>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>UB0086</t>
+          <t>UB0087</t>
         </is>
       </c>
       <c r="C84" s="1" t="inlineStr">
@@ -13885,12 +13885,12 @@
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>FER0087</t>
+          <t>FER0088</t>
         </is>
       </c>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>UB0087</t>
+          <t>UB0088</t>
         </is>
       </c>
       <c r="C85" s="1" t="inlineStr">
@@ -13902,12 +13902,12 @@
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>FER0088</t>
+          <t>FER0089</t>
         </is>
       </c>
       <c r="B86" s="1" t="inlineStr">
         <is>
-          <t>UB0088</t>
+          <t>UB0089</t>
         </is>
       </c>
       <c r="C86" s="1" t="inlineStr">
@@ -13919,12 +13919,12 @@
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>FER0089</t>
+          <t>FER0090</t>
         </is>
       </c>
       <c r="B87" s="1" t="inlineStr">
         <is>
-          <t>UB0089</t>
+          <t>UB0090</t>
         </is>
       </c>
       <c r="C87" s="1" t="inlineStr">
@@ -13936,12 +13936,12 @@
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>FER0090</t>
+          <t>FER0091</t>
         </is>
       </c>
       <c r="B88" s="1" t="inlineStr">
         <is>
-          <t>UB0090</t>
+          <t>UB0091</t>
         </is>
       </c>
       <c r="C88" s="1" t="inlineStr">
@@ -13953,12 +13953,12 @@
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>FER0091</t>
+          <t>FER0092</t>
         </is>
       </c>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>UB0091</t>
+          <t>UB0092</t>
         </is>
       </c>
       <c r="C89" s="1" t="inlineStr">
@@ -13970,12 +13970,12 @@
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>FER0092</t>
+          <t>FER0093</t>
         </is>
       </c>
       <c r="B90" s="1" t="inlineStr">
         <is>
-          <t>UB0092</t>
+          <t>UB0093</t>
         </is>
       </c>
       <c r="C90" s="1" t="inlineStr">
@@ -13987,12 +13987,12 @@
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>FER0093</t>
+          <t>FER0094</t>
         </is>
       </c>
       <c r="B91" s="1" t="inlineStr">
         <is>
-          <t>UB0093</t>
+          <t>UB0094</t>
         </is>
       </c>
       <c r="C91" s="1" t="inlineStr">
@@ -14004,12 +14004,12 @@
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>FER0094</t>
+          <t>FER0095</t>
         </is>
       </c>
       <c r="B92" s="1" t="inlineStr">
         <is>
-          <t>UB0094</t>
+          <t>UB0095</t>
         </is>
       </c>
       <c r="C92" s="1" t="inlineStr">
@@ -14021,12 +14021,12 @@
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>FER0095</t>
+          <t>FER0096</t>
         </is>
       </c>
       <c r="B93" s="1" t="inlineStr">
         <is>
-          <t>UB0095</t>
+          <t>UB0096</t>
         </is>
       </c>
       <c r="C93" s="1" t="inlineStr">
@@ -14038,12 +14038,12 @@
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>FER0096</t>
+          <t>FER0097</t>
         </is>
       </c>
       <c r="B94" s="1" t="inlineStr">
         <is>
-          <t>UB0096</t>
+          <t>UB0097</t>
         </is>
       </c>
       <c r="C94" s="1" t="inlineStr">
@@ -14055,12 +14055,12 @@
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>FER0097</t>
+          <t>FER0098</t>
         </is>
       </c>
       <c r="B95" s="1" t="inlineStr">
         <is>
-          <t>UB0097</t>
+          <t>UB0098</t>
         </is>
       </c>
       <c r="C95" s="1" t="inlineStr">
@@ -14072,12 +14072,12 @@
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>FER0098</t>
+          <t>FER0099</t>
         </is>
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>UB0098</t>
+          <t>UB0099</t>
         </is>
       </c>
       <c r="C96" s="1" t="inlineStr">
@@ -14089,12 +14089,12 @@
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>FER0099</t>
+          <t>FER0100</t>
         </is>
       </c>
       <c r="B97" s="1" t="inlineStr">
         <is>
-          <t>UB0099</t>
+          <t>UB0100</t>
         </is>
       </c>
       <c r="C97" s="1" t="inlineStr">
@@ -14106,12 +14106,12 @@
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>FER0100</t>
+          <t>FER0101</t>
         </is>
       </c>
       <c r="B98" s="1" t="inlineStr">
         <is>
-          <t>UB0100</t>
+          <t>UB0101</t>
         </is>
       </c>
       <c r="C98" s="1" t="inlineStr">
@@ -14123,12 +14123,12 @@
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>FER0101</t>
+          <t>FER0102</t>
         </is>
       </c>
       <c r="B99" s="1" t="inlineStr">
         <is>
-          <t>UB0101</t>
+          <t>UB0102</t>
         </is>
       </c>
       <c r="C99" s="1" t="inlineStr">
@@ -14140,12 +14140,12 @@
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>FER0102</t>
+          <t>FER0103</t>
         </is>
       </c>
       <c r="B100" s="1" t="inlineStr">
         <is>
-          <t>UB0102</t>
+          <t>UB0103</t>
         </is>
       </c>
       <c r="C100" s="1" t="inlineStr">
@@ -14157,12 +14157,12 @@
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>FER0103</t>
+          <t>FER0104</t>
         </is>
       </c>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t>UB0103</t>
+          <t>UB0104</t>
         </is>
       </c>
       <c r="C101" s="1" t="inlineStr">
@@ -14174,12 +14174,12 @@
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>FER0104</t>
+          <t>FER0105</t>
         </is>
       </c>
       <c r="B102" s="1" t="inlineStr">
         <is>
-          <t>UB0104</t>
+          <t>UB0105</t>
         </is>
       </c>
       <c r="C102" s="1" t="inlineStr">
@@ -14191,12 +14191,12 @@
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>FER0105</t>
+          <t>FER0106</t>
         </is>
       </c>
       <c r="B103" s="1" t="inlineStr">
         <is>
-          <t>UB0105</t>
+          <t>UB0106</t>
         </is>
       </c>
       <c r="C103" s="1" t="inlineStr">
@@ -14208,12 +14208,12 @@
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>FER0106</t>
+          <t>FER0107</t>
         </is>
       </c>
       <c r="B104" s="1" t="inlineStr">
         <is>
-          <t>UB0106</t>
+          <t>UB0107</t>
         </is>
       </c>
       <c r="C104" s="1" t="inlineStr">
@@ -14225,12 +14225,12 @@
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>FER0107</t>
+          <t>FER0108</t>
         </is>
       </c>
       <c r="B105" s="1" t="inlineStr">
         <is>
-          <t>UB0107</t>
+          <t>UB0108</t>
         </is>
       </c>
       <c r="C105" s="1" t="inlineStr">
@@ -14242,12 +14242,12 @@
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>FER0108</t>
+          <t>FER0109</t>
         </is>
       </c>
       <c r="B106" s="1" t="inlineStr">
         <is>
-          <t>UB0108</t>
+          <t>UB0109</t>
         </is>
       </c>
       <c r="C106" s="1" t="inlineStr">
@@ -14259,12 +14259,12 @@
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>FER0109</t>
+          <t>FER0110</t>
         </is>
       </c>
       <c r="B107" s="1" t="inlineStr">
         <is>
-          <t>UB0109</t>
+          <t>UB0110</t>
         </is>
       </c>
       <c r="C107" s="1" t="inlineStr">
@@ -14276,12 +14276,12 @@
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>FER0110</t>
+          <t>FER0111</t>
         </is>
       </c>
       <c r="B108" s="1" t="inlineStr">
         <is>
-          <t>UB0110</t>
+          <t>UB0111</t>
         </is>
       </c>
       <c r="C108" s="1" t="inlineStr">
@@ -14293,12 +14293,12 @@
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>FER0111</t>
+          <t>FER0112</t>
         </is>
       </c>
       <c r="B109" s="1" t="inlineStr">
         <is>
-          <t>UB0111</t>
+          <t>UB0112</t>
         </is>
       </c>
       <c r="C109" s="1" t="inlineStr">
@@ -14310,12 +14310,12 @@
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>FER0112</t>
+          <t>FER0113</t>
         </is>
       </c>
       <c r="B110" s="1" t="inlineStr">
         <is>
-          <t>UB0112</t>
+          <t>UB0113</t>
         </is>
       </c>
       <c r="C110" s="1" t="inlineStr">
@@ -14327,12 +14327,12 @@
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>FER0113</t>
+          <t>FER0114</t>
         </is>
       </c>
       <c r="B111" s="1" t="inlineStr">
         <is>
-          <t>UB0113</t>
+          <t>UB0114</t>
         </is>
       </c>
       <c r="C111" s="1" t="inlineStr">
@@ -14344,12 +14344,12 @@
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>FER0114</t>
+          <t>FER0115</t>
         </is>
       </c>
       <c r="B112" s="1" t="inlineStr">
         <is>
-          <t>UB0114</t>
+          <t>UB0115</t>
         </is>
       </c>
       <c r="C112" s="1" t="inlineStr">
@@ -14361,12 +14361,12 @@
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>FER0115</t>
+          <t>FER0116</t>
         </is>
       </c>
       <c r="B113" s="1" t="inlineStr">
         <is>
-          <t>UB0115</t>
+          <t>UB0116</t>
         </is>
       </c>
       <c r="C113" s="1" t="inlineStr">
@@ -14378,12 +14378,12 @@
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>FER0116</t>
+          <t>FER0117</t>
         </is>
       </c>
       <c r="B114" s="1" t="inlineStr">
         <is>
-          <t>UB0116</t>
+          <t>UB0117</t>
         </is>
       </c>
       <c r="C114" s="1" t="inlineStr">
@@ -14395,12 +14395,12 @@
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>FER0117</t>
+          <t>FER0118</t>
         </is>
       </c>
       <c r="B115" s="1" t="inlineStr">
         <is>
-          <t>UB0117</t>
+          <t>UB0118</t>
         </is>
       </c>
       <c r="C115" s="1" t="inlineStr">
@@ -14412,12 +14412,12 @@
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>FER0118</t>
+          <t>FER0119</t>
         </is>
       </c>
       <c r="B116" s="1" t="inlineStr">
         <is>
-          <t>UB0118</t>
+          <t>UB0119</t>
         </is>
       </c>
       <c r="C116" s="1" t="inlineStr">
@@ -14429,12 +14429,12 @@
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>FER0119</t>
+          <t>FER0120</t>
         </is>
       </c>
       <c r="B117" s="1" t="inlineStr">
         <is>
-          <t>UB0119</t>
+          <t>UB0120</t>
         </is>
       </c>
       <c r="C117" s="1" t="inlineStr">
@@ -14446,12 +14446,12 @@
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>FER0120</t>
+          <t>FER0121</t>
         </is>
       </c>
       <c r="B118" s="1" t="inlineStr">
         <is>
-          <t>UB0120</t>
+          <t>UB0121</t>
         </is>
       </c>
       <c r="C118" s="1" t="inlineStr">
@@ -14463,12 +14463,12 @@
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>FER0121</t>
+          <t>FER0122</t>
         </is>
       </c>
       <c r="B119" s="1" t="inlineStr">
         <is>
-          <t>UB0121</t>
+          <t>UB0122</t>
         </is>
       </c>
       <c r="C119" s="1" t="inlineStr">
@@ -14480,12 +14480,12 @@
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>FER0122</t>
+          <t>FER0123</t>
         </is>
       </c>
       <c r="B120" s="1" t="inlineStr">
         <is>
-          <t>UB0122</t>
+          <t>UB0123</t>
         </is>
       </c>
       <c r="C120" s="1" t="inlineStr">
@@ -14497,12 +14497,12 @@
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>FER0123</t>
+          <t>FER0124</t>
         </is>
       </c>
       <c r="B121" s="1" t="inlineStr">
         <is>
-          <t>UB0123</t>
+          <t>UB0124</t>
         </is>
       </c>
       <c r="C121" s="1" t="inlineStr">
@@ -14514,12 +14514,12 @@
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>FER0124</t>
+          <t>FER0125</t>
         </is>
       </c>
       <c r="B122" s="1" t="inlineStr">
         <is>
-          <t>UB0124</t>
+          <t>UB0125</t>
         </is>
       </c>
       <c r="C122" s="1" t="inlineStr">
@@ -14531,12 +14531,12 @@
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>FER0125</t>
+          <t>FER0126</t>
         </is>
       </c>
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t>UB0125</t>
+          <t>UB0126</t>
         </is>
       </c>
       <c r="C123" s="1" t="inlineStr">
@@ -14548,12 +14548,12 @@
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>FER0126</t>
+          <t>FER0127</t>
         </is>
       </c>
       <c r="B124" s="1" t="inlineStr">
         <is>
-          <t>UB0126</t>
+          <t>UB0127</t>
         </is>
       </c>
       <c r="C124" s="1" t="inlineStr">
@@ -14565,12 +14565,12 @@
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>FER0127</t>
+          <t>FER0128</t>
         </is>
       </c>
       <c r="B125" s="1" t="inlineStr">
         <is>
-          <t>UB0127</t>
+          <t>UB0128</t>
         </is>
       </c>
       <c r="C125" s="1" t="inlineStr">
@@ -14582,12 +14582,12 @@
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>FER0128</t>
+          <t>FER0129</t>
         </is>
       </c>
       <c r="B126" s="1" t="inlineStr">
         <is>
-          <t>UB0128</t>
+          <t>UB0129</t>
         </is>
       </c>
       <c r="C126" s="1" t="inlineStr">
@@ -14599,12 +14599,12 @@
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>FER0129</t>
+          <t>FER0130</t>
         </is>
       </c>
       <c r="B127" s="1" t="inlineStr">
         <is>
-          <t>UB0129</t>
+          <t>UB0130</t>
         </is>
       </c>
       <c r="C127" s="1" t="inlineStr">
@@ -14616,12 +14616,12 @@
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>FER0130</t>
+          <t>FER0131</t>
         </is>
       </c>
       <c r="B128" s="1" t="inlineStr">
         <is>
-          <t>UB0130</t>
+          <t>UB0131</t>
         </is>
       </c>
       <c r="C128" s="1" t="inlineStr">
@@ -14633,12 +14633,12 @@
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>FER0131</t>
+          <t>FER0132</t>
         </is>
       </c>
       <c r="B129" s="1" t="inlineStr">
         <is>
-          <t>UB0131</t>
+          <t>UB0132</t>
         </is>
       </c>
       <c r="C129" s="1" t="inlineStr">
@@ -14650,12 +14650,12 @@
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>FER0132</t>
+          <t>FER0133</t>
         </is>
       </c>
       <c r="B130" s="1" t="inlineStr">
         <is>
-          <t>UB0132</t>
+          <t>UB0133</t>
         </is>
       </c>
       <c r="C130" s="1" t="inlineStr">
@@ -14667,12 +14667,12 @@
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>FER0133</t>
+          <t>FER0134</t>
         </is>
       </c>
       <c r="B131" s="1" t="inlineStr">
         <is>
-          <t>UB0133</t>
+          <t>UB0134</t>
         </is>
       </c>
       <c r="C131" s="1" t="inlineStr">
@@ -14684,12 +14684,12 @@
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>FER0134</t>
+          <t>FER0135</t>
         </is>
       </c>
       <c r="B132" s="1" t="inlineStr">
         <is>
-          <t>UB0134</t>
+          <t>UB0135</t>
         </is>
       </c>
       <c r="C132" s="1" t="inlineStr">
@@ -14701,12 +14701,12 @@
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>FER0135</t>
+          <t>FER0136</t>
         </is>
       </c>
       <c r="B133" s="1" t="inlineStr">
         <is>
-          <t>UB0135</t>
+          <t>UB0136</t>
         </is>
       </c>
       <c r="C133" s="1" t="inlineStr">
@@ -14718,12 +14718,12 @@
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>FER0136</t>
+          <t>FER0137</t>
         </is>
       </c>
       <c r="B134" s="1" t="inlineStr">
         <is>
-          <t>UB0136</t>
+          <t>UB0137</t>
         </is>
       </c>
       <c r="C134" s="1" t="inlineStr">
@@ -14735,12 +14735,12 @@
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>FER0137</t>
+          <t>FER0138</t>
         </is>
       </c>
       <c r="B135" s="1" t="inlineStr">
         <is>
-          <t>UB0137</t>
+          <t>UB0138</t>
         </is>
       </c>
       <c r="C135" s="1" t="inlineStr">
@@ -14752,12 +14752,12 @@
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>FER0138</t>
+          <t>FER0139</t>
         </is>
       </c>
       <c r="B136" s="1" t="inlineStr">
         <is>
-          <t>UB0138</t>
+          <t>UB0139</t>
         </is>
       </c>
       <c r="C136" s="1" t="inlineStr">
@@ -14769,12 +14769,12 @@
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>FER0139</t>
+          <t>FER0140</t>
         </is>
       </c>
       <c r="B137" s="1" t="inlineStr">
         <is>
-          <t>UB0139</t>
+          <t>UB0140</t>
         </is>
       </c>
       <c r="C137" s="1" t="inlineStr">
@@ -14786,12 +14786,12 @@
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>FER0140</t>
+          <t>FER0141</t>
         </is>
       </c>
       <c r="B138" s="1" t="inlineStr">
         <is>
-          <t>UB0140</t>
+          <t>UB0141</t>
         </is>
       </c>
       <c r="C138" s="1" t="inlineStr">
@@ -14803,12 +14803,12 @@
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>FER0141</t>
+          <t>FER0142</t>
         </is>
       </c>
       <c r="B139" s="1" t="inlineStr">
         <is>
-          <t>UB0141</t>
+          <t>UB0142</t>
         </is>
       </c>
       <c r="C139" s="1" t="inlineStr">
@@ -14820,12 +14820,12 @@
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>FER0142</t>
+          <t>FER0143</t>
         </is>
       </c>
       <c r="B140" s="1" t="inlineStr">
         <is>
-          <t>UB0142</t>
+          <t>UB0143</t>
         </is>
       </c>
       <c r="C140" s="1" t="inlineStr">
@@ -14837,12 +14837,12 @@
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>FER0143</t>
+          <t>FER0144</t>
         </is>
       </c>
       <c r="B141" s="1" t="inlineStr">
         <is>
-          <t>UB0143</t>
+          <t>UB0144</t>
         </is>
       </c>
       <c r="C141" s="1" t="inlineStr">
@@ -14854,12 +14854,12 @@
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>FER0144</t>
+          <t>FER0145</t>
         </is>
       </c>
       <c r="B142" s="1" t="inlineStr">
         <is>
-          <t>UB0144</t>
+          <t>UB0145</t>
         </is>
       </c>
       <c r="C142" s="1" t="inlineStr">
@@ -14871,12 +14871,12 @@
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>FER0145</t>
+          <t>FER0146</t>
         </is>
       </c>
       <c r="B143" s="1" t="inlineStr">
         <is>
-          <t>UB0145</t>
+          <t>UB0146</t>
         </is>
       </c>
       <c r="C143" s="1" t="inlineStr">
@@ -14888,12 +14888,12 @@
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>FER0146</t>
+          <t>FER0147</t>
         </is>
       </c>
       <c r="B144" s="1" t="inlineStr">
         <is>
-          <t>UB0146</t>
+          <t>UB0147</t>
         </is>
       </c>
       <c r="C144" s="1" t="inlineStr">
@@ -14905,12 +14905,12 @@
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>FER0147</t>
+          <t>FER0148</t>
         </is>
       </c>
       <c r="B145" s="1" t="inlineStr">
         <is>
-          <t>UB0147</t>
+          <t>UB0148</t>
         </is>
       </c>
       <c r="C145" s="1" t="inlineStr">
@@ -14922,12 +14922,12 @@
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>FER0148</t>
+          <t>FER0149</t>
         </is>
       </c>
       <c r="B146" s="1" t="inlineStr">
         <is>
-          <t>UB0148</t>
+          <t>UB0149</t>
         </is>
       </c>
       <c r="C146" s="1" t="inlineStr">
@@ -14939,12 +14939,12 @@
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>FER0149</t>
+          <t>FER0150</t>
         </is>
       </c>
       <c r="B147" s="1" t="inlineStr">
         <is>
-          <t>UB0149</t>
+          <t>UB0150</t>
         </is>
       </c>
       <c r="C147" s="1" t="inlineStr">
@@ -14956,12 +14956,12 @@
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>FER0150</t>
+          <t>FER0151</t>
         </is>
       </c>
       <c r="B148" s="1" t="inlineStr">
         <is>
-          <t>UB0150</t>
+          <t>UB0151</t>
         </is>
       </c>
       <c r="C148" s="1" t="inlineStr">
@@ -14973,12 +14973,12 @@
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>FER0151</t>
+          <t>FER0152</t>
         </is>
       </c>
       <c r="B149" s="1" t="inlineStr">
         <is>
-          <t>UB0151</t>
+          <t>UB0152</t>
         </is>
       </c>
       <c r="C149" s="1" t="inlineStr">
@@ -14990,12 +14990,12 @@
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>FER0152</t>
+          <t>FER0153</t>
         </is>
       </c>
       <c r="B150" s="1" t="inlineStr">
         <is>
-          <t>UB0152</t>
+          <t>UB0153</t>
         </is>
       </c>
       <c r="C150" s="1" t="inlineStr">
@@ -15007,12 +15007,12 @@
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>FER0153</t>
+          <t>FER0154</t>
         </is>
       </c>
       <c r="B151" s="1" t="inlineStr">
         <is>
-          <t>UB0153</t>
+          <t>UB0154</t>
         </is>
       </c>
       <c r="C151" s="1" t="inlineStr">
@@ -15024,12 +15024,12 @@
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>FER0154</t>
+          <t>FER0155</t>
         </is>
       </c>
       <c r="B152" s="1" t="inlineStr">
         <is>
-          <t>UB0154</t>
+          <t>UB0155</t>
         </is>
       </c>
       <c r="C152" s="1" t="inlineStr">
@@ -15041,12 +15041,12 @@
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>FER0155</t>
+          <t>FER0156</t>
         </is>
       </c>
       <c r="B153" s="1" t="inlineStr">
         <is>
-          <t>UB0155</t>
+          <t>UB0156</t>
         </is>
       </c>
       <c r="C153" s="1" t="inlineStr">
@@ -15058,12 +15058,12 @@
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>FER0156</t>
+          <t>FER0157</t>
         </is>
       </c>
       <c r="B154" s="1" t="inlineStr">
         <is>
-          <t>UB0156</t>
+          <t>UB0157</t>
         </is>
       </c>
       <c r="C154" s="1" t="inlineStr">
@@ -15075,12 +15075,12 @@
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>FER0157</t>
+          <t>FER0158</t>
         </is>
       </c>
       <c r="B155" s="1" t="inlineStr">
         <is>
-          <t>UB0157</t>
+          <t>UB0158</t>
         </is>
       </c>
       <c r="C155" s="1" t="inlineStr">
@@ -15092,12 +15092,12 @@
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>FER0158</t>
+          <t>FER0159</t>
         </is>
       </c>
       <c r="B156" s="1" t="inlineStr">
         <is>
-          <t>UB0158</t>
+          <t>UB0159</t>
         </is>
       </c>
       <c r="C156" s="1" t="inlineStr">
@@ -15109,12 +15109,12 @@
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>FER0159</t>
+          <t>FER0160</t>
         </is>
       </c>
       <c r="B157" s="1" t="inlineStr">
         <is>
-          <t>UB0159</t>
+          <t>UB0160</t>
         </is>
       </c>
       <c r="C157" s="1" t="inlineStr">
@@ -15126,12 +15126,12 @@
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>FER0160</t>
+          <t>FER0161</t>
         </is>
       </c>
       <c r="B158" s="1" t="inlineStr">
         <is>
-          <t>UB0160</t>
+          <t>UB0161</t>
         </is>
       </c>
       <c r="C158" s="1" t="inlineStr">
@@ -15143,12 +15143,12 @@
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>FER0161</t>
+          <t>FER0162</t>
         </is>
       </c>
       <c r="B159" s="1" t="inlineStr">
         <is>
-          <t>UB0161</t>
+          <t>UB0162</t>
         </is>
       </c>
       <c r="C159" s="1" t="inlineStr">
@@ -15160,12 +15160,12 @@
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>FER0162</t>
+          <t>FER0163</t>
         </is>
       </c>
       <c r="B160" s="1" t="inlineStr">
         <is>
-          <t>UB0162</t>
+          <t>UB0163</t>
         </is>
       </c>
       <c r="C160" s="1" t="inlineStr">
@@ -15177,12 +15177,12 @@
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>FER0163</t>
+          <t>FER0164</t>
         </is>
       </c>
       <c r="B161" s="1" t="inlineStr">
         <is>
-          <t>UB0163</t>
+          <t>UB0164</t>
         </is>
       </c>
       <c r="C161" s="1" t="inlineStr">
@@ -15194,12 +15194,12 @@
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>FER0164</t>
+          <t>FER0165</t>
         </is>
       </c>
       <c r="B162" s="1" t="inlineStr">
         <is>
-          <t>UB0164</t>
+          <t>UB0165</t>
         </is>
       </c>
       <c r="C162" s="1" t="inlineStr">
@@ -15211,12 +15211,12 @@
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>FER0165</t>
+          <t>FER0166</t>
         </is>
       </c>
       <c r="B163" s="1" t="inlineStr">
         <is>
-          <t>UB0165</t>
+          <t>UB0166</t>
         </is>
       </c>
       <c r="C163" s="1" t="inlineStr">
@@ -15228,12 +15228,12 @@
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>FER0166</t>
+          <t>FER0167</t>
         </is>
       </c>
       <c r="B164" s="1" t="inlineStr">
         <is>
-          <t>UB0166</t>
+          <t>UB0167</t>
         </is>
       </c>
       <c r="C164" s="1" t="inlineStr">
@@ -15245,12 +15245,12 @@
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>FER0167</t>
+          <t>FER0168</t>
         </is>
       </c>
       <c r="B165" s="1" t="inlineStr">
         <is>
-          <t>UB0167</t>
+          <t>UB0168</t>
         </is>
       </c>
       <c r="C165" s="1" t="inlineStr">
@@ -15262,12 +15262,12 @@
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>FER0168</t>
+          <t>FER0169</t>
         </is>
       </c>
       <c r="B166" s="1" t="inlineStr">
         <is>
-          <t>UB0168</t>
+          <t>UB0169</t>
         </is>
       </c>
       <c r="C166" s="1" t="inlineStr">
@@ -15279,12 +15279,12 @@
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>FER0169</t>
+          <t>FER0170</t>
         </is>
       </c>
       <c r="B167" s="1" t="inlineStr">
         <is>
-          <t>UB0169</t>
+          <t>UB0170</t>
         </is>
       </c>
       <c r="C167" s="1" t="inlineStr">
@@ -15296,12 +15296,12 @@
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>FER0170</t>
+          <t>FER0171</t>
         </is>
       </c>
       <c r="B168" s="1" t="inlineStr">
         <is>
-          <t>UB0170</t>
+          <t>UB0171</t>
         </is>
       </c>
       <c r="C168" s="1" t="inlineStr">
@@ -15313,12 +15313,12 @@
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>FER0171</t>
+          <t>FER0172</t>
         </is>
       </c>
       <c r="B169" s="1" t="inlineStr">
         <is>
-          <t>UB0171</t>
+          <t>UB0172</t>
         </is>
       </c>
       <c r="C169" s="1" t="inlineStr">
@@ -15330,12 +15330,12 @@
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>FER0172</t>
+          <t>FER0173</t>
         </is>
       </c>
       <c r="B170" s="1" t="inlineStr">
         <is>
-          <t>UB0172</t>
+          <t>UB0173</t>
         </is>
       </c>
       <c r="C170" s="1" t="inlineStr">
@@ -15347,12 +15347,12 @@
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t>FER0173</t>
+          <t>FER0174</t>
         </is>
       </c>
       <c r="B171" s="1" t="inlineStr">
         <is>
-          <t>UB0173</t>
+          <t>UB0174</t>
         </is>
       </c>
       <c r="C171" s="1" t="inlineStr">
@@ -15364,12 +15364,12 @@
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t>FER0174</t>
+          <t>FER0175</t>
         </is>
       </c>
       <c r="B172" s="1" t="inlineStr">
         <is>
-          <t>UB0174</t>
+          <t>UB0175</t>
         </is>
       </c>
       <c r="C172" s="1" t="inlineStr">
@@ -15381,12 +15381,12 @@
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
         <is>
-          <t>FER0175</t>
+          <t>FER0176</t>
         </is>
       </c>
       <c r="B173" s="1" t="inlineStr">
         <is>
-          <t>UB0175</t>
+          <t>UB0176</t>
         </is>
       </c>
       <c r="C173" s="1" t="inlineStr">
@@ -15398,12 +15398,12 @@
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
         <is>
-          <t>FER0176</t>
+          <t>FER0177</t>
         </is>
       </c>
       <c r="B174" s="1" t="inlineStr">
         <is>
-          <t>UB0176</t>
+          <t>UB0177</t>
         </is>
       </c>
       <c r="C174" s="1" t="inlineStr">
@@ -15415,12 +15415,12 @@
     <row r="175">
       <c r="A175" s="1" t="inlineStr">
         <is>
-          <t>FER0177</t>
+          <t>FER0178</t>
         </is>
       </c>
       <c r="B175" s="1" t="inlineStr">
         <is>
-          <t>UB0177</t>
+          <t>UB0178</t>
         </is>
       </c>
       <c r="C175" s="1" t="inlineStr">
@@ -15432,12 +15432,12 @@
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
         <is>
-          <t>FER0178</t>
+          <t>FER0179</t>
         </is>
       </c>
       <c r="B176" s="1" t="inlineStr">
         <is>
-          <t>UB0178</t>
+          <t>UB0179</t>
         </is>
       </c>
       <c r="C176" s="1" t="inlineStr">
@@ -15449,12 +15449,12 @@
     <row r="177">
       <c r="A177" s="1" t="inlineStr">
         <is>
-          <t>FER0179</t>
+          <t>FER0180</t>
         </is>
       </c>
       <c r="B177" s="1" t="inlineStr">
         <is>
-          <t>UB0179</t>
+          <t>UB0180</t>
         </is>
       </c>
       <c r="C177" s="1" t="inlineStr">
@@ -15466,12 +15466,12 @@
     <row r="178">
       <c r="A178" s="1" t="inlineStr">
         <is>
-          <t>FER0180</t>
+          <t>FER0181</t>
         </is>
       </c>
       <c r="B178" s="1" t="inlineStr">
         <is>
-          <t>UB0180</t>
+          <t>UB0181</t>
         </is>
       </c>
       <c r="C178" s="1" t="inlineStr">
@@ -15483,12 +15483,12 @@
     <row r="179">
       <c r="A179" s="1" t="inlineStr">
         <is>
-          <t>FER0181</t>
+          <t>FER0182</t>
         </is>
       </c>
       <c r="B179" s="1" t="inlineStr">
         <is>
-          <t>UB0181</t>
+          <t>UB0182</t>
         </is>
       </c>
       <c r="C179" s="1" t="inlineStr">
@@ -15500,12 +15500,12 @@
     <row r="180">
       <c r="A180" s="1" t="inlineStr">
         <is>
-          <t>FER0182</t>
+          <t>FER0183</t>
         </is>
       </c>
       <c r="B180" s="1" t="inlineStr">
         <is>
-          <t>UB0182</t>
+          <t>UB0183</t>
         </is>
       </c>
       <c r="C180" s="1" t="inlineStr">
@@ -15517,12 +15517,12 @@
     <row r="181">
       <c r="A181" s="1" t="inlineStr">
         <is>
-          <t>FER0183</t>
+          <t>FER0184</t>
         </is>
       </c>
       <c r="B181" s="1" t="inlineStr">
         <is>
-          <t>UB0183</t>
+          <t>UB0184</t>
         </is>
       </c>
       <c r="C181" s="1" t="inlineStr">
@@ -15534,12 +15534,12 @@
     <row r="182">
       <c r="A182" s="1" t="inlineStr">
         <is>
-          <t>FER0184</t>
+          <t>FER0185</t>
         </is>
       </c>
       <c r="B182" s="1" t="inlineStr">
         <is>
-          <t>UB0184</t>
+          <t>UB0185</t>
         </is>
       </c>
       <c r="C182" s="1" t="inlineStr">
@@ -15551,12 +15551,12 @@
     <row r="183">
       <c r="A183" s="1" t="inlineStr">
         <is>
-          <t>FER0185</t>
+          <t>FER0186</t>
         </is>
       </c>
       <c r="B183" s="1" t="inlineStr">
         <is>
-          <t>UB0185</t>
+          <t>UB0186</t>
         </is>
       </c>
       <c r="C183" s="1" t="inlineStr">
@@ -15568,12 +15568,12 @@
     <row r="184">
       <c r="A184" s="1" t="inlineStr">
         <is>
-          <t>FER0186</t>
+          <t>FER0187</t>
         </is>
       </c>
       <c r="B184" s="1" t="inlineStr">
         <is>
-          <t>UB0186</t>
+          <t>UB0187</t>
         </is>
       </c>
       <c r="C184" s="1" t="inlineStr">
@@ -15585,12 +15585,12 @@
     <row r="185">
       <c r="A185" s="1" t="inlineStr">
         <is>
-          <t>FER0187</t>
+          <t>FER0188</t>
         </is>
       </c>
       <c r="B185" s="1" t="inlineStr">
         <is>
-          <t>UB0187</t>
+          <t>UB0188</t>
         </is>
       </c>
       <c r="C185" s="1" t="inlineStr">
@@ -15602,12 +15602,12 @@
     <row r="186">
       <c r="A186" s="1" t="inlineStr">
         <is>
-          <t>FER0188</t>
+          <t>FER0190</t>
         </is>
       </c>
       <c r="B186" s="1" t="inlineStr">
         <is>
-          <t>UB0188</t>
+          <t>UB0190</t>
         </is>
       </c>
       <c r="C186" s="1" t="inlineStr">
@@ -15619,12 +15619,12 @@
     <row r="187">
       <c r="A187" s="1" t="inlineStr">
         <is>
-          <t>FER0190</t>
+          <t>FER0191</t>
         </is>
       </c>
       <c r="B187" s="1" t="inlineStr">
         <is>
-          <t>UB0190</t>
+          <t>UB0191</t>
         </is>
       </c>
       <c r="C187" s="1" t="inlineStr">
@@ -15636,12 +15636,12 @@
     <row r="188">
       <c r="A188" s="1" t="inlineStr">
         <is>
-          <t>FER0191</t>
+          <t>FER0192</t>
         </is>
       </c>
       <c r="B188" s="1" t="inlineStr">
         <is>
-          <t>UB0191</t>
+          <t>UB0192</t>
         </is>
       </c>
       <c r="C188" s="1" t="inlineStr">
@@ -15653,12 +15653,12 @@
     <row r="189">
       <c r="A189" s="1" t="inlineStr">
         <is>
-          <t>FER0192</t>
+          <t>FER0193</t>
         </is>
       </c>
       <c r="B189" s="1" t="inlineStr">
         <is>
-          <t>UB0192</t>
+          <t>UB0193</t>
         </is>
       </c>
       <c r="C189" s="1" t="inlineStr">
@@ -15670,12 +15670,12 @@
     <row r="190">
       <c r="A190" s="1" t="inlineStr">
         <is>
-          <t>FER0193</t>
+          <t>FER0194</t>
         </is>
       </c>
       <c r="B190" s="1" t="inlineStr">
         <is>
-          <t>UB0193</t>
+          <t>UB0194</t>
         </is>
       </c>
       <c r="C190" s="1" t="inlineStr">
@@ -15687,12 +15687,12 @@
     <row r="191">
       <c r="A191" s="1" t="inlineStr">
         <is>
-          <t>FER0194</t>
+          <t>FER0195</t>
         </is>
       </c>
       <c r="B191" s="1" t="inlineStr">
         <is>
-          <t>UB0194</t>
+          <t>UB0195</t>
         </is>
       </c>
       <c r="C191" s="1" t="inlineStr">
@@ -15704,12 +15704,12 @@
     <row r="192">
       <c r="A192" s="1" t="inlineStr">
         <is>
-          <t>FER0195</t>
+          <t>FER0196</t>
         </is>
       </c>
       <c r="B192" s="1" t="inlineStr">
         <is>
-          <t>UB0195</t>
+          <t>UB0196</t>
         </is>
       </c>
       <c r="C192" s="1" t="inlineStr">
@@ -15721,12 +15721,12 @@
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
         <is>
-          <t>FER0196</t>
+          <t>FER0197</t>
         </is>
       </c>
       <c r="B193" s="1" t="inlineStr">
         <is>
-          <t>UB0196</t>
+          <t>UB0197</t>
         </is>
       </c>
       <c r="C193" s="1" t="inlineStr">
@@ -15738,12 +15738,12 @@
     <row r="194">
       <c r="A194" s="1" t="inlineStr">
         <is>
-          <t>FER0197</t>
+          <t>FER0198</t>
         </is>
       </c>
       <c r="B194" s="1" t="inlineStr">
         <is>
-          <t>UB0197</t>
+          <t>UB0198</t>
         </is>
       </c>
       <c r="C194" s="1" t="inlineStr">
@@ -15755,12 +15755,12 @@
     <row r="195">
       <c r="A195" s="1" t="inlineStr">
         <is>
-          <t>FER0198</t>
+          <t>FER0199</t>
         </is>
       </c>
       <c r="B195" s="1" t="inlineStr">
         <is>
-          <t>UB0198</t>
+          <t>UB0199</t>
         </is>
       </c>
       <c r="C195" s="1" t="inlineStr">
@@ -15772,12 +15772,12 @@
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
         <is>
-          <t>FER0199</t>
+          <t>FER0200</t>
         </is>
       </c>
       <c r="B196" s="1" t="inlineStr">
         <is>
-          <t>UB0199</t>
+          <t>UB0200</t>
         </is>
       </c>
       <c r="C196" s="1" t="inlineStr">
@@ -15789,12 +15789,12 @@
     <row r="197">
       <c r="A197" s="1" t="inlineStr">
         <is>
-          <t>FER0200</t>
+          <t>FER0001</t>
         </is>
       </c>
       <c r="B197" s="1" t="inlineStr">
         <is>
-          <t>UB0200</t>
+          <t>UB0001</t>
         </is>
       </c>
       <c r="C197" s="1" t="inlineStr">
@@ -15806,12 +15806,12 @@
     <row r="198">
       <c r="A198" s="1" t="inlineStr">
         <is>
-          <t>FER0001</t>
+          <t>FER0006</t>
         </is>
       </c>
       <c r="B198" s="1" t="inlineStr">
         <is>
-          <t>UB0001</t>
+          <t>UB0006</t>
         </is>
       </c>
       <c r="C198" s="1" t="inlineStr">
@@ -15823,17 +15823,17 @@
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
         <is>
-          <t>FER0006</t>
+          <t>FER0189</t>
         </is>
       </c>
       <c r="B199" s="1" t="inlineStr">
         <is>
-          <t>UB0006</t>
+          <t>UB0189</t>
         </is>
       </c>
       <c r="C199" s="1" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -15845,24 +15845,24 @@
       </c>
       <c r="B200" s="1" t="inlineStr">
         <is>
-          <t>UB0189</t>
+          <t>UB0001</t>
         </is>
       </c>
       <c r="C200" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="inlineStr">
         <is>
-          <t>FER0189</t>
+          <t>FER0029</t>
         </is>
       </c>
       <c r="B201" s="1" t="inlineStr">
         <is>
-          <t>UB0001</t>
+          <t>UB0029</t>
         </is>
       </c>
       <c r="C201" s="1" t="inlineStr">
@@ -15874,17 +15874,51 @@
     <row r="202">
       <c r="A202" s="1" t="inlineStr">
         <is>
-          <t>FER0029</t>
+          <t>FER0042</t>
         </is>
       </c>
       <c r="B202" s="1" t="inlineStr">
         <is>
-          <t>UB0029</t>
+          <t>UB0042</t>
         </is>
       </c>
       <c r="C202" s="1" t="inlineStr">
         <is>
           <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="inlineStr">
+        <is>
+          <t>FER0042</t>
+        </is>
+      </c>
+      <c r="B203" s="1" t="inlineStr">
+        <is>
+          <t>UB0005</t>
+        </is>
+      </c>
+      <c r="C203" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="inlineStr">
+        <is>
+          <t>FER0042</t>
+        </is>
+      </c>
+      <c r="B204" s="1" t="inlineStr">
+        <is>
+          <t>UB0007</t>
+        </is>
+      </c>
+      <c r="C204" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -15913,7 +15913,7 @@
       </c>
       <c r="B204" s="1" t="inlineStr">
         <is>
-          <t>UB0007</t>
+          <t>UB0015</t>
         </is>
       </c>
       <c r="C204" s="1" t="inlineStr">

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -1578,7 +1578,7 @@
       </c>
       <c r="E43" s="1" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -1578,7 +1578,7 @@
       </c>
       <c r="E43" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -465,7 +465,7 @@
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>Martillo de uña 16 oz. Artículo de ferretería para trabajos y proyectos relacionados con herramientas.</t>
+          <t>Martillo de uña 16 oz. Artículo de ferretería para trabajos y proyectos relacionados con herramientas 1 y 2.</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
@@ -15789,12 +15789,12 @@
     <row r="197">
       <c r="A197" s="1" t="inlineStr">
         <is>
-          <t>FER0001</t>
+          <t>FER0006</t>
         </is>
       </c>
       <c r="B197" s="1" t="inlineStr">
         <is>
-          <t>UB0001</t>
+          <t>UB0006</t>
         </is>
       </c>
       <c r="C197" s="1" t="inlineStr">
@@ -15806,17 +15806,17 @@
     <row r="198">
       <c r="A198" s="1" t="inlineStr">
         <is>
-          <t>FER0006</t>
+          <t>FER0189</t>
         </is>
       </c>
       <c r="B198" s="1" t="inlineStr">
         <is>
-          <t>UB0006</t>
+          <t>UB0189</t>
         </is>
       </c>
       <c r="C198" s="1" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -15828,24 +15828,24 @@
       </c>
       <c r="B199" s="1" t="inlineStr">
         <is>
-          <t>UB0189</t>
+          <t>UB0001</t>
         </is>
       </c>
       <c r="C199" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
         <is>
-          <t>FER0189</t>
+          <t>FER0029</t>
         </is>
       </c>
       <c r="B200" s="1" t="inlineStr">
         <is>
-          <t>UB0001</t>
+          <t>UB0029</t>
         </is>
       </c>
       <c r="C200" s="1" t="inlineStr">
@@ -15857,12 +15857,12 @@
     <row r="201">
       <c r="A201" s="1" t="inlineStr">
         <is>
-          <t>FER0029</t>
+          <t>FER0042</t>
         </is>
       </c>
       <c r="B201" s="1" t="inlineStr">
         <is>
-          <t>UB0029</t>
+          <t>UB0042</t>
         </is>
       </c>
       <c r="C201" s="1" t="inlineStr">
@@ -15879,12 +15879,12 @@
       </c>
       <c r="B202" s="1" t="inlineStr">
         <is>
-          <t>UB0042</t>
+          <t>UB0005</t>
         </is>
       </c>
       <c r="C202" s="1" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -15896,7 +15896,7 @@
       </c>
       <c r="B203" s="1" t="inlineStr">
         <is>
-          <t>UB0005</t>
+          <t>UB0015</t>
         </is>
       </c>
       <c r="C203" s="1" t="inlineStr">
@@ -15908,17 +15908,17 @@
     <row r="204">
       <c r="A204" s="1" t="inlineStr">
         <is>
-          <t>FER0042</t>
+          <t>FER0001</t>
         </is>
       </c>
       <c r="B204" s="1" t="inlineStr">
         <is>
-          <t>UB0015</t>
+          <t>UB0001</t>
         </is>
       </c>
       <c r="C204" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -465,7 +465,7 @@
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>Martillo de uña 16 oz. Artículo de ferretería para trabajos y proyectos relacionados con herramientas 1 y 2.</t>
+          <t>Martillo de uña 16 oz. Artículo de ferretería para trabajos y proyectos relacionados con herramientas.</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -465,7 +465,7 @@
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>Martillo de uña 16 oz. Artículo de ferretería para trabajos y proyectos relacionados con herramientas.</t>
+          <t>Martillo de uña 16 oz. Artículo de ferretería para trabajos y proyectos relacionados con herramientas 12.</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D42" s="1" t="inlineStr">
         <is>
-          <t>Clavos de acabado 1 1/2 pulg. Artículo de ferretería para trabajos y proyectos relacionados con tornillería y fijaciones.</t>
+          <t>Clavos de acabado 1 1/2 pulg. Artículo de ferretería para trabajos y proyectos relacionados con tornillería y fijaciones 33.</t>
         </is>
       </c>
       <c r="E42" s="1" t="inlineStr">
@@ -13103,12 +13103,12 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>FER0041</t>
+          <t>FER0043</t>
         </is>
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>UB0041</t>
+          <t>UB0043</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr">
@@ -13120,12 +13120,12 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>FER0043</t>
+          <t>FER0044</t>
         </is>
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>UB0043</t>
+          <t>UB0044</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr">
@@ -13137,12 +13137,12 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>FER0044</t>
+          <t>FER0045</t>
         </is>
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>UB0044</t>
+          <t>UB0045</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
@@ -13154,12 +13154,12 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>FER0045</t>
+          <t>FER0046</t>
         </is>
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>UB0045</t>
+          <t>UB0046</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
@@ -13171,12 +13171,12 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>FER0046</t>
+          <t>FER0047</t>
         </is>
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>UB0046</t>
+          <t>UB0047</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
@@ -13188,12 +13188,12 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>FER0047</t>
+          <t>FER0048</t>
         </is>
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>UB0047</t>
+          <t>UB0048</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
@@ -13205,12 +13205,12 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>FER0048</t>
+          <t>FER0049</t>
         </is>
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>UB0048</t>
+          <t>UB0049</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
@@ -13222,12 +13222,12 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>FER0049</t>
+          <t>FER0050</t>
         </is>
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>UB0049</t>
+          <t>UB0050</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
@@ -13239,12 +13239,12 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>FER0050</t>
+          <t>FER0051</t>
         </is>
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>UB0050</t>
+          <t>UB0051</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr">
@@ -13256,12 +13256,12 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>FER0051</t>
+          <t>FER0052</t>
         </is>
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>UB0051</t>
+          <t>UB0052</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr">
@@ -13273,12 +13273,12 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>FER0052</t>
+          <t>FER0053</t>
         </is>
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>UB0052</t>
+          <t>UB0053</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr">
@@ -13290,12 +13290,12 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>FER0053</t>
+          <t>FER0054</t>
         </is>
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>UB0053</t>
+          <t>UB0054</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
@@ -13307,12 +13307,12 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>FER0054</t>
+          <t>FER0055</t>
         </is>
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>UB0054</t>
+          <t>UB0055</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
@@ -13324,12 +13324,12 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>FER0055</t>
+          <t>FER0056</t>
         </is>
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>UB0055</t>
+          <t>UB0056</t>
         </is>
       </c>
       <c r="C52" s="1" t="inlineStr">
@@ -13341,12 +13341,12 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>FER0056</t>
+          <t>FER0057</t>
         </is>
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>UB0056</t>
+          <t>UB0057</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
@@ -13358,12 +13358,12 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>FER0057</t>
+          <t>FER0058</t>
         </is>
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>UB0057</t>
+          <t>UB0058</t>
         </is>
       </c>
       <c r="C54" s="1" t="inlineStr">
@@ -13375,12 +13375,12 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>FER0058</t>
+          <t>FER0059</t>
         </is>
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>UB0058</t>
+          <t>UB0059</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr">
@@ -13392,12 +13392,12 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>FER0059</t>
+          <t>FER0060</t>
         </is>
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>UB0059</t>
+          <t>UB0060</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr">
@@ -13409,12 +13409,12 @@
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>FER0060</t>
+          <t>FER0061</t>
         </is>
       </c>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>UB0060</t>
+          <t>UB0061</t>
         </is>
       </c>
       <c r="C57" s="1" t="inlineStr">
@@ -13426,12 +13426,12 @@
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>FER0061</t>
+          <t>FER0062</t>
         </is>
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>UB0061</t>
+          <t>UB0062</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
@@ -13443,12 +13443,12 @@
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>FER0062</t>
+          <t>FER0063</t>
         </is>
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>UB0062</t>
+          <t>UB0063</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
@@ -13460,12 +13460,12 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>FER0063</t>
+          <t>FER0064</t>
         </is>
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>UB0063</t>
+          <t>UB0064</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
@@ -13477,12 +13477,12 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>FER0064</t>
+          <t>FER0065</t>
         </is>
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>UB0064</t>
+          <t>UB0065</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
@@ -13494,12 +13494,12 @@
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>FER0065</t>
+          <t>FER0066</t>
         </is>
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>UB0065</t>
+          <t>UB0066</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
@@ -13511,12 +13511,12 @@
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>FER0066</t>
+          <t>FER0067</t>
         </is>
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>UB0066</t>
+          <t>UB0067</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
@@ -13528,12 +13528,12 @@
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>FER0067</t>
+          <t>FER0068</t>
         </is>
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>UB0067</t>
+          <t>UB0068</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
@@ -13545,12 +13545,12 @@
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>FER0068</t>
+          <t>FER0069</t>
         </is>
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>UB0068</t>
+          <t>UB0069</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
@@ -13562,12 +13562,12 @@
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>FER0069</t>
+          <t>FER0070</t>
         </is>
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>UB0069</t>
+          <t>UB0070</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
@@ -13579,12 +13579,12 @@
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>FER0070</t>
+          <t>FER0071</t>
         </is>
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>UB0070</t>
+          <t>UB0071</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
@@ -13596,12 +13596,12 @@
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>FER0071</t>
+          <t>FER0072</t>
         </is>
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>UB0071</t>
+          <t>UB0072</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
@@ -13613,12 +13613,12 @@
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>FER0072</t>
+          <t>FER0073</t>
         </is>
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>UB0072</t>
+          <t>UB0073</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
@@ -13630,12 +13630,12 @@
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>FER0073</t>
+          <t>FER0074</t>
         </is>
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>UB0073</t>
+          <t>UB0074</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr">
@@ -13647,12 +13647,12 @@
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>FER0074</t>
+          <t>FER0075</t>
         </is>
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>UB0074</t>
+          <t>UB0075</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
@@ -13664,12 +13664,12 @@
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>FER0075</t>
+          <t>FER0076</t>
         </is>
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>UB0075</t>
+          <t>UB0076</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
@@ -13681,12 +13681,12 @@
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>FER0076</t>
+          <t>FER0077</t>
         </is>
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>UB0076</t>
+          <t>UB0077</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr">
@@ -13698,12 +13698,12 @@
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>FER0077</t>
+          <t>FER0078</t>
         </is>
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>UB0077</t>
+          <t>UB0078</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
@@ -13715,12 +13715,12 @@
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>FER0078</t>
+          <t>FER0079</t>
         </is>
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>UB0078</t>
+          <t>UB0079</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr">
@@ -13732,12 +13732,12 @@
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>FER0079</t>
+          <t>FER0080</t>
         </is>
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>UB0079</t>
+          <t>UB0080</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
@@ -13749,12 +13749,12 @@
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>FER0080</t>
+          <t>FER0081</t>
         </is>
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>UB0080</t>
+          <t>UB0081</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
@@ -13766,12 +13766,12 @@
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>FER0081</t>
+          <t>FER0082</t>
         </is>
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>UB0081</t>
+          <t>UB0082</t>
         </is>
       </c>
       <c r="C78" s="1" t="inlineStr">
@@ -13783,12 +13783,12 @@
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>FER0082</t>
+          <t>FER0083</t>
         </is>
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>UB0082</t>
+          <t>UB0083</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
@@ -13800,12 +13800,12 @@
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>FER0083</t>
+          <t>FER0084</t>
         </is>
       </c>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>UB0083</t>
+          <t>UB0084</t>
         </is>
       </c>
       <c r="C80" s="1" t="inlineStr">
@@ -13817,12 +13817,12 @@
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>FER0084</t>
+          <t>FER0085</t>
         </is>
       </c>
       <c r="B81" s="1" t="inlineStr">
         <is>
-          <t>UB0084</t>
+          <t>UB0085</t>
         </is>
       </c>
       <c r="C81" s="1" t="inlineStr">
@@ -13834,12 +13834,12 @@
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>FER0085</t>
+          <t>FER0086</t>
         </is>
       </c>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>UB0085</t>
+          <t>UB0086</t>
         </is>
       </c>
       <c r="C82" s="1" t="inlineStr">
@@ -13851,12 +13851,12 @@
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>FER0086</t>
+          <t>FER0087</t>
         </is>
       </c>
       <c r="B83" s="1" t="inlineStr">
         <is>
-          <t>UB0086</t>
+          <t>UB0087</t>
         </is>
       </c>
       <c r="C83" s="1" t="inlineStr">
@@ -13868,12 +13868,12 @@
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>FER0087</t>
+          <t>FER0088</t>
         </is>
       </c>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>UB0087</t>
+          <t>UB0088</t>
         </is>
       </c>
       <c r="C84" s="1" t="inlineStr">
@@ -13885,12 +13885,12 @@
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>FER0088</t>
+          <t>FER0089</t>
         </is>
       </c>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>UB0088</t>
+          <t>UB0089</t>
         </is>
       </c>
       <c r="C85" s="1" t="inlineStr">
@@ -13902,12 +13902,12 @@
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>FER0089</t>
+          <t>FER0090</t>
         </is>
       </c>
       <c r="B86" s="1" t="inlineStr">
         <is>
-          <t>UB0089</t>
+          <t>UB0090</t>
         </is>
       </c>
       <c r="C86" s="1" t="inlineStr">
@@ -13919,12 +13919,12 @@
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>FER0090</t>
+          <t>FER0091</t>
         </is>
       </c>
       <c r="B87" s="1" t="inlineStr">
         <is>
-          <t>UB0090</t>
+          <t>UB0091</t>
         </is>
       </c>
       <c r="C87" s="1" t="inlineStr">
@@ -13936,12 +13936,12 @@
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>FER0091</t>
+          <t>FER0092</t>
         </is>
       </c>
       <c r="B88" s="1" t="inlineStr">
         <is>
-          <t>UB0091</t>
+          <t>UB0092</t>
         </is>
       </c>
       <c r="C88" s="1" t="inlineStr">
@@ -13953,12 +13953,12 @@
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>FER0092</t>
+          <t>FER0093</t>
         </is>
       </c>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>UB0092</t>
+          <t>UB0093</t>
         </is>
       </c>
       <c r="C89" s="1" t="inlineStr">
@@ -13970,12 +13970,12 @@
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>FER0093</t>
+          <t>FER0094</t>
         </is>
       </c>
       <c r="B90" s="1" t="inlineStr">
         <is>
-          <t>UB0093</t>
+          <t>UB0094</t>
         </is>
       </c>
       <c r="C90" s="1" t="inlineStr">
@@ -13987,12 +13987,12 @@
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>FER0094</t>
+          <t>FER0095</t>
         </is>
       </c>
       <c r="B91" s="1" t="inlineStr">
         <is>
-          <t>UB0094</t>
+          <t>UB0095</t>
         </is>
       </c>
       <c r="C91" s="1" t="inlineStr">
@@ -14004,12 +14004,12 @@
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>FER0095</t>
+          <t>FER0096</t>
         </is>
       </c>
       <c r="B92" s="1" t="inlineStr">
         <is>
-          <t>UB0095</t>
+          <t>UB0096</t>
         </is>
       </c>
       <c r="C92" s="1" t="inlineStr">
@@ -14021,12 +14021,12 @@
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>FER0096</t>
+          <t>FER0097</t>
         </is>
       </c>
       <c r="B93" s="1" t="inlineStr">
         <is>
-          <t>UB0096</t>
+          <t>UB0097</t>
         </is>
       </c>
       <c r="C93" s="1" t="inlineStr">
@@ -14038,12 +14038,12 @@
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>FER0097</t>
+          <t>FER0098</t>
         </is>
       </c>
       <c r="B94" s="1" t="inlineStr">
         <is>
-          <t>UB0097</t>
+          <t>UB0098</t>
         </is>
       </c>
       <c r="C94" s="1" t="inlineStr">
@@ -14055,12 +14055,12 @@
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>FER0098</t>
+          <t>FER0099</t>
         </is>
       </c>
       <c r="B95" s="1" t="inlineStr">
         <is>
-          <t>UB0098</t>
+          <t>UB0099</t>
         </is>
       </c>
       <c r="C95" s="1" t="inlineStr">
@@ -14072,12 +14072,12 @@
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>FER0099</t>
+          <t>FER0100</t>
         </is>
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>UB0099</t>
+          <t>UB0100</t>
         </is>
       </c>
       <c r="C96" s="1" t="inlineStr">
@@ -14089,12 +14089,12 @@
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>FER0100</t>
+          <t>FER0101</t>
         </is>
       </c>
       <c r="B97" s="1" t="inlineStr">
         <is>
-          <t>UB0100</t>
+          <t>UB0101</t>
         </is>
       </c>
       <c r="C97" s="1" t="inlineStr">
@@ -14106,12 +14106,12 @@
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>FER0101</t>
+          <t>FER0102</t>
         </is>
       </c>
       <c r="B98" s="1" t="inlineStr">
         <is>
-          <t>UB0101</t>
+          <t>UB0102</t>
         </is>
       </c>
       <c r="C98" s="1" t="inlineStr">
@@ -14123,12 +14123,12 @@
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>FER0102</t>
+          <t>FER0103</t>
         </is>
       </c>
       <c r="B99" s="1" t="inlineStr">
         <is>
-          <t>UB0102</t>
+          <t>UB0103</t>
         </is>
       </c>
       <c r="C99" s="1" t="inlineStr">
@@ -14140,12 +14140,12 @@
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>FER0103</t>
+          <t>FER0104</t>
         </is>
       </c>
       <c r="B100" s="1" t="inlineStr">
         <is>
-          <t>UB0103</t>
+          <t>UB0104</t>
         </is>
       </c>
       <c r="C100" s="1" t="inlineStr">
@@ -14157,12 +14157,12 @@
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>FER0104</t>
+          <t>FER0105</t>
         </is>
       </c>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t>UB0104</t>
+          <t>UB0105</t>
         </is>
       </c>
       <c r="C101" s="1" t="inlineStr">
@@ -14174,12 +14174,12 @@
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>FER0105</t>
+          <t>FER0106</t>
         </is>
       </c>
       <c r="B102" s="1" t="inlineStr">
         <is>
-          <t>UB0105</t>
+          <t>UB0106</t>
         </is>
       </c>
       <c r="C102" s="1" t="inlineStr">
@@ -14191,12 +14191,12 @@
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>FER0106</t>
+          <t>FER0107</t>
         </is>
       </c>
       <c r="B103" s="1" t="inlineStr">
         <is>
-          <t>UB0106</t>
+          <t>UB0107</t>
         </is>
       </c>
       <c r="C103" s="1" t="inlineStr">
@@ -14208,12 +14208,12 @@
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>FER0107</t>
+          <t>FER0108</t>
         </is>
       </c>
       <c r="B104" s="1" t="inlineStr">
         <is>
-          <t>UB0107</t>
+          <t>UB0108</t>
         </is>
       </c>
       <c r="C104" s="1" t="inlineStr">
@@ -14225,12 +14225,12 @@
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>FER0108</t>
+          <t>FER0109</t>
         </is>
       </c>
       <c r="B105" s="1" t="inlineStr">
         <is>
-          <t>UB0108</t>
+          <t>UB0109</t>
         </is>
       </c>
       <c r="C105" s="1" t="inlineStr">
@@ -14242,12 +14242,12 @@
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>FER0109</t>
+          <t>FER0110</t>
         </is>
       </c>
       <c r="B106" s="1" t="inlineStr">
         <is>
-          <t>UB0109</t>
+          <t>UB0110</t>
         </is>
       </c>
       <c r="C106" s="1" t="inlineStr">
@@ -14259,12 +14259,12 @@
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>FER0110</t>
+          <t>FER0111</t>
         </is>
       </c>
       <c r="B107" s="1" t="inlineStr">
         <is>
-          <t>UB0110</t>
+          <t>UB0111</t>
         </is>
       </c>
       <c r="C107" s="1" t="inlineStr">
@@ -14276,12 +14276,12 @@
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>FER0111</t>
+          <t>FER0112</t>
         </is>
       </c>
       <c r="B108" s="1" t="inlineStr">
         <is>
-          <t>UB0111</t>
+          <t>UB0112</t>
         </is>
       </c>
       <c r="C108" s="1" t="inlineStr">
@@ -14293,12 +14293,12 @@
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>FER0112</t>
+          <t>FER0113</t>
         </is>
       </c>
       <c r="B109" s="1" t="inlineStr">
         <is>
-          <t>UB0112</t>
+          <t>UB0113</t>
         </is>
       </c>
       <c r="C109" s="1" t="inlineStr">
@@ -14310,12 +14310,12 @@
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>FER0113</t>
+          <t>FER0114</t>
         </is>
       </c>
       <c r="B110" s="1" t="inlineStr">
         <is>
-          <t>UB0113</t>
+          <t>UB0114</t>
         </is>
       </c>
       <c r="C110" s="1" t="inlineStr">
@@ -14327,12 +14327,12 @@
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>FER0114</t>
+          <t>FER0115</t>
         </is>
       </c>
       <c r="B111" s="1" t="inlineStr">
         <is>
-          <t>UB0114</t>
+          <t>UB0115</t>
         </is>
       </c>
       <c r="C111" s="1" t="inlineStr">
@@ -14344,12 +14344,12 @@
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>FER0115</t>
+          <t>FER0116</t>
         </is>
       </c>
       <c r="B112" s="1" t="inlineStr">
         <is>
-          <t>UB0115</t>
+          <t>UB0116</t>
         </is>
       </c>
       <c r="C112" s="1" t="inlineStr">
@@ -14361,12 +14361,12 @@
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>FER0116</t>
+          <t>FER0117</t>
         </is>
       </c>
       <c r="B113" s="1" t="inlineStr">
         <is>
-          <t>UB0116</t>
+          <t>UB0117</t>
         </is>
       </c>
       <c r="C113" s="1" t="inlineStr">
@@ -14378,12 +14378,12 @@
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>FER0117</t>
+          <t>FER0118</t>
         </is>
       </c>
       <c r="B114" s="1" t="inlineStr">
         <is>
-          <t>UB0117</t>
+          <t>UB0118</t>
         </is>
       </c>
       <c r="C114" s="1" t="inlineStr">
@@ -14395,12 +14395,12 @@
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>FER0118</t>
+          <t>FER0119</t>
         </is>
       </c>
       <c r="B115" s="1" t="inlineStr">
         <is>
-          <t>UB0118</t>
+          <t>UB0119</t>
         </is>
       </c>
       <c r="C115" s="1" t="inlineStr">
@@ -14412,12 +14412,12 @@
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>FER0119</t>
+          <t>FER0120</t>
         </is>
       </c>
       <c r="B116" s="1" t="inlineStr">
         <is>
-          <t>UB0119</t>
+          <t>UB0120</t>
         </is>
       </c>
       <c r="C116" s="1" t="inlineStr">
@@ -14429,12 +14429,12 @@
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>FER0120</t>
+          <t>FER0121</t>
         </is>
       </c>
       <c r="B117" s="1" t="inlineStr">
         <is>
-          <t>UB0120</t>
+          <t>UB0121</t>
         </is>
       </c>
       <c r="C117" s="1" t="inlineStr">
@@ -14446,12 +14446,12 @@
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>FER0121</t>
+          <t>FER0122</t>
         </is>
       </c>
       <c r="B118" s="1" t="inlineStr">
         <is>
-          <t>UB0121</t>
+          <t>UB0122</t>
         </is>
       </c>
       <c r="C118" s="1" t="inlineStr">
@@ -14463,12 +14463,12 @@
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>FER0122</t>
+          <t>FER0123</t>
         </is>
       </c>
       <c r="B119" s="1" t="inlineStr">
         <is>
-          <t>UB0122</t>
+          <t>UB0123</t>
         </is>
       </c>
       <c r="C119" s="1" t="inlineStr">
@@ -14480,12 +14480,12 @@
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>FER0123</t>
+          <t>FER0124</t>
         </is>
       </c>
       <c r="B120" s="1" t="inlineStr">
         <is>
-          <t>UB0123</t>
+          <t>UB0124</t>
         </is>
       </c>
       <c r="C120" s="1" t="inlineStr">
@@ -14497,12 +14497,12 @@
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>FER0124</t>
+          <t>FER0125</t>
         </is>
       </c>
       <c r="B121" s="1" t="inlineStr">
         <is>
-          <t>UB0124</t>
+          <t>UB0125</t>
         </is>
       </c>
       <c r="C121" s="1" t="inlineStr">
@@ -14514,12 +14514,12 @@
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>FER0125</t>
+          <t>FER0126</t>
         </is>
       </c>
       <c r="B122" s="1" t="inlineStr">
         <is>
-          <t>UB0125</t>
+          <t>UB0126</t>
         </is>
       </c>
       <c r="C122" s="1" t="inlineStr">
@@ -14531,12 +14531,12 @@
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>FER0126</t>
+          <t>FER0127</t>
         </is>
       </c>
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t>UB0126</t>
+          <t>UB0127</t>
         </is>
       </c>
       <c r="C123" s="1" t="inlineStr">
@@ -14548,12 +14548,12 @@
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>FER0127</t>
+          <t>FER0128</t>
         </is>
       </c>
       <c r="B124" s="1" t="inlineStr">
         <is>
-          <t>UB0127</t>
+          <t>UB0128</t>
         </is>
       </c>
       <c r="C124" s="1" t="inlineStr">
@@ -14565,12 +14565,12 @@
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>FER0128</t>
+          <t>FER0129</t>
         </is>
       </c>
       <c r="B125" s="1" t="inlineStr">
         <is>
-          <t>UB0128</t>
+          <t>UB0129</t>
         </is>
       </c>
       <c r="C125" s="1" t="inlineStr">
@@ -14582,12 +14582,12 @@
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>FER0129</t>
+          <t>FER0130</t>
         </is>
       </c>
       <c r="B126" s="1" t="inlineStr">
         <is>
-          <t>UB0129</t>
+          <t>UB0130</t>
         </is>
       </c>
       <c r="C126" s="1" t="inlineStr">
@@ -14599,12 +14599,12 @@
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>FER0130</t>
+          <t>FER0131</t>
         </is>
       </c>
       <c r="B127" s="1" t="inlineStr">
         <is>
-          <t>UB0130</t>
+          <t>UB0131</t>
         </is>
       </c>
       <c r="C127" s="1" t="inlineStr">
@@ -14616,12 +14616,12 @@
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>FER0131</t>
+          <t>FER0132</t>
         </is>
       </c>
       <c r="B128" s="1" t="inlineStr">
         <is>
-          <t>UB0131</t>
+          <t>UB0132</t>
         </is>
       </c>
       <c r="C128" s="1" t="inlineStr">
@@ -14633,12 +14633,12 @@
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>FER0132</t>
+          <t>FER0133</t>
         </is>
       </c>
       <c r="B129" s="1" t="inlineStr">
         <is>
-          <t>UB0132</t>
+          <t>UB0133</t>
         </is>
       </c>
       <c r="C129" s="1" t="inlineStr">
@@ -14650,12 +14650,12 @@
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>FER0133</t>
+          <t>FER0134</t>
         </is>
       </c>
       <c r="B130" s="1" t="inlineStr">
         <is>
-          <t>UB0133</t>
+          <t>UB0134</t>
         </is>
       </c>
       <c r="C130" s="1" t="inlineStr">
@@ -14667,12 +14667,12 @@
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>FER0134</t>
+          <t>FER0135</t>
         </is>
       </c>
       <c r="B131" s="1" t="inlineStr">
         <is>
-          <t>UB0134</t>
+          <t>UB0135</t>
         </is>
       </c>
       <c r="C131" s="1" t="inlineStr">
@@ -14684,12 +14684,12 @@
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>FER0135</t>
+          <t>FER0136</t>
         </is>
       </c>
       <c r="B132" s="1" t="inlineStr">
         <is>
-          <t>UB0135</t>
+          <t>UB0136</t>
         </is>
       </c>
       <c r="C132" s="1" t="inlineStr">
@@ -14701,12 +14701,12 @@
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>FER0136</t>
+          <t>FER0137</t>
         </is>
       </c>
       <c r="B133" s="1" t="inlineStr">
         <is>
-          <t>UB0136</t>
+          <t>UB0137</t>
         </is>
       </c>
       <c r="C133" s="1" t="inlineStr">
@@ -14718,12 +14718,12 @@
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>FER0137</t>
+          <t>FER0138</t>
         </is>
       </c>
       <c r="B134" s="1" t="inlineStr">
         <is>
-          <t>UB0137</t>
+          <t>UB0138</t>
         </is>
       </c>
       <c r="C134" s="1" t="inlineStr">
@@ -14735,12 +14735,12 @@
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>FER0138</t>
+          <t>FER0139</t>
         </is>
       </c>
       <c r="B135" s="1" t="inlineStr">
         <is>
-          <t>UB0138</t>
+          <t>UB0139</t>
         </is>
       </c>
       <c r="C135" s="1" t="inlineStr">
@@ -14752,12 +14752,12 @@
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>FER0139</t>
+          <t>FER0140</t>
         </is>
       </c>
       <c r="B136" s="1" t="inlineStr">
         <is>
-          <t>UB0139</t>
+          <t>UB0140</t>
         </is>
       </c>
       <c r="C136" s="1" t="inlineStr">
@@ -14769,12 +14769,12 @@
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>FER0140</t>
+          <t>FER0141</t>
         </is>
       </c>
       <c r="B137" s="1" t="inlineStr">
         <is>
-          <t>UB0140</t>
+          <t>UB0141</t>
         </is>
       </c>
       <c r="C137" s="1" t="inlineStr">
@@ -14786,12 +14786,12 @@
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>FER0141</t>
+          <t>FER0142</t>
         </is>
       </c>
       <c r="B138" s="1" t="inlineStr">
         <is>
-          <t>UB0141</t>
+          <t>UB0142</t>
         </is>
       </c>
       <c r="C138" s="1" t="inlineStr">
@@ -14803,12 +14803,12 @@
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>FER0142</t>
+          <t>FER0143</t>
         </is>
       </c>
       <c r="B139" s="1" t="inlineStr">
         <is>
-          <t>UB0142</t>
+          <t>UB0143</t>
         </is>
       </c>
       <c r="C139" s="1" t="inlineStr">
@@ -14820,12 +14820,12 @@
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>FER0143</t>
+          <t>FER0144</t>
         </is>
       </c>
       <c r="B140" s="1" t="inlineStr">
         <is>
-          <t>UB0143</t>
+          <t>UB0144</t>
         </is>
       </c>
       <c r="C140" s="1" t="inlineStr">
@@ -14837,12 +14837,12 @@
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>FER0144</t>
+          <t>FER0145</t>
         </is>
       </c>
       <c r="B141" s="1" t="inlineStr">
         <is>
-          <t>UB0144</t>
+          <t>UB0145</t>
         </is>
       </c>
       <c r="C141" s="1" t="inlineStr">
@@ -14854,12 +14854,12 @@
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>FER0145</t>
+          <t>FER0146</t>
         </is>
       </c>
       <c r="B142" s="1" t="inlineStr">
         <is>
-          <t>UB0145</t>
+          <t>UB0146</t>
         </is>
       </c>
       <c r="C142" s="1" t="inlineStr">
@@ -14871,12 +14871,12 @@
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>FER0146</t>
+          <t>FER0147</t>
         </is>
       </c>
       <c r="B143" s="1" t="inlineStr">
         <is>
-          <t>UB0146</t>
+          <t>UB0147</t>
         </is>
       </c>
       <c r="C143" s="1" t="inlineStr">
@@ -14888,12 +14888,12 @@
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>FER0147</t>
+          <t>FER0148</t>
         </is>
       </c>
       <c r="B144" s="1" t="inlineStr">
         <is>
-          <t>UB0147</t>
+          <t>UB0148</t>
         </is>
       </c>
       <c r="C144" s="1" t="inlineStr">
@@ -14905,12 +14905,12 @@
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>FER0148</t>
+          <t>FER0149</t>
         </is>
       </c>
       <c r="B145" s="1" t="inlineStr">
         <is>
-          <t>UB0148</t>
+          <t>UB0149</t>
         </is>
       </c>
       <c r="C145" s="1" t="inlineStr">
@@ -14922,12 +14922,12 @@
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>FER0149</t>
+          <t>FER0150</t>
         </is>
       </c>
       <c r="B146" s="1" t="inlineStr">
         <is>
-          <t>UB0149</t>
+          <t>UB0150</t>
         </is>
       </c>
       <c r="C146" s="1" t="inlineStr">
@@ -14939,12 +14939,12 @@
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>FER0150</t>
+          <t>FER0151</t>
         </is>
       </c>
       <c r="B147" s="1" t="inlineStr">
         <is>
-          <t>UB0150</t>
+          <t>UB0151</t>
         </is>
       </c>
       <c r="C147" s="1" t="inlineStr">
@@ -14956,12 +14956,12 @@
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>FER0151</t>
+          <t>FER0152</t>
         </is>
       </c>
       <c r="B148" s="1" t="inlineStr">
         <is>
-          <t>UB0151</t>
+          <t>UB0152</t>
         </is>
       </c>
       <c r="C148" s="1" t="inlineStr">
@@ -14973,12 +14973,12 @@
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>FER0152</t>
+          <t>FER0153</t>
         </is>
       </c>
       <c r="B149" s="1" t="inlineStr">
         <is>
-          <t>UB0152</t>
+          <t>UB0153</t>
         </is>
       </c>
       <c r="C149" s="1" t="inlineStr">
@@ -14990,12 +14990,12 @@
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>FER0153</t>
+          <t>FER0154</t>
         </is>
       </c>
       <c r="B150" s="1" t="inlineStr">
         <is>
-          <t>UB0153</t>
+          <t>UB0154</t>
         </is>
       </c>
       <c r="C150" s="1" t="inlineStr">
@@ -15007,12 +15007,12 @@
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>FER0154</t>
+          <t>FER0155</t>
         </is>
       </c>
       <c r="B151" s="1" t="inlineStr">
         <is>
-          <t>UB0154</t>
+          <t>UB0155</t>
         </is>
       </c>
       <c r="C151" s="1" t="inlineStr">
@@ -15024,12 +15024,12 @@
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>FER0155</t>
+          <t>FER0156</t>
         </is>
       </c>
       <c r="B152" s="1" t="inlineStr">
         <is>
-          <t>UB0155</t>
+          <t>UB0156</t>
         </is>
       </c>
       <c r="C152" s="1" t="inlineStr">
@@ -15041,12 +15041,12 @@
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>FER0156</t>
+          <t>FER0157</t>
         </is>
       </c>
       <c r="B153" s="1" t="inlineStr">
         <is>
-          <t>UB0156</t>
+          <t>UB0157</t>
         </is>
       </c>
       <c r="C153" s="1" t="inlineStr">
@@ -15058,12 +15058,12 @@
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>FER0157</t>
+          <t>FER0158</t>
         </is>
       </c>
       <c r="B154" s="1" t="inlineStr">
         <is>
-          <t>UB0157</t>
+          <t>UB0158</t>
         </is>
       </c>
       <c r="C154" s="1" t="inlineStr">
@@ -15075,12 +15075,12 @@
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>FER0158</t>
+          <t>FER0159</t>
         </is>
       </c>
       <c r="B155" s="1" t="inlineStr">
         <is>
-          <t>UB0158</t>
+          <t>UB0159</t>
         </is>
       </c>
       <c r="C155" s="1" t="inlineStr">
@@ -15092,12 +15092,12 @@
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>FER0159</t>
+          <t>FER0160</t>
         </is>
       </c>
       <c r="B156" s="1" t="inlineStr">
         <is>
-          <t>UB0159</t>
+          <t>UB0160</t>
         </is>
       </c>
       <c r="C156" s="1" t="inlineStr">
@@ -15109,12 +15109,12 @@
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>FER0160</t>
+          <t>FER0161</t>
         </is>
       </c>
       <c r="B157" s="1" t="inlineStr">
         <is>
-          <t>UB0160</t>
+          <t>UB0161</t>
         </is>
       </c>
       <c r="C157" s="1" t="inlineStr">
@@ -15126,12 +15126,12 @@
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>FER0161</t>
+          <t>FER0162</t>
         </is>
       </c>
       <c r="B158" s="1" t="inlineStr">
         <is>
-          <t>UB0161</t>
+          <t>UB0162</t>
         </is>
       </c>
       <c r="C158" s="1" t="inlineStr">
@@ -15143,12 +15143,12 @@
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>FER0162</t>
+          <t>FER0163</t>
         </is>
       </c>
       <c r="B159" s="1" t="inlineStr">
         <is>
-          <t>UB0162</t>
+          <t>UB0163</t>
         </is>
       </c>
       <c r="C159" s="1" t="inlineStr">
@@ -15160,12 +15160,12 @@
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>FER0163</t>
+          <t>FER0164</t>
         </is>
       </c>
       <c r="B160" s="1" t="inlineStr">
         <is>
-          <t>UB0163</t>
+          <t>UB0164</t>
         </is>
       </c>
       <c r="C160" s="1" t="inlineStr">
@@ -15177,12 +15177,12 @@
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>FER0164</t>
+          <t>FER0165</t>
         </is>
       </c>
       <c r="B161" s="1" t="inlineStr">
         <is>
-          <t>UB0164</t>
+          <t>UB0165</t>
         </is>
       </c>
       <c r="C161" s="1" t="inlineStr">
@@ -15194,12 +15194,12 @@
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>FER0165</t>
+          <t>FER0166</t>
         </is>
       </c>
       <c r="B162" s="1" t="inlineStr">
         <is>
-          <t>UB0165</t>
+          <t>UB0166</t>
         </is>
       </c>
       <c r="C162" s="1" t="inlineStr">
@@ -15211,12 +15211,12 @@
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>FER0166</t>
+          <t>FER0167</t>
         </is>
       </c>
       <c r="B163" s="1" t="inlineStr">
         <is>
-          <t>UB0166</t>
+          <t>UB0167</t>
         </is>
       </c>
       <c r="C163" s="1" t="inlineStr">
@@ -15228,12 +15228,12 @@
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>FER0167</t>
+          <t>FER0168</t>
         </is>
       </c>
       <c r="B164" s="1" t="inlineStr">
         <is>
-          <t>UB0167</t>
+          <t>UB0168</t>
         </is>
       </c>
       <c r="C164" s="1" t="inlineStr">
@@ -15245,12 +15245,12 @@
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>FER0168</t>
+          <t>FER0169</t>
         </is>
       </c>
       <c r="B165" s="1" t="inlineStr">
         <is>
-          <t>UB0168</t>
+          <t>UB0169</t>
         </is>
       </c>
       <c r="C165" s="1" t="inlineStr">
@@ -15262,12 +15262,12 @@
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>FER0169</t>
+          <t>FER0170</t>
         </is>
       </c>
       <c r="B166" s="1" t="inlineStr">
         <is>
-          <t>UB0169</t>
+          <t>UB0170</t>
         </is>
       </c>
       <c r="C166" s="1" t="inlineStr">
@@ -15279,12 +15279,12 @@
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>FER0170</t>
+          <t>FER0171</t>
         </is>
       </c>
       <c r="B167" s="1" t="inlineStr">
         <is>
-          <t>UB0170</t>
+          <t>UB0171</t>
         </is>
       </c>
       <c r="C167" s="1" t="inlineStr">
@@ -15296,12 +15296,12 @@
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>FER0171</t>
+          <t>FER0172</t>
         </is>
       </c>
       <c r="B168" s="1" t="inlineStr">
         <is>
-          <t>UB0171</t>
+          <t>UB0172</t>
         </is>
       </c>
       <c r="C168" s="1" t="inlineStr">
@@ -15313,12 +15313,12 @@
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>FER0172</t>
+          <t>FER0173</t>
         </is>
       </c>
       <c r="B169" s="1" t="inlineStr">
         <is>
-          <t>UB0172</t>
+          <t>UB0173</t>
         </is>
       </c>
       <c r="C169" s="1" t="inlineStr">
@@ -15330,12 +15330,12 @@
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>FER0173</t>
+          <t>FER0174</t>
         </is>
       </c>
       <c r="B170" s="1" t="inlineStr">
         <is>
-          <t>UB0173</t>
+          <t>UB0174</t>
         </is>
       </c>
       <c r="C170" s="1" t="inlineStr">
@@ -15347,12 +15347,12 @@
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t>FER0174</t>
+          <t>FER0175</t>
         </is>
       </c>
       <c r="B171" s="1" t="inlineStr">
         <is>
-          <t>UB0174</t>
+          <t>UB0175</t>
         </is>
       </c>
       <c r="C171" s="1" t="inlineStr">
@@ -15364,12 +15364,12 @@
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t>FER0175</t>
+          <t>FER0176</t>
         </is>
       </c>
       <c r="B172" s="1" t="inlineStr">
         <is>
-          <t>UB0175</t>
+          <t>UB0176</t>
         </is>
       </c>
       <c r="C172" s="1" t="inlineStr">
@@ -15381,12 +15381,12 @@
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
         <is>
-          <t>FER0176</t>
+          <t>FER0177</t>
         </is>
       </c>
       <c r="B173" s="1" t="inlineStr">
         <is>
-          <t>UB0176</t>
+          <t>UB0177</t>
         </is>
       </c>
       <c r="C173" s="1" t="inlineStr">
@@ -15398,12 +15398,12 @@
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
         <is>
-          <t>FER0177</t>
+          <t>FER0178</t>
         </is>
       </c>
       <c r="B174" s="1" t="inlineStr">
         <is>
-          <t>UB0177</t>
+          <t>UB0178</t>
         </is>
       </c>
       <c r="C174" s="1" t="inlineStr">
@@ -15415,12 +15415,12 @@
     <row r="175">
       <c r="A175" s="1" t="inlineStr">
         <is>
-          <t>FER0178</t>
+          <t>FER0179</t>
         </is>
       </c>
       <c r="B175" s="1" t="inlineStr">
         <is>
-          <t>UB0178</t>
+          <t>UB0179</t>
         </is>
       </c>
       <c r="C175" s="1" t="inlineStr">
@@ -15432,12 +15432,12 @@
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
         <is>
-          <t>FER0179</t>
+          <t>FER0180</t>
         </is>
       </c>
       <c r="B176" s="1" t="inlineStr">
         <is>
-          <t>UB0179</t>
+          <t>UB0180</t>
         </is>
       </c>
       <c r="C176" s="1" t="inlineStr">
@@ -15449,12 +15449,12 @@
     <row r="177">
       <c r="A177" s="1" t="inlineStr">
         <is>
-          <t>FER0180</t>
+          <t>FER0181</t>
         </is>
       </c>
       <c r="B177" s="1" t="inlineStr">
         <is>
-          <t>UB0180</t>
+          <t>UB0181</t>
         </is>
       </c>
       <c r="C177" s="1" t="inlineStr">
@@ -15466,12 +15466,12 @@
     <row r="178">
       <c r="A178" s="1" t="inlineStr">
         <is>
-          <t>FER0181</t>
+          <t>FER0182</t>
         </is>
       </c>
       <c r="B178" s="1" t="inlineStr">
         <is>
-          <t>UB0181</t>
+          <t>UB0182</t>
         </is>
       </c>
       <c r="C178" s="1" t="inlineStr">
@@ -15483,12 +15483,12 @@
     <row r="179">
       <c r="A179" s="1" t="inlineStr">
         <is>
-          <t>FER0182</t>
+          <t>FER0183</t>
         </is>
       </c>
       <c r="B179" s="1" t="inlineStr">
         <is>
-          <t>UB0182</t>
+          <t>UB0183</t>
         </is>
       </c>
       <c r="C179" s="1" t="inlineStr">
@@ -15500,12 +15500,12 @@
     <row r="180">
       <c r="A180" s="1" t="inlineStr">
         <is>
-          <t>FER0183</t>
+          <t>FER0184</t>
         </is>
       </c>
       <c r="B180" s="1" t="inlineStr">
         <is>
-          <t>UB0183</t>
+          <t>UB0184</t>
         </is>
       </c>
       <c r="C180" s="1" t="inlineStr">
@@ -15517,12 +15517,12 @@
     <row r="181">
       <c r="A181" s="1" t="inlineStr">
         <is>
-          <t>FER0184</t>
+          <t>FER0185</t>
         </is>
       </c>
       <c r="B181" s="1" t="inlineStr">
         <is>
-          <t>UB0184</t>
+          <t>UB0185</t>
         </is>
       </c>
       <c r="C181" s="1" t="inlineStr">
@@ -15534,12 +15534,12 @@
     <row r="182">
       <c r="A182" s="1" t="inlineStr">
         <is>
-          <t>FER0185</t>
+          <t>FER0186</t>
         </is>
       </c>
       <c r="B182" s="1" t="inlineStr">
         <is>
-          <t>UB0185</t>
+          <t>UB0186</t>
         </is>
       </c>
       <c r="C182" s="1" t="inlineStr">
@@ -15551,12 +15551,12 @@
     <row r="183">
       <c r="A183" s="1" t="inlineStr">
         <is>
-          <t>FER0186</t>
+          <t>FER0187</t>
         </is>
       </c>
       <c r="B183" s="1" t="inlineStr">
         <is>
-          <t>UB0186</t>
+          <t>UB0187</t>
         </is>
       </c>
       <c r="C183" s="1" t="inlineStr">
@@ -15568,12 +15568,12 @@
     <row r="184">
       <c r="A184" s="1" t="inlineStr">
         <is>
-          <t>FER0187</t>
+          <t>FER0188</t>
         </is>
       </c>
       <c r="B184" s="1" t="inlineStr">
         <is>
-          <t>UB0187</t>
+          <t>UB0188</t>
         </is>
       </c>
       <c r="C184" s="1" t="inlineStr">
@@ -15585,12 +15585,12 @@
     <row r="185">
       <c r="A185" s="1" t="inlineStr">
         <is>
-          <t>FER0188</t>
+          <t>FER0190</t>
         </is>
       </c>
       <c r="B185" s="1" t="inlineStr">
         <is>
-          <t>UB0188</t>
+          <t>UB0190</t>
         </is>
       </c>
       <c r="C185" s="1" t="inlineStr">
@@ -15602,12 +15602,12 @@
     <row r="186">
       <c r="A186" s="1" t="inlineStr">
         <is>
-          <t>FER0190</t>
+          <t>FER0191</t>
         </is>
       </c>
       <c r="B186" s="1" t="inlineStr">
         <is>
-          <t>UB0190</t>
+          <t>UB0191</t>
         </is>
       </c>
       <c r="C186" s="1" t="inlineStr">
@@ -15619,12 +15619,12 @@
     <row r="187">
       <c r="A187" s="1" t="inlineStr">
         <is>
-          <t>FER0191</t>
+          <t>FER0192</t>
         </is>
       </c>
       <c r="B187" s="1" t="inlineStr">
         <is>
-          <t>UB0191</t>
+          <t>UB0192</t>
         </is>
       </c>
       <c r="C187" s="1" t="inlineStr">
@@ -15636,12 +15636,12 @@
     <row r="188">
       <c r="A188" s="1" t="inlineStr">
         <is>
-          <t>FER0192</t>
+          <t>FER0193</t>
         </is>
       </c>
       <c r="B188" s="1" t="inlineStr">
         <is>
-          <t>UB0192</t>
+          <t>UB0193</t>
         </is>
       </c>
       <c r="C188" s="1" t="inlineStr">
@@ -15653,12 +15653,12 @@
     <row r="189">
       <c r="A189" s="1" t="inlineStr">
         <is>
-          <t>FER0193</t>
+          <t>FER0194</t>
         </is>
       </c>
       <c r="B189" s="1" t="inlineStr">
         <is>
-          <t>UB0193</t>
+          <t>UB0194</t>
         </is>
       </c>
       <c r="C189" s="1" t="inlineStr">
@@ -15670,12 +15670,12 @@
     <row r="190">
       <c r="A190" s="1" t="inlineStr">
         <is>
-          <t>FER0194</t>
+          <t>FER0195</t>
         </is>
       </c>
       <c r="B190" s="1" t="inlineStr">
         <is>
-          <t>UB0194</t>
+          <t>UB0195</t>
         </is>
       </c>
       <c r="C190" s="1" t="inlineStr">
@@ -15687,12 +15687,12 @@
     <row r="191">
       <c r="A191" s="1" t="inlineStr">
         <is>
-          <t>FER0195</t>
+          <t>FER0196</t>
         </is>
       </c>
       <c r="B191" s="1" t="inlineStr">
         <is>
-          <t>UB0195</t>
+          <t>UB0196</t>
         </is>
       </c>
       <c r="C191" s="1" t="inlineStr">
@@ -15704,12 +15704,12 @@
     <row r="192">
       <c r="A192" s="1" t="inlineStr">
         <is>
-          <t>FER0196</t>
+          <t>FER0197</t>
         </is>
       </c>
       <c r="B192" s="1" t="inlineStr">
         <is>
-          <t>UB0196</t>
+          <t>UB0197</t>
         </is>
       </c>
       <c r="C192" s="1" t="inlineStr">
@@ -15721,12 +15721,12 @@
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
         <is>
-          <t>FER0197</t>
+          <t>FER0198</t>
         </is>
       </c>
       <c r="B193" s="1" t="inlineStr">
         <is>
-          <t>UB0197</t>
+          <t>UB0198</t>
         </is>
       </c>
       <c r="C193" s="1" t="inlineStr">
@@ -15738,12 +15738,12 @@
     <row r="194">
       <c r="A194" s="1" t="inlineStr">
         <is>
-          <t>FER0198</t>
+          <t>FER0199</t>
         </is>
       </c>
       <c r="B194" s="1" t="inlineStr">
         <is>
-          <t>UB0198</t>
+          <t>UB0199</t>
         </is>
       </c>
       <c r="C194" s="1" t="inlineStr">
@@ -15755,12 +15755,12 @@
     <row r="195">
       <c r="A195" s="1" t="inlineStr">
         <is>
-          <t>FER0199</t>
+          <t>FER0200</t>
         </is>
       </c>
       <c r="B195" s="1" t="inlineStr">
         <is>
-          <t>UB0199</t>
+          <t>UB0200</t>
         </is>
       </c>
       <c r="C195" s="1" t="inlineStr">
@@ -15772,12 +15772,12 @@
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
         <is>
-          <t>FER0200</t>
+          <t>FER0006</t>
         </is>
       </c>
       <c r="B196" s="1" t="inlineStr">
         <is>
-          <t>UB0200</t>
+          <t>UB0006</t>
         </is>
       </c>
       <c r="C196" s="1" t="inlineStr">
@@ -15789,17 +15789,17 @@
     <row r="197">
       <c r="A197" s="1" t="inlineStr">
         <is>
-          <t>FER0006</t>
+          <t>FER0189</t>
         </is>
       </c>
       <c r="B197" s="1" t="inlineStr">
         <is>
-          <t>UB0006</t>
+          <t>UB0189</t>
         </is>
       </c>
       <c r="C197" s="1" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -15811,24 +15811,24 @@
       </c>
       <c r="B198" s="1" t="inlineStr">
         <is>
-          <t>UB0189</t>
+          <t>UB0001</t>
         </is>
       </c>
       <c r="C198" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
         <is>
-          <t>FER0189</t>
+          <t>FER0029</t>
         </is>
       </c>
       <c r="B199" s="1" t="inlineStr">
         <is>
-          <t>UB0001</t>
+          <t>UB0029</t>
         </is>
       </c>
       <c r="C199" s="1" t="inlineStr">
@@ -15840,12 +15840,12 @@
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
         <is>
-          <t>FER0029</t>
+          <t>FER0042</t>
         </is>
       </c>
       <c r="B200" s="1" t="inlineStr">
         <is>
-          <t>UB0029</t>
+          <t>UB0042</t>
         </is>
       </c>
       <c r="C200" s="1" t="inlineStr">
@@ -15862,12 +15862,12 @@
       </c>
       <c r="B201" s="1" t="inlineStr">
         <is>
-          <t>UB0042</t>
+          <t>UB0005</t>
         </is>
       </c>
       <c r="C201" s="1" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -15879,7 +15879,7 @@
       </c>
       <c r="B202" s="1" t="inlineStr">
         <is>
-          <t>UB0005</t>
+          <t>UB0015</t>
         </is>
       </c>
       <c r="C202" s="1" t="inlineStr">
@@ -15891,29 +15891,29 @@
     <row r="203">
       <c r="A203" s="1" t="inlineStr">
         <is>
-          <t>FER0042</t>
+          <t>FER0001</t>
         </is>
       </c>
       <c r="B203" s="1" t="inlineStr">
         <is>
-          <t>UB0015</t>
+          <t>UB0001</t>
         </is>
       </c>
       <c r="C203" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="inlineStr">
         <is>
-          <t>FER0001</t>
+          <t>FER0041</t>
         </is>
       </c>
       <c r="B204" s="1" t="inlineStr">
         <is>
-          <t>UB0001</t>
+          <t>UB0041</t>
         </is>
       </c>
       <c r="C204" s="1" t="inlineStr">

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -2815,7 +2815,7 @@
       </c>
       <c r="D89" s="1" t="inlineStr">
         <is>
-          <t>Caja eléctrica PVC 2 x 4 pulg. Artículo de ferretería para trabajos y proyectos relacionados con electricidad e iluminación.</t>
+          <t>Caja eléctrica PVC 2 x 4 pulg. Artículo de ferretería para trabajos y proyectos relacionados con electricidad e iluminación 88.</t>
         </is>
       </c>
       <c r="E89" s="1" t="inlineStr">
@@ -13868,12 +13868,12 @@
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>FER0088</t>
+          <t>FER0089</t>
         </is>
       </c>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>UB0088</t>
+          <t>UB0089</t>
         </is>
       </c>
       <c r="C84" s="1" t="inlineStr">
@@ -13885,12 +13885,12 @@
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>FER0089</t>
+          <t>FER0090</t>
         </is>
       </c>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>UB0089</t>
+          <t>UB0090</t>
         </is>
       </c>
       <c r="C85" s="1" t="inlineStr">
@@ -13902,12 +13902,12 @@
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>FER0090</t>
+          <t>FER0091</t>
         </is>
       </c>
       <c r="B86" s="1" t="inlineStr">
         <is>
-          <t>UB0090</t>
+          <t>UB0091</t>
         </is>
       </c>
       <c r="C86" s="1" t="inlineStr">
@@ -13919,12 +13919,12 @@
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>FER0091</t>
+          <t>FER0092</t>
         </is>
       </c>
       <c r="B87" s="1" t="inlineStr">
         <is>
-          <t>UB0091</t>
+          <t>UB0092</t>
         </is>
       </c>
       <c r="C87" s="1" t="inlineStr">
@@ -13936,12 +13936,12 @@
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>FER0092</t>
+          <t>FER0093</t>
         </is>
       </c>
       <c r="B88" s="1" t="inlineStr">
         <is>
-          <t>UB0092</t>
+          <t>UB0093</t>
         </is>
       </c>
       <c r="C88" s="1" t="inlineStr">
@@ -13953,12 +13953,12 @@
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>FER0093</t>
+          <t>FER0094</t>
         </is>
       </c>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>UB0093</t>
+          <t>UB0094</t>
         </is>
       </c>
       <c r="C89" s="1" t="inlineStr">
@@ -13970,12 +13970,12 @@
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>FER0094</t>
+          <t>FER0095</t>
         </is>
       </c>
       <c r="B90" s="1" t="inlineStr">
         <is>
-          <t>UB0094</t>
+          <t>UB0095</t>
         </is>
       </c>
       <c r="C90" s="1" t="inlineStr">
@@ -13987,12 +13987,12 @@
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>FER0095</t>
+          <t>FER0096</t>
         </is>
       </c>
       <c r="B91" s="1" t="inlineStr">
         <is>
-          <t>UB0095</t>
+          <t>UB0096</t>
         </is>
       </c>
       <c r="C91" s="1" t="inlineStr">
@@ -14004,12 +14004,12 @@
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>FER0096</t>
+          <t>FER0097</t>
         </is>
       </c>
       <c r="B92" s="1" t="inlineStr">
         <is>
-          <t>UB0096</t>
+          <t>UB0097</t>
         </is>
       </c>
       <c r="C92" s="1" t="inlineStr">
@@ -14021,12 +14021,12 @@
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>FER0097</t>
+          <t>FER0098</t>
         </is>
       </c>
       <c r="B93" s="1" t="inlineStr">
         <is>
-          <t>UB0097</t>
+          <t>UB0098</t>
         </is>
       </c>
       <c r="C93" s="1" t="inlineStr">
@@ -14038,12 +14038,12 @@
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>FER0098</t>
+          <t>FER0099</t>
         </is>
       </c>
       <c r="B94" s="1" t="inlineStr">
         <is>
-          <t>UB0098</t>
+          <t>UB0099</t>
         </is>
       </c>
       <c r="C94" s="1" t="inlineStr">
@@ -14055,12 +14055,12 @@
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>FER0099</t>
+          <t>FER0100</t>
         </is>
       </c>
       <c r="B95" s="1" t="inlineStr">
         <is>
-          <t>UB0099</t>
+          <t>UB0100</t>
         </is>
       </c>
       <c r="C95" s="1" t="inlineStr">
@@ -14072,12 +14072,12 @@
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>FER0100</t>
+          <t>FER0101</t>
         </is>
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>UB0100</t>
+          <t>UB0101</t>
         </is>
       </c>
       <c r="C96" s="1" t="inlineStr">
@@ -14089,12 +14089,12 @@
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>FER0101</t>
+          <t>FER0102</t>
         </is>
       </c>
       <c r="B97" s="1" t="inlineStr">
         <is>
-          <t>UB0101</t>
+          <t>UB0102</t>
         </is>
       </c>
       <c r="C97" s="1" t="inlineStr">
@@ -14106,12 +14106,12 @@
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>FER0102</t>
+          <t>FER0103</t>
         </is>
       </c>
       <c r="B98" s="1" t="inlineStr">
         <is>
-          <t>UB0102</t>
+          <t>UB0103</t>
         </is>
       </c>
       <c r="C98" s="1" t="inlineStr">
@@ -14123,12 +14123,12 @@
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>FER0103</t>
+          <t>FER0104</t>
         </is>
       </c>
       <c r="B99" s="1" t="inlineStr">
         <is>
-          <t>UB0103</t>
+          <t>UB0104</t>
         </is>
       </c>
       <c r="C99" s="1" t="inlineStr">
@@ -14140,12 +14140,12 @@
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>FER0104</t>
+          <t>FER0105</t>
         </is>
       </c>
       <c r="B100" s="1" t="inlineStr">
         <is>
-          <t>UB0104</t>
+          <t>UB0105</t>
         </is>
       </c>
       <c r="C100" s="1" t="inlineStr">
@@ -14157,12 +14157,12 @@
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>FER0105</t>
+          <t>FER0106</t>
         </is>
       </c>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t>UB0105</t>
+          <t>UB0106</t>
         </is>
       </c>
       <c r="C101" s="1" t="inlineStr">
@@ -14174,12 +14174,12 @@
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>FER0106</t>
+          <t>FER0107</t>
         </is>
       </c>
       <c r="B102" s="1" t="inlineStr">
         <is>
-          <t>UB0106</t>
+          <t>UB0107</t>
         </is>
       </c>
       <c r="C102" s="1" t="inlineStr">
@@ -14191,12 +14191,12 @@
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>FER0107</t>
+          <t>FER0108</t>
         </is>
       </c>
       <c r="B103" s="1" t="inlineStr">
         <is>
-          <t>UB0107</t>
+          <t>UB0108</t>
         </is>
       </c>
       <c r="C103" s="1" t="inlineStr">
@@ -14208,12 +14208,12 @@
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>FER0108</t>
+          <t>FER0109</t>
         </is>
       </c>
       <c r="B104" s="1" t="inlineStr">
         <is>
-          <t>UB0108</t>
+          <t>UB0109</t>
         </is>
       </c>
       <c r="C104" s="1" t="inlineStr">
@@ -14225,12 +14225,12 @@
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>FER0109</t>
+          <t>FER0110</t>
         </is>
       </c>
       <c r="B105" s="1" t="inlineStr">
         <is>
-          <t>UB0109</t>
+          <t>UB0110</t>
         </is>
       </c>
       <c r="C105" s="1" t="inlineStr">
@@ -14242,12 +14242,12 @@
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>FER0110</t>
+          <t>FER0111</t>
         </is>
       </c>
       <c r="B106" s="1" t="inlineStr">
         <is>
-          <t>UB0110</t>
+          <t>UB0111</t>
         </is>
       </c>
       <c r="C106" s="1" t="inlineStr">
@@ -14259,12 +14259,12 @@
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>FER0111</t>
+          <t>FER0112</t>
         </is>
       </c>
       <c r="B107" s="1" t="inlineStr">
         <is>
-          <t>UB0111</t>
+          <t>UB0112</t>
         </is>
       </c>
       <c r="C107" s="1" t="inlineStr">
@@ -14276,12 +14276,12 @@
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>FER0112</t>
+          <t>FER0113</t>
         </is>
       </c>
       <c r="B108" s="1" t="inlineStr">
         <is>
-          <t>UB0112</t>
+          <t>UB0113</t>
         </is>
       </c>
       <c r="C108" s="1" t="inlineStr">
@@ -14293,12 +14293,12 @@
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>FER0113</t>
+          <t>FER0114</t>
         </is>
       </c>
       <c r="B109" s="1" t="inlineStr">
         <is>
-          <t>UB0113</t>
+          <t>UB0114</t>
         </is>
       </c>
       <c r="C109" s="1" t="inlineStr">
@@ -14310,12 +14310,12 @@
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>FER0114</t>
+          <t>FER0115</t>
         </is>
       </c>
       <c r="B110" s="1" t="inlineStr">
         <is>
-          <t>UB0114</t>
+          <t>UB0115</t>
         </is>
       </c>
       <c r="C110" s="1" t="inlineStr">
@@ -14327,12 +14327,12 @@
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>FER0115</t>
+          <t>FER0116</t>
         </is>
       </c>
       <c r="B111" s="1" t="inlineStr">
         <is>
-          <t>UB0115</t>
+          <t>UB0116</t>
         </is>
       </c>
       <c r="C111" s="1" t="inlineStr">
@@ -14344,12 +14344,12 @@
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>FER0116</t>
+          <t>FER0117</t>
         </is>
       </c>
       <c r="B112" s="1" t="inlineStr">
         <is>
-          <t>UB0116</t>
+          <t>UB0117</t>
         </is>
       </c>
       <c r="C112" s="1" t="inlineStr">
@@ -14361,12 +14361,12 @@
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>FER0117</t>
+          <t>FER0118</t>
         </is>
       </c>
       <c r="B113" s="1" t="inlineStr">
         <is>
-          <t>UB0117</t>
+          <t>UB0118</t>
         </is>
       </c>
       <c r="C113" s="1" t="inlineStr">
@@ -14378,12 +14378,12 @@
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>FER0118</t>
+          <t>FER0119</t>
         </is>
       </c>
       <c r="B114" s="1" t="inlineStr">
         <is>
-          <t>UB0118</t>
+          <t>UB0119</t>
         </is>
       </c>
       <c r="C114" s="1" t="inlineStr">
@@ -14395,12 +14395,12 @@
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>FER0119</t>
+          <t>FER0120</t>
         </is>
       </c>
       <c r="B115" s="1" t="inlineStr">
         <is>
-          <t>UB0119</t>
+          <t>UB0120</t>
         </is>
       </c>
       <c r="C115" s="1" t="inlineStr">
@@ -14412,12 +14412,12 @@
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>FER0120</t>
+          <t>FER0121</t>
         </is>
       </c>
       <c r="B116" s="1" t="inlineStr">
         <is>
-          <t>UB0120</t>
+          <t>UB0121</t>
         </is>
       </c>
       <c r="C116" s="1" t="inlineStr">
@@ -14429,12 +14429,12 @@
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>FER0121</t>
+          <t>FER0122</t>
         </is>
       </c>
       <c r="B117" s="1" t="inlineStr">
         <is>
-          <t>UB0121</t>
+          <t>UB0122</t>
         </is>
       </c>
       <c r="C117" s="1" t="inlineStr">
@@ -14446,12 +14446,12 @@
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>FER0122</t>
+          <t>FER0123</t>
         </is>
       </c>
       <c r="B118" s="1" t="inlineStr">
         <is>
-          <t>UB0122</t>
+          <t>UB0123</t>
         </is>
       </c>
       <c r="C118" s="1" t="inlineStr">
@@ -14463,12 +14463,12 @@
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>FER0123</t>
+          <t>FER0124</t>
         </is>
       </c>
       <c r="B119" s="1" t="inlineStr">
         <is>
-          <t>UB0123</t>
+          <t>UB0124</t>
         </is>
       </c>
       <c r="C119" s="1" t="inlineStr">
@@ -14480,12 +14480,12 @@
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>FER0124</t>
+          <t>FER0125</t>
         </is>
       </c>
       <c r="B120" s="1" t="inlineStr">
         <is>
-          <t>UB0124</t>
+          <t>UB0125</t>
         </is>
       </c>
       <c r="C120" s="1" t="inlineStr">
@@ -14497,12 +14497,12 @@
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>FER0125</t>
+          <t>FER0126</t>
         </is>
       </c>
       <c r="B121" s="1" t="inlineStr">
         <is>
-          <t>UB0125</t>
+          <t>UB0126</t>
         </is>
       </c>
       <c r="C121" s="1" t="inlineStr">
@@ -14514,12 +14514,12 @@
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>FER0126</t>
+          <t>FER0127</t>
         </is>
       </c>
       <c r="B122" s="1" t="inlineStr">
         <is>
-          <t>UB0126</t>
+          <t>UB0127</t>
         </is>
       </c>
       <c r="C122" s="1" t="inlineStr">
@@ -14531,12 +14531,12 @@
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>FER0127</t>
+          <t>FER0128</t>
         </is>
       </c>
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t>UB0127</t>
+          <t>UB0128</t>
         </is>
       </c>
       <c r="C123" s="1" t="inlineStr">
@@ -14548,12 +14548,12 @@
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>FER0128</t>
+          <t>FER0129</t>
         </is>
       </c>
       <c r="B124" s="1" t="inlineStr">
         <is>
-          <t>UB0128</t>
+          <t>UB0129</t>
         </is>
       </c>
       <c r="C124" s="1" t="inlineStr">
@@ -14565,12 +14565,12 @@
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>FER0129</t>
+          <t>FER0130</t>
         </is>
       </c>
       <c r="B125" s="1" t="inlineStr">
         <is>
-          <t>UB0129</t>
+          <t>UB0130</t>
         </is>
       </c>
       <c r="C125" s="1" t="inlineStr">
@@ -14582,12 +14582,12 @@
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>FER0130</t>
+          <t>FER0131</t>
         </is>
       </c>
       <c r="B126" s="1" t="inlineStr">
         <is>
-          <t>UB0130</t>
+          <t>UB0131</t>
         </is>
       </c>
       <c r="C126" s="1" t="inlineStr">
@@ -14599,12 +14599,12 @@
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>FER0131</t>
+          <t>FER0132</t>
         </is>
       </c>
       <c r="B127" s="1" t="inlineStr">
         <is>
-          <t>UB0131</t>
+          <t>UB0132</t>
         </is>
       </c>
       <c r="C127" s="1" t="inlineStr">
@@ -14616,12 +14616,12 @@
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>FER0132</t>
+          <t>FER0133</t>
         </is>
       </c>
       <c r="B128" s="1" t="inlineStr">
         <is>
-          <t>UB0132</t>
+          <t>UB0133</t>
         </is>
       </c>
       <c r="C128" s="1" t="inlineStr">
@@ -14633,12 +14633,12 @@
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>FER0133</t>
+          <t>FER0134</t>
         </is>
       </c>
       <c r="B129" s="1" t="inlineStr">
         <is>
-          <t>UB0133</t>
+          <t>UB0134</t>
         </is>
       </c>
       <c r="C129" s="1" t="inlineStr">
@@ -14650,12 +14650,12 @@
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>FER0134</t>
+          <t>FER0135</t>
         </is>
       </c>
       <c r="B130" s="1" t="inlineStr">
         <is>
-          <t>UB0134</t>
+          <t>UB0135</t>
         </is>
       </c>
       <c r="C130" s="1" t="inlineStr">
@@ -14667,12 +14667,12 @@
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>FER0135</t>
+          <t>FER0136</t>
         </is>
       </c>
       <c r="B131" s="1" t="inlineStr">
         <is>
-          <t>UB0135</t>
+          <t>UB0136</t>
         </is>
       </c>
       <c r="C131" s="1" t="inlineStr">
@@ -14684,12 +14684,12 @@
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>FER0136</t>
+          <t>FER0137</t>
         </is>
       </c>
       <c r="B132" s="1" t="inlineStr">
         <is>
-          <t>UB0136</t>
+          <t>UB0137</t>
         </is>
       </c>
       <c r="C132" s="1" t="inlineStr">
@@ -14701,12 +14701,12 @@
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>FER0137</t>
+          <t>FER0138</t>
         </is>
       </c>
       <c r="B133" s="1" t="inlineStr">
         <is>
-          <t>UB0137</t>
+          <t>UB0138</t>
         </is>
       </c>
       <c r="C133" s="1" t="inlineStr">
@@ -14718,12 +14718,12 @@
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>FER0138</t>
+          <t>FER0139</t>
         </is>
       </c>
       <c r="B134" s="1" t="inlineStr">
         <is>
-          <t>UB0138</t>
+          <t>UB0139</t>
         </is>
       </c>
       <c r="C134" s="1" t="inlineStr">
@@ -14735,12 +14735,12 @@
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>FER0139</t>
+          <t>FER0140</t>
         </is>
       </c>
       <c r="B135" s="1" t="inlineStr">
         <is>
-          <t>UB0139</t>
+          <t>UB0140</t>
         </is>
       </c>
       <c r="C135" s="1" t="inlineStr">
@@ -14752,12 +14752,12 @@
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>FER0140</t>
+          <t>FER0141</t>
         </is>
       </c>
       <c r="B136" s="1" t="inlineStr">
         <is>
-          <t>UB0140</t>
+          <t>UB0141</t>
         </is>
       </c>
       <c r="C136" s="1" t="inlineStr">
@@ -14769,12 +14769,12 @@
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>FER0141</t>
+          <t>FER0142</t>
         </is>
       </c>
       <c r="B137" s="1" t="inlineStr">
         <is>
-          <t>UB0141</t>
+          <t>UB0142</t>
         </is>
       </c>
       <c r="C137" s="1" t="inlineStr">
@@ -14786,12 +14786,12 @@
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>FER0142</t>
+          <t>FER0143</t>
         </is>
       </c>
       <c r="B138" s="1" t="inlineStr">
         <is>
-          <t>UB0142</t>
+          <t>UB0143</t>
         </is>
       </c>
       <c r="C138" s="1" t="inlineStr">
@@ -14803,12 +14803,12 @@
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>FER0143</t>
+          <t>FER0144</t>
         </is>
       </c>
       <c r="B139" s="1" t="inlineStr">
         <is>
-          <t>UB0143</t>
+          <t>UB0144</t>
         </is>
       </c>
       <c r="C139" s="1" t="inlineStr">
@@ -14820,12 +14820,12 @@
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>FER0144</t>
+          <t>FER0145</t>
         </is>
       </c>
       <c r="B140" s="1" t="inlineStr">
         <is>
-          <t>UB0144</t>
+          <t>UB0145</t>
         </is>
       </c>
       <c r="C140" s="1" t="inlineStr">
@@ -14837,12 +14837,12 @@
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>FER0145</t>
+          <t>FER0146</t>
         </is>
       </c>
       <c r="B141" s="1" t="inlineStr">
         <is>
-          <t>UB0145</t>
+          <t>UB0146</t>
         </is>
       </c>
       <c r="C141" s="1" t="inlineStr">
@@ -14854,12 +14854,12 @@
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>FER0146</t>
+          <t>FER0147</t>
         </is>
       </c>
       <c r="B142" s="1" t="inlineStr">
         <is>
-          <t>UB0146</t>
+          <t>UB0147</t>
         </is>
       </c>
       <c r="C142" s="1" t="inlineStr">
@@ -14871,12 +14871,12 @@
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>FER0147</t>
+          <t>FER0148</t>
         </is>
       </c>
       <c r="B143" s="1" t="inlineStr">
         <is>
-          <t>UB0147</t>
+          <t>UB0148</t>
         </is>
       </c>
       <c r="C143" s="1" t="inlineStr">
@@ -14888,12 +14888,12 @@
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>FER0148</t>
+          <t>FER0149</t>
         </is>
       </c>
       <c r="B144" s="1" t="inlineStr">
         <is>
-          <t>UB0148</t>
+          <t>UB0149</t>
         </is>
       </c>
       <c r="C144" s="1" t="inlineStr">
@@ -14905,12 +14905,12 @@
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>FER0149</t>
+          <t>FER0150</t>
         </is>
       </c>
       <c r="B145" s="1" t="inlineStr">
         <is>
-          <t>UB0149</t>
+          <t>UB0150</t>
         </is>
       </c>
       <c r="C145" s="1" t="inlineStr">
@@ -14922,12 +14922,12 @@
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>FER0150</t>
+          <t>FER0151</t>
         </is>
       </c>
       <c r="B146" s="1" t="inlineStr">
         <is>
-          <t>UB0150</t>
+          <t>UB0151</t>
         </is>
       </c>
       <c r="C146" s="1" t="inlineStr">
@@ -14939,12 +14939,12 @@
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>FER0151</t>
+          <t>FER0152</t>
         </is>
       </c>
       <c r="B147" s="1" t="inlineStr">
         <is>
-          <t>UB0151</t>
+          <t>UB0152</t>
         </is>
       </c>
       <c r="C147" s="1" t="inlineStr">
@@ -14956,12 +14956,12 @@
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>FER0152</t>
+          <t>FER0153</t>
         </is>
       </c>
       <c r="B148" s="1" t="inlineStr">
         <is>
-          <t>UB0152</t>
+          <t>UB0153</t>
         </is>
       </c>
       <c r="C148" s="1" t="inlineStr">
@@ -14973,12 +14973,12 @@
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>FER0153</t>
+          <t>FER0154</t>
         </is>
       </c>
       <c r="B149" s="1" t="inlineStr">
         <is>
-          <t>UB0153</t>
+          <t>UB0154</t>
         </is>
       </c>
       <c r="C149" s="1" t="inlineStr">
@@ -14990,12 +14990,12 @@
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>FER0154</t>
+          <t>FER0155</t>
         </is>
       </c>
       <c r="B150" s="1" t="inlineStr">
         <is>
-          <t>UB0154</t>
+          <t>UB0155</t>
         </is>
       </c>
       <c r="C150" s="1" t="inlineStr">
@@ -15007,12 +15007,12 @@
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>FER0155</t>
+          <t>FER0156</t>
         </is>
       </c>
       <c r="B151" s="1" t="inlineStr">
         <is>
-          <t>UB0155</t>
+          <t>UB0156</t>
         </is>
       </c>
       <c r="C151" s="1" t="inlineStr">
@@ -15024,12 +15024,12 @@
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>FER0156</t>
+          <t>FER0157</t>
         </is>
       </c>
       <c r="B152" s="1" t="inlineStr">
         <is>
-          <t>UB0156</t>
+          <t>UB0157</t>
         </is>
       </c>
       <c r="C152" s="1" t="inlineStr">
@@ -15041,12 +15041,12 @@
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>FER0157</t>
+          <t>FER0158</t>
         </is>
       </c>
       <c r="B153" s="1" t="inlineStr">
         <is>
-          <t>UB0157</t>
+          <t>UB0158</t>
         </is>
       </c>
       <c r="C153" s="1" t="inlineStr">
@@ -15058,12 +15058,12 @@
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>FER0158</t>
+          <t>FER0159</t>
         </is>
       </c>
       <c r="B154" s="1" t="inlineStr">
         <is>
-          <t>UB0158</t>
+          <t>UB0159</t>
         </is>
       </c>
       <c r="C154" s="1" t="inlineStr">
@@ -15075,12 +15075,12 @@
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>FER0159</t>
+          <t>FER0160</t>
         </is>
       </c>
       <c r="B155" s="1" t="inlineStr">
         <is>
-          <t>UB0159</t>
+          <t>UB0160</t>
         </is>
       </c>
       <c r="C155" s="1" t="inlineStr">
@@ -15092,12 +15092,12 @@
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>FER0160</t>
+          <t>FER0161</t>
         </is>
       </c>
       <c r="B156" s="1" t="inlineStr">
         <is>
-          <t>UB0160</t>
+          <t>UB0161</t>
         </is>
       </c>
       <c r="C156" s="1" t="inlineStr">
@@ -15109,12 +15109,12 @@
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>FER0161</t>
+          <t>FER0162</t>
         </is>
       </c>
       <c r="B157" s="1" t="inlineStr">
         <is>
-          <t>UB0161</t>
+          <t>UB0162</t>
         </is>
       </c>
       <c r="C157" s="1" t="inlineStr">
@@ -15126,12 +15126,12 @@
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>FER0162</t>
+          <t>FER0163</t>
         </is>
       </c>
       <c r="B158" s="1" t="inlineStr">
         <is>
-          <t>UB0162</t>
+          <t>UB0163</t>
         </is>
       </c>
       <c r="C158" s="1" t="inlineStr">
@@ -15143,12 +15143,12 @@
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>FER0163</t>
+          <t>FER0164</t>
         </is>
       </c>
       <c r="B159" s="1" t="inlineStr">
         <is>
-          <t>UB0163</t>
+          <t>UB0164</t>
         </is>
       </c>
       <c r="C159" s="1" t="inlineStr">
@@ -15160,12 +15160,12 @@
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>FER0164</t>
+          <t>FER0165</t>
         </is>
       </c>
       <c r="B160" s="1" t="inlineStr">
         <is>
-          <t>UB0164</t>
+          <t>UB0165</t>
         </is>
       </c>
       <c r="C160" s="1" t="inlineStr">
@@ -15177,12 +15177,12 @@
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>FER0165</t>
+          <t>FER0166</t>
         </is>
       </c>
       <c r="B161" s="1" t="inlineStr">
         <is>
-          <t>UB0165</t>
+          <t>UB0166</t>
         </is>
       </c>
       <c r="C161" s="1" t="inlineStr">
@@ -15194,12 +15194,12 @@
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>FER0166</t>
+          <t>FER0167</t>
         </is>
       </c>
       <c r="B162" s="1" t="inlineStr">
         <is>
-          <t>UB0166</t>
+          <t>UB0167</t>
         </is>
       </c>
       <c r="C162" s="1" t="inlineStr">
@@ -15211,12 +15211,12 @@
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>FER0167</t>
+          <t>FER0168</t>
         </is>
       </c>
       <c r="B163" s="1" t="inlineStr">
         <is>
-          <t>UB0167</t>
+          <t>UB0168</t>
         </is>
       </c>
       <c r="C163" s="1" t="inlineStr">
@@ -15228,12 +15228,12 @@
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>FER0168</t>
+          <t>FER0169</t>
         </is>
       </c>
       <c r="B164" s="1" t="inlineStr">
         <is>
-          <t>UB0168</t>
+          <t>UB0169</t>
         </is>
       </c>
       <c r="C164" s="1" t="inlineStr">
@@ -15245,12 +15245,12 @@
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>FER0169</t>
+          <t>FER0170</t>
         </is>
       </c>
       <c r="B165" s="1" t="inlineStr">
         <is>
-          <t>UB0169</t>
+          <t>UB0170</t>
         </is>
       </c>
       <c r="C165" s="1" t="inlineStr">
@@ -15262,12 +15262,12 @@
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>FER0170</t>
+          <t>FER0171</t>
         </is>
       </c>
       <c r="B166" s="1" t="inlineStr">
         <is>
-          <t>UB0170</t>
+          <t>UB0171</t>
         </is>
       </c>
       <c r="C166" s="1" t="inlineStr">
@@ -15279,12 +15279,12 @@
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>FER0171</t>
+          <t>FER0172</t>
         </is>
       </c>
       <c r="B167" s="1" t="inlineStr">
         <is>
-          <t>UB0171</t>
+          <t>UB0172</t>
         </is>
       </c>
       <c r="C167" s="1" t="inlineStr">
@@ -15296,12 +15296,12 @@
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>FER0172</t>
+          <t>FER0173</t>
         </is>
       </c>
       <c r="B168" s="1" t="inlineStr">
         <is>
-          <t>UB0172</t>
+          <t>UB0173</t>
         </is>
       </c>
       <c r="C168" s="1" t="inlineStr">
@@ -15313,12 +15313,12 @@
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>FER0173</t>
+          <t>FER0174</t>
         </is>
       </c>
       <c r="B169" s="1" t="inlineStr">
         <is>
-          <t>UB0173</t>
+          <t>UB0174</t>
         </is>
       </c>
       <c r="C169" s="1" t="inlineStr">
@@ -15330,12 +15330,12 @@
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>FER0174</t>
+          <t>FER0175</t>
         </is>
       </c>
       <c r="B170" s="1" t="inlineStr">
         <is>
-          <t>UB0174</t>
+          <t>UB0175</t>
         </is>
       </c>
       <c r="C170" s="1" t="inlineStr">
@@ -15347,12 +15347,12 @@
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t>FER0175</t>
+          <t>FER0176</t>
         </is>
       </c>
       <c r="B171" s="1" t="inlineStr">
         <is>
-          <t>UB0175</t>
+          <t>UB0176</t>
         </is>
       </c>
       <c r="C171" s="1" t="inlineStr">
@@ -15364,12 +15364,12 @@
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t>FER0176</t>
+          <t>FER0177</t>
         </is>
       </c>
       <c r="B172" s="1" t="inlineStr">
         <is>
-          <t>UB0176</t>
+          <t>UB0177</t>
         </is>
       </c>
       <c r="C172" s="1" t="inlineStr">
@@ -15381,12 +15381,12 @@
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
         <is>
-          <t>FER0177</t>
+          <t>FER0178</t>
         </is>
       </c>
       <c r="B173" s="1" t="inlineStr">
         <is>
-          <t>UB0177</t>
+          <t>UB0178</t>
         </is>
       </c>
       <c r="C173" s="1" t="inlineStr">
@@ -15398,12 +15398,12 @@
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
         <is>
-          <t>FER0178</t>
+          <t>FER0179</t>
         </is>
       </c>
       <c r="B174" s="1" t="inlineStr">
         <is>
-          <t>UB0178</t>
+          <t>UB0179</t>
         </is>
       </c>
       <c r="C174" s="1" t="inlineStr">
@@ -15415,12 +15415,12 @@
     <row r="175">
       <c r="A175" s="1" t="inlineStr">
         <is>
-          <t>FER0179</t>
+          <t>FER0180</t>
         </is>
       </c>
       <c r="B175" s="1" t="inlineStr">
         <is>
-          <t>UB0179</t>
+          <t>UB0180</t>
         </is>
       </c>
       <c r="C175" s="1" t="inlineStr">
@@ -15432,12 +15432,12 @@
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
         <is>
-          <t>FER0180</t>
+          <t>FER0181</t>
         </is>
       </c>
       <c r="B176" s="1" t="inlineStr">
         <is>
-          <t>UB0180</t>
+          <t>UB0181</t>
         </is>
       </c>
       <c r="C176" s="1" t="inlineStr">
@@ -15449,12 +15449,12 @@
     <row r="177">
       <c r="A177" s="1" t="inlineStr">
         <is>
-          <t>FER0181</t>
+          <t>FER0182</t>
         </is>
       </c>
       <c r="B177" s="1" t="inlineStr">
         <is>
-          <t>UB0181</t>
+          <t>UB0182</t>
         </is>
       </c>
       <c r="C177" s="1" t="inlineStr">
@@ -15466,12 +15466,12 @@
     <row r="178">
       <c r="A178" s="1" t="inlineStr">
         <is>
-          <t>FER0182</t>
+          <t>FER0183</t>
         </is>
       </c>
       <c r="B178" s="1" t="inlineStr">
         <is>
-          <t>UB0182</t>
+          <t>UB0183</t>
         </is>
       </c>
       <c r="C178" s="1" t="inlineStr">
@@ -15483,12 +15483,12 @@
     <row r="179">
       <c r="A179" s="1" t="inlineStr">
         <is>
-          <t>FER0183</t>
+          <t>FER0184</t>
         </is>
       </c>
       <c r="B179" s="1" t="inlineStr">
         <is>
-          <t>UB0183</t>
+          <t>UB0184</t>
         </is>
       </c>
       <c r="C179" s="1" t="inlineStr">
@@ -15500,12 +15500,12 @@
     <row r="180">
       <c r="A180" s="1" t="inlineStr">
         <is>
-          <t>FER0184</t>
+          <t>FER0185</t>
         </is>
       </c>
       <c r="B180" s="1" t="inlineStr">
         <is>
-          <t>UB0184</t>
+          <t>UB0185</t>
         </is>
       </c>
       <c r="C180" s="1" t="inlineStr">
@@ -15517,12 +15517,12 @@
     <row r="181">
       <c r="A181" s="1" t="inlineStr">
         <is>
-          <t>FER0185</t>
+          <t>FER0186</t>
         </is>
       </c>
       <c r="B181" s="1" t="inlineStr">
         <is>
-          <t>UB0185</t>
+          <t>UB0186</t>
         </is>
       </c>
       <c r="C181" s="1" t="inlineStr">
@@ -15534,12 +15534,12 @@
     <row r="182">
       <c r="A182" s="1" t="inlineStr">
         <is>
-          <t>FER0186</t>
+          <t>FER0187</t>
         </is>
       </c>
       <c r="B182" s="1" t="inlineStr">
         <is>
-          <t>UB0186</t>
+          <t>UB0187</t>
         </is>
       </c>
       <c r="C182" s="1" t="inlineStr">
@@ -15551,12 +15551,12 @@
     <row r="183">
       <c r="A183" s="1" t="inlineStr">
         <is>
-          <t>FER0187</t>
+          <t>FER0188</t>
         </is>
       </c>
       <c r="B183" s="1" t="inlineStr">
         <is>
-          <t>UB0187</t>
+          <t>UB0188</t>
         </is>
       </c>
       <c r="C183" s="1" t="inlineStr">
@@ -15568,12 +15568,12 @@
     <row r="184">
       <c r="A184" s="1" t="inlineStr">
         <is>
-          <t>FER0188</t>
+          <t>FER0190</t>
         </is>
       </c>
       <c r="B184" s="1" t="inlineStr">
         <is>
-          <t>UB0188</t>
+          <t>UB0190</t>
         </is>
       </c>
       <c r="C184" s="1" t="inlineStr">
@@ -15585,12 +15585,12 @@
     <row r="185">
       <c r="A185" s="1" t="inlineStr">
         <is>
-          <t>FER0190</t>
+          <t>FER0191</t>
         </is>
       </c>
       <c r="B185" s="1" t="inlineStr">
         <is>
-          <t>UB0190</t>
+          <t>UB0191</t>
         </is>
       </c>
       <c r="C185" s="1" t="inlineStr">
@@ -15602,12 +15602,12 @@
     <row r="186">
       <c r="A186" s="1" t="inlineStr">
         <is>
-          <t>FER0191</t>
+          <t>FER0192</t>
         </is>
       </c>
       <c r="B186" s="1" t="inlineStr">
         <is>
-          <t>UB0191</t>
+          <t>UB0192</t>
         </is>
       </c>
       <c r="C186" s="1" t="inlineStr">
@@ -15619,12 +15619,12 @@
     <row r="187">
       <c r="A187" s="1" t="inlineStr">
         <is>
-          <t>FER0192</t>
+          <t>FER0193</t>
         </is>
       </c>
       <c r="B187" s="1" t="inlineStr">
         <is>
-          <t>UB0192</t>
+          <t>UB0193</t>
         </is>
       </c>
       <c r="C187" s="1" t="inlineStr">
@@ -15636,12 +15636,12 @@
     <row r="188">
       <c r="A188" s="1" t="inlineStr">
         <is>
-          <t>FER0193</t>
+          <t>FER0194</t>
         </is>
       </c>
       <c r="B188" s="1" t="inlineStr">
         <is>
-          <t>UB0193</t>
+          <t>UB0194</t>
         </is>
       </c>
       <c r="C188" s="1" t="inlineStr">
@@ -15653,12 +15653,12 @@
     <row r="189">
       <c r="A189" s="1" t="inlineStr">
         <is>
-          <t>FER0194</t>
+          <t>FER0195</t>
         </is>
       </c>
       <c r="B189" s="1" t="inlineStr">
         <is>
-          <t>UB0194</t>
+          <t>UB0195</t>
         </is>
       </c>
       <c r="C189" s="1" t="inlineStr">
@@ -15670,12 +15670,12 @@
     <row r="190">
       <c r="A190" s="1" t="inlineStr">
         <is>
-          <t>FER0195</t>
+          <t>FER0196</t>
         </is>
       </c>
       <c r="B190" s="1" t="inlineStr">
         <is>
-          <t>UB0195</t>
+          <t>UB0196</t>
         </is>
       </c>
       <c r="C190" s="1" t="inlineStr">
@@ -15687,12 +15687,12 @@
     <row r="191">
       <c r="A191" s="1" t="inlineStr">
         <is>
-          <t>FER0196</t>
+          <t>FER0197</t>
         </is>
       </c>
       <c r="B191" s="1" t="inlineStr">
         <is>
-          <t>UB0196</t>
+          <t>UB0197</t>
         </is>
       </c>
       <c r="C191" s="1" t="inlineStr">
@@ -15704,12 +15704,12 @@
     <row r="192">
       <c r="A192" s="1" t="inlineStr">
         <is>
-          <t>FER0197</t>
+          <t>FER0198</t>
         </is>
       </c>
       <c r="B192" s="1" t="inlineStr">
         <is>
-          <t>UB0197</t>
+          <t>UB0198</t>
         </is>
       </c>
       <c r="C192" s="1" t="inlineStr">
@@ -15721,12 +15721,12 @@
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
         <is>
-          <t>FER0198</t>
+          <t>FER0199</t>
         </is>
       </c>
       <c r="B193" s="1" t="inlineStr">
         <is>
-          <t>UB0198</t>
+          <t>UB0199</t>
         </is>
       </c>
       <c r="C193" s="1" t="inlineStr">
@@ -15738,12 +15738,12 @@
     <row r="194">
       <c r="A194" s="1" t="inlineStr">
         <is>
-          <t>FER0199</t>
+          <t>FER0200</t>
         </is>
       </c>
       <c r="B194" s="1" t="inlineStr">
         <is>
-          <t>UB0199</t>
+          <t>UB0200</t>
         </is>
       </c>
       <c r="C194" s="1" t="inlineStr">
@@ -15755,12 +15755,12 @@
     <row r="195">
       <c r="A195" s="1" t="inlineStr">
         <is>
-          <t>FER0200</t>
+          <t>FER0006</t>
         </is>
       </c>
       <c r="B195" s="1" t="inlineStr">
         <is>
-          <t>UB0200</t>
+          <t>UB0006</t>
         </is>
       </c>
       <c r="C195" s="1" t="inlineStr">
@@ -15772,17 +15772,17 @@
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
         <is>
-          <t>FER0006</t>
+          <t>FER0189</t>
         </is>
       </c>
       <c r="B196" s="1" t="inlineStr">
         <is>
-          <t>UB0006</t>
+          <t>UB0189</t>
         </is>
       </c>
       <c r="C196" s="1" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -15794,24 +15794,24 @@
       </c>
       <c r="B197" s="1" t="inlineStr">
         <is>
-          <t>UB0189</t>
+          <t>UB0001</t>
         </is>
       </c>
       <c r="C197" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="inlineStr">
         <is>
-          <t>FER0189</t>
+          <t>FER0029</t>
         </is>
       </c>
       <c r="B198" s="1" t="inlineStr">
         <is>
-          <t>UB0001</t>
+          <t>UB0029</t>
         </is>
       </c>
       <c r="C198" s="1" t="inlineStr">
@@ -15823,12 +15823,12 @@
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
         <is>
-          <t>FER0029</t>
+          <t>FER0042</t>
         </is>
       </c>
       <c r="B199" s="1" t="inlineStr">
         <is>
-          <t>UB0029</t>
+          <t>UB0042</t>
         </is>
       </c>
       <c r="C199" s="1" t="inlineStr">
@@ -15845,12 +15845,12 @@
       </c>
       <c r="B200" s="1" t="inlineStr">
         <is>
-          <t>UB0042</t>
+          <t>UB0005</t>
         </is>
       </c>
       <c r="C200" s="1" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -15862,7 +15862,7 @@
       </c>
       <c r="B201" s="1" t="inlineStr">
         <is>
-          <t>UB0005</t>
+          <t>UB0015</t>
         </is>
       </c>
       <c r="C201" s="1" t="inlineStr">
@@ -15874,29 +15874,29 @@
     <row r="202">
       <c r="A202" s="1" t="inlineStr">
         <is>
-          <t>FER0042</t>
+          <t>FER0001</t>
         </is>
       </c>
       <c r="B202" s="1" t="inlineStr">
         <is>
-          <t>UB0015</t>
+          <t>UB0001</t>
         </is>
       </c>
       <c r="C202" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="inlineStr">
         <is>
-          <t>FER0001</t>
+          <t>FER0041</t>
         </is>
       </c>
       <c r="B203" s="1" t="inlineStr">
         <is>
-          <t>UB0001</t>
+          <t>UB0041</t>
         </is>
       </c>
       <c r="C203" s="1" t="inlineStr">
@@ -15908,12 +15908,12 @@
     <row r="204">
       <c r="A204" s="1" t="inlineStr">
         <is>
-          <t>FER0041</t>
+          <t>FER0088</t>
         </is>
       </c>
       <c r="B204" s="1" t="inlineStr">
         <is>
-          <t>UB0041</t>
+          <t>UB0088</t>
         </is>
       </c>
       <c r="C204" s="1" t="inlineStr">

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -2815,7 +2815,7 @@
       </c>
       <c r="D89" s="1" t="inlineStr">
         <is>
-          <t>Caja eléctrica PVC 2 x 4 pulg. Artículo de ferretería para trabajos y proyectos relacionados con electricidad e iluminación 88.</t>
+          <t>Caja eléctrica PVC 2 x 4 pulg. Artículo de ferretería para trabajos y proyectos relacionados con electricidad e iluminación 33 7.</t>
         </is>
       </c>
       <c r="E89" s="1" t="inlineStr">

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -1573,7 +1573,7 @@
       </c>
       <c r="D43" s="1" t="inlineStr">
         <is>
-          <t>Clavos comunes 2 pulg. Artículo de ferretería para trabajos y proyectos relacionados con tornillería y fijaciones. Esta en tres areas</t>
+          <t>Clavos comunes 2 pulg. Artículo de ferretería para trabajos y proyectos relacionados con tornillería y fijaciones. Esta en tres areas 55</t>
         </is>
       </c>
       <c r="E43" s="1" t="inlineStr">
@@ -12451,7 +12451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C204"/>
+  <dimension ref="A1:C205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15823,12 +15823,12 @@
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
         <is>
-          <t>FER0042</t>
+          <t>FER0001</t>
         </is>
       </c>
       <c r="B199" s="1" t="inlineStr">
         <is>
-          <t>UB0042</t>
+          <t>UB0001</t>
         </is>
       </c>
       <c r="C199" s="1" t="inlineStr">
@@ -15840,46 +15840,46 @@
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
         <is>
-          <t>FER0042</t>
+          <t>FER0041</t>
         </is>
       </c>
       <c r="B200" s="1" t="inlineStr">
         <is>
-          <t>UB0005</t>
+          <t>UB0041</t>
         </is>
       </c>
       <c r="C200" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="inlineStr">
         <is>
-          <t>FER0042</t>
+          <t>FER0088</t>
         </is>
       </c>
       <c r="B201" s="1" t="inlineStr">
         <is>
-          <t>UB0015</t>
+          <t>UB0088</t>
         </is>
       </c>
       <c r="C201" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="inlineStr">
         <is>
-          <t>FER0001</t>
+          <t>FER0042</t>
         </is>
       </c>
       <c r="B202" s="1" t="inlineStr">
         <is>
-          <t>UB0001</t>
+          <t>UB0042</t>
         </is>
       </c>
       <c r="C202" s="1" t="inlineStr">
@@ -15891,34 +15891,51 @@
     <row r="203">
       <c r="A203" s="1" t="inlineStr">
         <is>
-          <t>FER0041</t>
+          <t>FER0042</t>
         </is>
       </c>
       <c r="B203" s="1" t="inlineStr">
         <is>
-          <t>UB0041</t>
+          <t>UB0005</t>
         </is>
       </c>
       <c r="C203" s="1" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="inlineStr">
         <is>
-          <t>FER0088</t>
+          <t>FER0042</t>
         </is>
       </c>
       <c r="B204" s="1" t="inlineStr">
         <is>
-          <t>UB0088</t>
+          <t>UB0015</t>
         </is>
       </c>
       <c r="C204" s="1" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="inlineStr">
+        <is>
+          <t>FER0042</t>
+        </is>
+      </c>
+      <c r="B205" s="1" t="inlineStr">
+        <is>
+          <t>UB0006</t>
+        </is>
+      </c>
+      <c r="C205" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -5990,7 +5990,7 @@
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>Adhesivos y mantenimiento</t>
+          <t>Adhesivos y mantenimiento11</t>
         </is>
       </c>
     </row>

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -5859,7 +5859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5991,6 +5991,18 @@
       <c r="B11" s="1" t="inlineStr">
         <is>
           <t>Adhesivos y mantenimiento11</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>CAT011 — Adhesivos y mantenimiento11</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>test</t>
         </is>
       </c>
     </row>

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -6017,7 +6017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F201"/>
+  <dimension ref="A1:F202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12447,6 +12447,38 @@
         </is>
       </c>
       <c r="F201" s="1" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="inlineStr">
+        <is>
+          <t>UB0201</t>
+        </is>
+      </c>
+      <c r="B202" s="1" t="inlineStr">
+        <is>
+          <t>Test1</t>
+        </is>
+      </c>
+      <c r="C202" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D202" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E202" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F202" s="1" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -12495,7 +12495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C205"/>
+  <dimension ref="A1:C206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15867,12 +15867,12 @@
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
         <is>
-          <t>FER0001</t>
+          <t>FER0041</t>
         </is>
       </c>
       <c r="B199" s="1" t="inlineStr">
         <is>
-          <t>UB0001</t>
+          <t>UB0041</t>
         </is>
       </c>
       <c r="C199" s="1" t="inlineStr">
@@ -15884,12 +15884,12 @@
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
         <is>
-          <t>FER0041</t>
+          <t>FER0088</t>
         </is>
       </c>
       <c r="B200" s="1" t="inlineStr">
         <is>
-          <t>UB0041</t>
+          <t>UB0088</t>
         </is>
       </c>
       <c r="C200" s="1" t="inlineStr">
@@ -15901,12 +15901,12 @@
     <row r="201">
       <c r="A201" s="1" t="inlineStr">
         <is>
-          <t>FER0088</t>
+          <t>FER0042</t>
         </is>
       </c>
       <c r="B201" s="1" t="inlineStr">
         <is>
-          <t>UB0088</t>
+          <t>UB0042</t>
         </is>
       </c>
       <c r="C201" s="1" t="inlineStr">
@@ -15923,12 +15923,12 @@
       </c>
       <c r="B202" s="1" t="inlineStr">
         <is>
-          <t>UB0042</t>
+          <t>UB0005</t>
         </is>
       </c>
       <c r="C202" s="1" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -15940,7 +15940,7 @@
       </c>
       <c r="B203" s="1" t="inlineStr">
         <is>
-          <t>UB0005</t>
+          <t>UB0015</t>
         </is>
       </c>
       <c r="C203" s="1" t="inlineStr">
@@ -15957,7 +15957,7 @@
       </c>
       <c r="B204" s="1" t="inlineStr">
         <is>
-          <t>UB0015</t>
+          <t>UB0006</t>
         </is>
       </c>
       <c r="C204" s="1" t="inlineStr">
@@ -15969,15 +15969,32 @@
     <row r="205">
       <c r="A205" s="1" t="inlineStr">
         <is>
-          <t>FER0042</t>
+          <t>FER0001</t>
         </is>
       </c>
       <c r="B205" s="1" t="inlineStr">
         <is>
-          <t>UB0006</t>
+          <t>UB0001</t>
         </is>
       </c>
       <c r="C205" s="1" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="inlineStr">
+        <is>
+          <t>FER0001</t>
+        </is>
+      </c>
+      <c r="B206" s="1" t="inlineStr">
+        <is>
+          <t>UB0201</t>
+        </is>
+      </c>
+      <c r="C206" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -12495,7 +12495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C206"/>
+  <dimension ref="A1:C205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15983,23 +15983,6 @@
         </is>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" s="1" t="inlineStr">
-        <is>
-          <t>FER0001</t>
-        </is>
-      </c>
-      <c r="B206" s="1" t="inlineStr">
-        <is>
-          <t>UB0201</t>
-        </is>
-      </c>
-      <c r="C206" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -12465,12 +12465,12 @@
       </c>
       <c r="C202" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D202" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E202" s="1" t="inlineStr">

--- a/03_Aplicacion/inventario.xlsx
+++ b/03_Aplicacion/inventario.xlsx
@@ -12495,7 +12495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C205"/>
+  <dimension ref="A1:C206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15983,6 +15983,23 @@
         </is>
       </c>
     </row>
+    <row r="206">
+      <c r="A206" s="1" t="inlineStr">
+        <is>
+          <t>FER0001</t>
+        </is>
+      </c>
+      <c r="B206" s="1" t="inlineStr">
+        <is>
+          <t>UB0201</t>
+        </is>
+      </c>
+      <c r="C206" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
